--- a/latest-events.xlsx
+++ b/latest-events.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1287"/>
+  <dimension ref="A1:D1288"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5274,13 +5274,13 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B349">
-        <v>6598</v>
+        <v>6597</v>
       </c>
       <c r="C349" t="str">
-        <v>2026-07-30 22:46:18</v>
+        <v>2026-08-03 01:42:24</v>
       </c>
       <c r="D349" t="str">
         <v>SI</v>
@@ -5294,7 +5294,7 @@
         <v>6598</v>
       </c>
       <c r="C350" t="str">
-        <v>2026-07-30 23:50:13</v>
+        <v>2026-07-30 22:46:18</v>
       </c>
       <c r="D350" t="str">
         <v>SI</v>
@@ -5308,10 +5308,10 @@
         <v>6598</v>
       </c>
       <c r="C351" t="str">
-        <v>2026-07-31 12:06:30</v>
+        <v>2026-07-30 23:50:13</v>
       </c>
       <c r="D351" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="352">
@@ -5322,7 +5322,7 @@
         <v>6598</v>
       </c>
       <c r="C352" t="str">
-        <v>2026-07-31 13:19:17</v>
+        <v>2026-07-31 12:06:30</v>
       </c>
       <c r="D352" t="str">
         <v>NO</v>
@@ -5336,7 +5336,7 @@
         <v>6598</v>
       </c>
       <c r="C353" t="str">
-        <v>2026-07-31 15:13:47</v>
+        <v>2026-07-31 13:19:17</v>
       </c>
       <c r="D353" t="str">
         <v>NO</v>
@@ -5350,7 +5350,7 @@
         <v>6598</v>
       </c>
       <c r="C354" t="str">
-        <v>2026-07-31 15:48:58</v>
+        <v>2026-07-31 15:13:47</v>
       </c>
       <c r="D354" t="str">
         <v>NO</v>
@@ -5364,7 +5364,7 @@
         <v>6598</v>
       </c>
       <c r="C355" t="str">
-        <v>2026-07-31 16:31:17</v>
+        <v>2026-07-31 15:48:58</v>
       </c>
       <c r="D355" t="str">
         <v>NO</v>
@@ -5378,7 +5378,7 @@
         <v>6598</v>
       </c>
       <c r="C356" t="str">
-        <v>2026-07-31 17:26:08</v>
+        <v>2026-07-31 16:31:17</v>
       </c>
       <c r="D356" t="str">
         <v>NO</v>
@@ -5392,10 +5392,10 @@
         <v>6598</v>
       </c>
       <c r="C357" t="str">
-        <v>2026-07-31 23:09:40</v>
+        <v>2026-07-31 17:26:08</v>
       </c>
       <c r="D357" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="358">
@@ -5406,7 +5406,7 @@
         <v>6598</v>
       </c>
       <c r="C358" t="str">
-        <v>2026-08-01 12:59:50</v>
+        <v>2026-07-31 23:09:40</v>
       </c>
       <c r="D358" t="str">
         <v>SI</v>
@@ -5420,7 +5420,7 @@
         <v>6598</v>
       </c>
       <c r="C359" t="str">
-        <v>2026-08-01 13:20:14</v>
+        <v>2026-08-01 12:59:50</v>
       </c>
       <c r="D359" t="str">
         <v>SI</v>
@@ -5434,7 +5434,7 @@
         <v>6598</v>
       </c>
       <c r="C360" t="str">
-        <v>2026-08-01 13:36:19</v>
+        <v>2026-08-01 13:20:14</v>
       </c>
       <c r="D360" t="str">
         <v>SI</v>
@@ -5448,7 +5448,7 @@
         <v>6598</v>
       </c>
       <c r="C361" t="str">
-        <v>2026-08-01 18:10:55</v>
+        <v>2026-08-01 13:36:19</v>
       </c>
       <c r="D361" t="str">
         <v>SI</v>
@@ -5462,7 +5462,7 @@
         <v>6598</v>
       </c>
       <c r="C362" t="str">
-        <v>2026-08-01 21:41:37</v>
+        <v>2026-08-01 18:10:55</v>
       </c>
       <c r="D362" t="str">
         <v>SI</v>
@@ -5476,7 +5476,7 @@
         <v>6598</v>
       </c>
       <c r="C363" t="str">
-        <v>2026-08-01 23:09:33</v>
+        <v>2026-08-01 21:41:37</v>
       </c>
       <c r="D363" t="str">
         <v>SI</v>
@@ -5490,7 +5490,7 @@
         <v>6598</v>
       </c>
       <c r="C364" t="str">
-        <v>2026-08-01 23:14:55</v>
+        <v>2026-08-01 23:09:33</v>
       </c>
       <c r="D364" t="str">
         <v>SI</v>
@@ -5504,7 +5504,7 @@
         <v>6598</v>
       </c>
       <c r="C365" t="str">
-        <v>2026-08-01 23:53:22</v>
+        <v>2026-08-01 23:14:55</v>
       </c>
       <c r="D365" t="str">
         <v>SI</v>
@@ -5518,7 +5518,7 @@
         <v>6598</v>
       </c>
       <c r="C366" t="str">
-        <v>2026-08-02 20:31:36</v>
+        <v>2026-08-01 23:53:22</v>
       </c>
       <c r="D366" t="str">
         <v>SI</v>
@@ -5532,7 +5532,7 @@
         <v>6598</v>
       </c>
       <c r="C367" t="str">
-        <v>2026-08-02 21:44:15</v>
+        <v>2026-08-02 20:31:36</v>
       </c>
       <c r="D367" t="str">
         <v>SI</v>
@@ -5540,16 +5540,16 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B368">
-        <v>6586</v>
+        <v>6598</v>
       </c>
       <c r="C368" t="str">
-        <v>2026-07-27 12:10:20</v>
+        <v>2026-08-02 21:44:15</v>
       </c>
       <c r="D368" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="369">
@@ -5560,7 +5560,7 @@
         <v>6586</v>
       </c>
       <c r="C369" t="str">
-        <v>2026-07-27 12:30:29</v>
+        <v>2026-07-27 12:10:20</v>
       </c>
       <c r="D369" t="str">
         <v>NO</v>
@@ -5574,7 +5574,7 @@
         <v>6586</v>
       </c>
       <c r="C370" t="str">
-        <v>2026-07-27 13:47:52</v>
+        <v>2026-07-27 12:30:29</v>
       </c>
       <c r="D370" t="str">
         <v>NO</v>
@@ -5588,7 +5588,7 @@
         <v>6586</v>
       </c>
       <c r="C371" t="str">
-        <v>2026-07-27 18:03:37</v>
+        <v>2026-07-27 13:47:52</v>
       </c>
       <c r="D371" t="str">
         <v>NO</v>
@@ -5602,10 +5602,10 @@
         <v>6586</v>
       </c>
       <c r="C372" t="str">
-        <v>2026-07-27 19:43:05</v>
+        <v>2026-07-27 18:03:37</v>
       </c>
       <c r="D372" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="373">
@@ -5616,10 +5616,10 @@
         <v>6586</v>
       </c>
       <c r="C373" t="str">
-        <v>2026-07-28 12:10:24</v>
+        <v>2026-07-27 19:43:05</v>
       </c>
       <c r="D373" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="374">
@@ -5630,7 +5630,7 @@
         <v>6586</v>
       </c>
       <c r="C374" t="str">
-        <v>2026-07-28 12:37:48</v>
+        <v>2026-07-28 12:10:24</v>
       </c>
       <c r="D374" t="str">
         <v>NO</v>
@@ -5644,7 +5644,7 @@
         <v>6586</v>
       </c>
       <c r="C375" t="str">
-        <v>2026-07-28 12:41:48</v>
+        <v>2026-07-28 12:37:48</v>
       </c>
       <c r="D375" t="str">
         <v>NO</v>
@@ -5658,7 +5658,7 @@
         <v>6586</v>
       </c>
       <c r="C376" t="str">
-        <v>2026-07-28 12:50:05</v>
+        <v>2026-07-28 12:41:48</v>
       </c>
       <c r="D376" t="str">
         <v>NO</v>
@@ -5672,7 +5672,7 @@
         <v>6586</v>
       </c>
       <c r="C377" t="str">
-        <v>2026-07-28 13:51:54</v>
+        <v>2026-07-28 12:50:05</v>
       </c>
       <c r="D377" t="str">
         <v>NO</v>
@@ -5686,7 +5686,7 @@
         <v>6586</v>
       </c>
       <c r="C378" t="str">
-        <v>2026-07-28 16:28:38</v>
+        <v>2026-07-28 13:51:54</v>
       </c>
       <c r="D378" t="str">
         <v>NO</v>
@@ -5700,7 +5700,7 @@
         <v>6586</v>
       </c>
       <c r="C379" t="str">
-        <v>2026-07-28 18:19:48</v>
+        <v>2026-07-28 16:28:38</v>
       </c>
       <c r="D379" t="str">
         <v>NO</v>
@@ -5714,7 +5714,7 @@
         <v>6586</v>
       </c>
       <c r="C380" t="str">
-        <v>2026-07-28 18:43:03</v>
+        <v>2026-07-28 18:19:48</v>
       </c>
       <c r="D380" t="str">
         <v>NO</v>
@@ -5728,10 +5728,10 @@
         <v>6586</v>
       </c>
       <c r="C381" t="str">
-        <v>2026-07-28 19:06:32</v>
+        <v>2026-07-28 18:43:03</v>
       </c>
       <c r="D381" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="382">
@@ -5742,7 +5742,7 @@
         <v>6586</v>
       </c>
       <c r="C382" t="str">
-        <v>2026-07-28 19:48:12</v>
+        <v>2026-07-28 19:06:32</v>
       </c>
       <c r="D382" t="str">
         <v>SI</v>
@@ -5756,7 +5756,7 @@
         <v>6586</v>
       </c>
       <c r="C383" t="str">
-        <v>2026-07-28 19:54:43</v>
+        <v>2026-07-28 19:48:12</v>
       </c>
       <c r="D383" t="str">
         <v>SI</v>
@@ -5770,7 +5770,7 @@
         <v>6586</v>
       </c>
       <c r="C384" t="str">
-        <v>2026-07-28 20:36:45</v>
+        <v>2026-07-28 19:54:43</v>
       </c>
       <c r="D384" t="str">
         <v>SI</v>
@@ -5784,10 +5784,10 @@
         <v>6586</v>
       </c>
       <c r="C385" t="str">
-        <v>2026-07-29 12:04:34</v>
+        <v>2026-07-28 20:36:45</v>
       </c>
       <c r="D385" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="386">
@@ -5798,7 +5798,7 @@
         <v>6586</v>
       </c>
       <c r="C386" t="str">
-        <v>2026-07-29 13:10:02</v>
+        <v>2026-07-29 12:04:34</v>
       </c>
       <c r="D386" t="str">
         <v>NO</v>
@@ -5812,7 +5812,7 @@
         <v>6586</v>
       </c>
       <c r="C387" t="str">
-        <v>2026-07-29 13:36:54</v>
+        <v>2026-07-29 13:10:02</v>
       </c>
       <c r="D387" t="str">
         <v>NO</v>
@@ -5826,7 +5826,7 @@
         <v>6586</v>
       </c>
       <c r="C388" t="str">
-        <v>2026-07-29 13:40:09</v>
+        <v>2026-07-29 13:36:54</v>
       </c>
       <c r="D388" t="str">
         <v>NO</v>
@@ -5840,7 +5840,7 @@
         <v>6586</v>
       </c>
       <c r="C389" t="str">
-        <v>2026-07-29 13:41:56</v>
+        <v>2026-07-29 13:40:09</v>
       </c>
       <c r="D389" t="str">
         <v>NO</v>
@@ -5854,7 +5854,7 @@
         <v>6586</v>
       </c>
       <c r="C390" t="str">
-        <v>2026-07-29 13:53:52</v>
+        <v>2026-07-29 13:41:56</v>
       </c>
       <c r="D390" t="str">
         <v>NO</v>
@@ -5868,7 +5868,7 @@
         <v>6586</v>
       </c>
       <c r="C391" t="str">
-        <v>2026-07-29 14:45:05</v>
+        <v>2026-07-29 13:53:52</v>
       </c>
       <c r="D391" t="str">
         <v>NO</v>
@@ -5882,7 +5882,7 @@
         <v>6586</v>
       </c>
       <c r="C392" t="str">
-        <v>2026-07-29 15:08:44</v>
+        <v>2026-07-29 14:45:05</v>
       </c>
       <c r="D392" t="str">
         <v>NO</v>
@@ -5896,7 +5896,7 @@
         <v>6586</v>
       </c>
       <c r="C393" t="str">
-        <v>2026-07-29 15:22:00</v>
+        <v>2026-07-29 15:08:44</v>
       </c>
       <c r="D393" t="str">
         <v>NO</v>
@@ -5910,7 +5910,7 @@
         <v>6586</v>
       </c>
       <c r="C394" t="str">
-        <v>2026-07-29 17:57:08</v>
+        <v>2026-07-29 15:22:00</v>
       </c>
       <c r="D394" t="str">
         <v>NO</v>
@@ -5924,7 +5924,7 @@
         <v>6586</v>
       </c>
       <c r="C395" t="str">
-        <v>2026-07-29 18:16:38</v>
+        <v>2026-07-29 17:57:08</v>
       </c>
       <c r="D395" t="str">
         <v>NO</v>
@@ -5938,7 +5938,7 @@
         <v>6586</v>
       </c>
       <c r="C396" t="str">
-        <v>2026-07-29 18:34:44</v>
+        <v>2026-07-29 18:16:38</v>
       </c>
       <c r="D396" t="str">
         <v>NO</v>
@@ -5952,10 +5952,10 @@
         <v>6586</v>
       </c>
       <c r="C397" t="str">
-        <v>2026-07-29 19:35:50</v>
+        <v>2026-07-29 18:34:44</v>
       </c>
       <c r="D397" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="398">
@@ -5966,7 +5966,7 @@
         <v>6586</v>
       </c>
       <c r="C398" t="str">
-        <v>2026-07-29 20:28:49</v>
+        <v>2026-07-29 19:35:50</v>
       </c>
       <c r="D398" t="str">
         <v>SI</v>
@@ -5980,10 +5980,10 @@
         <v>6586</v>
       </c>
       <c r="C399" t="str">
-        <v>2026-07-30 12:10:06</v>
+        <v>2026-07-29 20:28:49</v>
       </c>
       <c r="D399" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="400">
@@ -5994,7 +5994,7 @@
         <v>6586</v>
       </c>
       <c r="C400" t="str">
-        <v>2026-07-30 12:45:52</v>
+        <v>2026-07-30 12:10:06</v>
       </c>
       <c r="D400" t="str">
         <v>NO</v>
@@ -6008,7 +6008,7 @@
         <v>6586</v>
       </c>
       <c r="C401" t="str">
-        <v>2026-07-30 13:27:50</v>
+        <v>2026-07-30 12:45:52</v>
       </c>
       <c r="D401" t="str">
         <v>NO</v>
@@ -6022,7 +6022,7 @@
         <v>6586</v>
       </c>
       <c r="C402" t="str">
-        <v>2026-07-30 13:35:16</v>
+        <v>2026-07-30 13:27:50</v>
       </c>
       <c r="D402" t="str">
         <v>NO</v>
@@ -6036,7 +6036,7 @@
         <v>6586</v>
       </c>
       <c r="C403" t="str">
-        <v>2026-07-30 13:54:12</v>
+        <v>2026-07-30 13:35:16</v>
       </c>
       <c r="D403" t="str">
         <v>NO</v>
@@ -6050,7 +6050,7 @@
         <v>6586</v>
       </c>
       <c r="C404" t="str">
-        <v>2026-07-30 14:11:22</v>
+        <v>2026-07-30 13:54:12</v>
       </c>
       <c r="D404" t="str">
         <v>NO</v>
@@ -6064,7 +6064,7 @@
         <v>6586</v>
       </c>
       <c r="C405" t="str">
-        <v>2026-07-30 14:33:26</v>
+        <v>2026-07-30 14:11:22</v>
       </c>
       <c r="D405" t="str">
         <v>NO</v>
@@ -6078,7 +6078,7 @@
         <v>6586</v>
       </c>
       <c r="C406" t="str">
-        <v>2026-07-30 16:23:24</v>
+        <v>2026-07-30 14:33:26</v>
       </c>
       <c r="D406" t="str">
         <v>NO</v>
@@ -6092,7 +6092,7 @@
         <v>6586</v>
       </c>
       <c r="C407" t="str">
-        <v>2026-07-30 17:57:22</v>
+        <v>2026-07-30 16:23:24</v>
       </c>
       <c r="D407" t="str">
         <v>NO</v>
@@ -6106,10 +6106,10 @@
         <v>6586</v>
       </c>
       <c r="C408" t="str">
-        <v>2026-07-30 20:06:50</v>
+        <v>2026-07-30 17:57:22</v>
       </c>
       <c r="D408" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="409">
@@ -6120,7 +6120,7 @@
         <v>6586</v>
       </c>
       <c r="C409" t="str">
-        <v>2026-07-30 20:31:32</v>
+        <v>2026-07-30 20:06:50</v>
       </c>
       <c r="D409" t="str">
         <v>SI</v>
@@ -6134,7 +6134,7 @@
         <v>6586</v>
       </c>
       <c r="C410" t="str">
-        <v>2026-07-30 20:40:54</v>
+        <v>2026-07-30 20:31:32</v>
       </c>
       <c r="D410" t="str">
         <v>SI</v>
@@ -6148,10 +6148,10 @@
         <v>6586</v>
       </c>
       <c r="C411" t="str">
-        <v>2026-07-31 12:23:02</v>
+        <v>2026-07-30 20:40:54</v>
       </c>
       <c r="D411" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="412">
@@ -6162,7 +6162,7 @@
         <v>6586</v>
       </c>
       <c r="C412" t="str">
-        <v>2026-07-31 13:24:08</v>
+        <v>2026-07-31 12:23:02</v>
       </c>
       <c r="D412" t="str">
         <v>NO</v>
@@ -6176,7 +6176,7 @@
         <v>6586</v>
       </c>
       <c r="C413" t="str">
-        <v>2026-07-31 18:09:44</v>
+        <v>2026-07-31 13:24:08</v>
       </c>
       <c r="D413" t="str">
         <v>NO</v>
@@ -6190,10 +6190,10 @@
         <v>6586</v>
       </c>
       <c r="C414" t="str">
-        <v>2026-07-31 19:21:37</v>
+        <v>2026-07-31 18:09:44</v>
       </c>
       <c r="D414" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="415">
@@ -6204,7 +6204,7 @@
         <v>6586</v>
       </c>
       <c r="C415" t="str">
-        <v>2026-07-31 19:38:12</v>
+        <v>2026-07-31 19:21:37</v>
       </c>
       <c r="D415" t="str">
         <v>SI</v>
@@ -6212,16 +6212,16 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B416">
-        <v>6604</v>
+        <v>6586</v>
       </c>
       <c r="C416" t="str">
-        <v>2026-07-27 14:15:16</v>
+        <v>2026-07-31 19:38:12</v>
       </c>
       <c r="D416" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="417">
@@ -6232,7 +6232,7 @@
         <v>6604</v>
       </c>
       <c r="C417" t="str">
-        <v>2026-07-27 14:56:14</v>
+        <v>2026-07-27 14:15:16</v>
       </c>
       <c r="D417" t="str">
         <v>NO</v>
@@ -6246,7 +6246,7 @@
         <v>6604</v>
       </c>
       <c r="C418" t="str">
-        <v>2026-07-27 15:10:07</v>
+        <v>2026-07-27 14:56:14</v>
       </c>
       <c r="D418" t="str">
         <v>NO</v>
@@ -6260,7 +6260,7 @@
         <v>6604</v>
       </c>
       <c r="C419" t="str">
-        <v>2026-07-29 13:48:13</v>
+        <v>2026-07-27 15:10:07</v>
       </c>
       <c r="D419" t="str">
         <v>NO</v>
@@ -6274,7 +6274,7 @@
         <v>6604</v>
       </c>
       <c r="C420" t="str">
-        <v>2026-07-29 18:35:06</v>
+        <v>2026-07-29 13:48:13</v>
       </c>
       <c r="D420" t="str">
         <v>NO</v>
@@ -6288,7 +6288,7 @@
         <v>6604</v>
       </c>
       <c r="C421" t="str">
-        <v>2026-07-30 14:30:59</v>
+        <v>2026-07-29 18:35:06</v>
       </c>
       <c r="D421" t="str">
         <v>NO</v>
@@ -6302,7 +6302,7 @@
         <v>6604</v>
       </c>
       <c r="C422" t="str">
-        <v>2026-07-30 18:22:45</v>
+        <v>2026-07-30 14:30:59</v>
       </c>
       <c r="D422" t="str">
         <v>NO</v>
@@ -6310,13 +6310,13 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B423">
-        <v>6601</v>
+        <v>6604</v>
       </c>
       <c r="C423" t="str">
-        <v>2026-07-30 16:03:58</v>
+        <v>2026-07-30 18:22:45</v>
       </c>
       <c r="D423" t="str">
         <v>NO</v>
@@ -6330,7 +6330,7 @@
         <v>6601</v>
       </c>
       <c r="C424" t="str">
-        <v>2026-07-30 18:13:18</v>
+        <v>2026-07-30 16:03:58</v>
       </c>
       <c r="D424" t="str">
         <v>NO</v>
@@ -6344,10 +6344,10 @@
         <v>6601</v>
       </c>
       <c r="C425" t="str">
-        <v>2026-07-30 20:05:46</v>
+        <v>2026-07-30 18:13:18</v>
       </c>
       <c r="D425" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="426">
@@ -6358,10 +6358,10 @@
         <v>6601</v>
       </c>
       <c r="C426" t="str">
-        <v>2026-07-31 13:32:02</v>
+        <v>2026-07-30 20:05:46</v>
       </c>
       <c r="D426" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="427">
@@ -6372,7 +6372,7 @@
         <v>6601</v>
       </c>
       <c r="C427" t="str">
-        <v>2026-07-31 13:49:26</v>
+        <v>2026-07-31 13:32:02</v>
       </c>
       <c r="D427" t="str">
         <v>NO</v>
@@ -6386,7 +6386,7 @@
         <v>6601</v>
       </c>
       <c r="C428" t="str">
-        <v>2026-07-31 14:28:52</v>
+        <v>2026-07-31 13:49:26</v>
       </c>
       <c r="D428" t="str">
         <v>NO</v>
@@ -6400,7 +6400,7 @@
         <v>6601</v>
       </c>
       <c r="C429" t="str">
-        <v>2026-07-31 16:42:07</v>
+        <v>2026-07-31 14:28:52</v>
       </c>
       <c r="D429" t="str">
         <v>NO</v>
@@ -6414,7 +6414,7 @@
         <v>6601</v>
       </c>
       <c r="C430" t="str">
-        <v>2026-07-31 17:03:10</v>
+        <v>2026-07-31 16:42:07</v>
       </c>
       <c r="D430" t="str">
         <v>NO</v>
@@ -6422,13 +6422,13 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B431">
-        <v>6606</v>
+        <v>6601</v>
       </c>
       <c r="C431" t="str">
-        <v>2026-07-30 15:13:24</v>
+        <v>2026-07-31 17:03:10</v>
       </c>
       <c r="D431" t="str">
         <v>NO</v>
@@ -6442,7 +6442,7 @@
         <v>6606</v>
       </c>
       <c r="C432" t="str">
-        <v>2026-07-30 15:29:06</v>
+        <v>2026-07-30 15:13:24</v>
       </c>
       <c r="D432" t="str">
         <v>NO</v>
@@ -6456,7 +6456,7 @@
         <v>6606</v>
       </c>
       <c r="C433" t="str">
-        <v>2026-07-30 15:46:42</v>
+        <v>2026-07-30 15:29:06</v>
       </c>
       <c r="D433" t="str">
         <v>NO</v>
@@ -6470,7 +6470,7 @@
         <v>6606</v>
       </c>
       <c r="C434" t="str">
-        <v>2026-07-30 17:16:19</v>
+        <v>2026-07-30 15:46:42</v>
       </c>
       <c r="D434" t="str">
         <v>NO</v>
@@ -6484,7 +6484,7 @@
         <v>6606</v>
       </c>
       <c r="C435" t="str">
-        <v>2026-07-30 18:25:22</v>
+        <v>2026-07-30 17:16:19</v>
       </c>
       <c r="D435" t="str">
         <v>NO</v>
@@ -6498,7 +6498,7 @@
         <v>6606</v>
       </c>
       <c r="C436" t="str">
-        <v>2026-07-30 18:25:23</v>
+        <v>2026-07-30 18:25:22</v>
       </c>
       <c r="D436" t="str">
         <v>NO</v>
@@ -6512,10 +6512,10 @@
         <v>6606</v>
       </c>
       <c r="C437" t="str">
-        <v>2026-07-30 19:01:25</v>
+        <v>2026-07-30 18:25:23</v>
       </c>
       <c r="D437" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="438">
@@ -6526,7 +6526,7 @@
         <v>6606</v>
       </c>
       <c r="C438" t="str">
-        <v>2026-07-30 19:38:30</v>
+        <v>2026-07-30 19:01:25</v>
       </c>
       <c r="D438" t="str">
         <v>SI</v>
@@ -6540,7 +6540,7 @@
         <v>6606</v>
       </c>
       <c r="C439" t="str">
-        <v>2026-07-30 20:07:37</v>
+        <v>2026-07-30 19:38:30</v>
       </c>
       <c r="D439" t="str">
         <v>SI</v>
@@ -6554,7 +6554,7 @@
         <v>6606</v>
       </c>
       <c r="C440" t="str">
-        <v>2026-07-30 20:41:04</v>
+        <v>2026-07-30 20:07:37</v>
       </c>
       <c r="D440" t="str">
         <v>SI</v>
@@ -6568,7 +6568,7 @@
         <v>6606</v>
       </c>
       <c r="C441" t="str">
-        <v>2026-07-30 21:07:42</v>
+        <v>2026-07-30 20:41:04</v>
       </c>
       <c r="D441" t="str">
         <v>SI</v>
@@ -6582,7 +6582,7 @@
         <v>6606</v>
       </c>
       <c r="C442" t="str">
-        <v>2026-07-30 21:54:53</v>
+        <v>2026-07-30 21:07:42</v>
       </c>
       <c r="D442" t="str">
         <v>SI</v>
@@ -6596,7 +6596,7 @@
         <v>6606</v>
       </c>
       <c r="C443" t="str">
-        <v>2026-07-31 00:48:27</v>
+        <v>2026-07-30 21:54:53</v>
       </c>
       <c r="D443" t="str">
         <v>SI</v>
@@ -6610,7 +6610,7 @@
         <v>6606</v>
       </c>
       <c r="C444" t="str">
-        <v>2026-07-31 01:22:26</v>
+        <v>2026-07-31 00:48:27</v>
       </c>
       <c r="D444" t="str">
         <v>SI</v>
@@ -6624,7 +6624,7 @@
         <v>6606</v>
       </c>
       <c r="C445" t="str">
-        <v>2026-07-31 02:58:25</v>
+        <v>2026-07-31 01:22:26</v>
       </c>
       <c r="D445" t="str">
         <v>SI</v>
@@ -6638,7 +6638,7 @@
         <v>6606</v>
       </c>
       <c r="C446" t="str">
-        <v>2026-07-31 03:10:45</v>
+        <v>2026-07-31 02:58:25</v>
       </c>
       <c r="D446" t="str">
         <v>SI</v>
@@ -6652,7 +6652,7 @@
         <v>6606</v>
       </c>
       <c r="C447" t="str">
-        <v>2026-07-31 05:13:07</v>
+        <v>2026-07-31 03:10:45</v>
       </c>
       <c r="D447" t="str">
         <v>SI</v>
@@ -6666,7 +6666,7 @@
         <v>6606</v>
       </c>
       <c r="C448" t="str">
-        <v>2026-07-31 05:52:18</v>
+        <v>2026-07-31 05:13:07</v>
       </c>
       <c r="D448" t="str">
         <v>SI</v>
@@ -6680,7 +6680,7 @@
         <v>6606</v>
       </c>
       <c r="C449" t="str">
-        <v>2026-07-31 06:30:26</v>
+        <v>2026-07-31 05:52:18</v>
       </c>
       <c r="D449" t="str">
         <v>SI</v>
@@ -6694,10 +6694,10 @@
         <v>6606</v>
       </c>
       <c r="C450" t="str">
-        <v>2026-07-31 10:38:52</v>
+        <v>2026-07-31 06:30:26</v>
       </c>
       <c r="D450" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="451">
@@ -6708,7 +6708,7 @@
         <v>6606</v>
       </c>
       <c r="C451" t="str">
-        <v>2026-07-31 14:08:01</v>
+        <v>2026-07-31 10:38:52</v>
       </c>
       <c r="D451" t="str">
         <v>NO</v>
@@ -6722,7 +6722,7 @@
         <v>6606</v>
       </c>
       <c r="C452" t="str">
-        <v>2026-07-31 14:17:17</v>
+        <v>2026-07-31 14:08:01</v>
       </c>
       <c r="D452" t="str">
         <v>NO</v>
@@ -6736,7 +6736,7 @@
         <v>6606</v>
       </c>
       <c r="C453" t="str">
-        <v>2026-07-31 15:25:51</v>
+        <v>2026-07-31 14:17:17</v>
       </c>
       <c r="D453" t="str">
         <v>NO</v>
@@ -6750,7 +6750,7 @@
         <v>6606</v>
       </c>
       <c r="C454" t="str">
-        <v>2026-07-31 15:37:13</v>
+        <v>2026-07-31 15:25:51</v>
       </c>
       <c r="D454" t="str">
         <v>NO</v>
@@ -6764,7 +6764,7 @@
         <v>6606</v>
       </c>
       <c r="C455" t="str">
-        <v>2026-07-31 16:20:49</v>
+        <v>2026-07-31 15:37:13</v>
       </c>
       <c r="D455" t="str">
         <v>NO</v>
@@ -6778,7 +6778,7 @@
         <v>6606</v>
       </c>
       <c r="C456" t="str">
-        <v>2026-07-31 18:00:07</v>
+        <v>2026-07-31 16:20:49</v>
       </c>
       <c r="D456" t="str">
         <v>NO</v>
@@ -6792,10 +6792,10 @@
         <v>6606</v>
       </c>
       <c r="C457" t="str">
-        <v>2026-07-31 19:08:07</v>
+        <v>2026-07-31 18:00:07</v>
       </c>
       <c r="D457" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="458">
@@ -6806,7 +6806,7 @@
         <v>6606</v>
       </c>
       <c r="C458" t="str">
-        <v>2026-07-31 19:33:39</v>
+        <v>2026-07-31 19:08:07</v>
       </c>
       <c r="D458" t="str">
         <v>SI</v>
@@ -6820,7 +6820,7 @@
         <v>6606</v>
       </c>
       <c r="C459" t="str">
-        <v>2026-07-31 19:39:00</v>
+        <v>2026-07-31 19:33:39</v>
       </c>
       <c r="D459" t="str">
         <v>SI</v>
@@ -6834,7 +6834,7 @@
         <v>6606</v>
       </c>
       <c r="C460" t="str">
-        <v>2026-07-31 19:49:04</v>
+        <v>2026-07-31 19:39:00</v>
       </c>
       <c r="D460" t="str">
         <v>SI</v>
@@ -6848,7 +6848,7 @@
         <v>6606</v>
       </c>
       <c r="C461" t="str">
-        <v>2026-07-31 19:57:18</v>
+        <v>2026-07-31 19:49:04</v>
       </c>
       <c r="D461" t="str">
         <v>SI</v>
@@ -6862,7 +6862,7 @@
         <v>6606</v>
       </c>
       <c r="C462" t="str">
-        <v>2026-07-31 20:10:19</v>
+        <v>2026-07-31 19:57:18</v>
       </c>
       <c r="D462" t="str">
         <v>SI</v>
@@ -6876,7 +6876,7 @@
         <v>6606</v>
       </c>
       <c r="C463" t="str">
-        <v>2026-07-31 20:17:57</v>
+        <v>2026-07-31 20:10:19</v>
       </c>
       <c r="D463" t="str">
         <v>SI</v>
@@ -6890,7 +6890,7 @@
         <v>6606</v>
       </c>
       <c r="C464" t="str">
-        <v>2026-07-31 22:26:53</v>
+        <v>2026-07-31 20:17:57</v>
       </c>
       <c r="D464" t="str">
         <v>SI</v>
@@ -6904,7 +6904,7 @@
         <v>6606</v>
       </c>
       <c r="C465" t="str">
-        <v>2026-07-31 23:44:29</v>
+        <v>2026-07-31 22:26:53</v>
       </c>
       <c r="D465" t="str">
         <v>SI</v>
@@ -6918,7 +6918,7 @@
         <v>6606</v>
       </c>
       <c r="C466" t="str">
-        <v>2026-07-31 23:48:07</v>
+        <v>2026-07-31 23:44:29</v>
       </c>
       <c r="D466" t="str">
         <v>SI</v>
@@ -6932,7 +6932,7 @@
         <v>6606</v>
       </c>
       <c r="C467" t="str">
-        <v>2026-08-01 00:39:05</v>
+        <v>2026-07-31 23:48:07</v>
       </c>
       <c r="D467" t="str">
         <v>SI</v>
@@ -6946,7 +6946,7 @@
         <v>6606</v>
       </c>
       <c r="C468" t="str">
-        <v>2026-08-01 01:02:25</v>
+        <v>2026-08-01 00:39:05</v>
       </c>
       <c r="D468" t="str">
         <v>SI</v>
@@ -6960,7 +6960,7 @@
         <v>6606</v>
       </c>
       <c r="C469" t="str">
-        <v>2026-08-01 02:38:51</v>
+        <v>2026-08-01 01:02:25</v>
       </c>
       <c r="D469" t="str">
         <v>SI</v>
@@ -6974,7 +6974,7 @@
         <v>6606</v>
       </c>
       <c r="C470" t="str">
-        <v>2026-08-01 02:53:41</v>
+        <v>2026-08-01 02:38:51</v>
       </c>
       <c r="D470" t="str">
         <v>SI</v>
@@ -6988,7 +6988,7 @@
         <v>6606</v>
       </c>
       <c r="C471" t="str">
-        <v>2026-08-01 03:41:53</v>
+        <v>2026-08-01 02:53:41</v>
       </c>
       <c r="D471" t="str">
         <v>SI</v>
@@ -7002,7 +7002,7 @@
         <v>6606</v>
       </c>
       <c r="C472" t="str">
-        <v>2026-08-01 04:10:07</v>
+        <v>2026-08-01 03:41:53</v>
       </c>
       <c r="D472" t="str">
         <v>SI</v>
@@ -7016,7 +7016,7 @@
         <v>6606</v>
       </c>
       <c r="C473" t="str">
-        <v>2026-08-01 04:35:15</v>
+        <v>2026-08-01 04:10:07</v>
       </c>
       <c r="D473" t="str">
         <v>SI</v>
@@ -7030,7 +7030,7 @@
         <v>6606</v>
       </c>
       <c r="C474" t="str">
-        <v>2026-08-01 05:10:43</v>
+        <v>2026-08-01 04:35:15</v>
       </c>
       <c r="D474" t="str">
         <v>SI</v>
@@ -7044,7 +7044,7 @@
         <v>6606</v>
       </c>
       <c r="C475" t="str">
-        <v>2026-08-01 06:26:05</v>
+        <v>2026-08-01 05:10:43</v>
       </c>
       <c r="D475" t="str">
         <v>SI</v>
@@ -7058,7 +7058,7 @@
         <v>6606</v>
       </c>
       <c r="C476" t="str">
-        <v>2026-08-01 10:15:22</v>
+        <v>2026-08-01 06:26:05</v>
       </c>
       <c r="D476" t="str">
         <v>SI</v>
@@ -7072,7 +7072,7 @@
         <v>6606</v>
       </c>
       <c r="C477" t="str">
-        <v>2026-08-01 12:35:57</v>
+        <v>2026-08-01 10:15:22</v>
       </c>
       <c r="D477" t="str">
         <v>SI</v>
@@ -7086,7 +7086,7 @@
         <v>6606</v>
       </c>
       <c r="C478" t="str">
-        <v>2026-08-01 15:23:04</v>
+        <v>2026-08-01 12:35:57</v>
       </c>
       <c r="D478" t="str">
         <v>SI</v>
@@ -7100,7 +7100,7 @@
         <v>6606</v>
       </c>
       <c r="C479" t="str">
-        <v>2026-08-01 17:19:15</v>
+        <v>2026-08-01 15:23:04</v>
       </c>
       <c r="D479" t="str">
         <v>SI</v>
@@ -7114,7 +7114,7 @@
         <v>6606</v>
       </c>
       <c r="C480" t="str">
-        <v>2026-08-01 17:34:46</v>
+        <v>2026-08-01 17:19:15</v>
       </c>
       <c r="D480" t="str">
         <v>SI</v>
@@ -7128,7 +7128,7 @@
         <v>6606</v>
       </c>
       <c r="C481" t="str">
-        <v>2026-08-01 18:18:31</v>
+        <v>2026-08-01 17:34:46</v>
       </c>
       <c r="D481" t="str">
         <v>SI</v>
@@ -7142,7 +7142,7 @@
         <v>6606</v>
       </c>
       <c r="C482" t="str">
-        <v>2026-08-01 19:59:01</v>
+        <v>2026-08-01 18:18:31</v>
       </c>
       <c r="D482" t="str">
         <v>SI</v>
@@ -7156,7 +7156,7 @@
         <v>6606</v>
       </c>
       <c r="C483" t="str">
-        <v>2026-08-01 22:33:23</v>
+        <v>2026-08-01 19:59:01</v>
       </c>
       <c r="D483" t="str">
         <v>SI</v>
@@ -7170,7 +7170,7 @@
         <v>6606</v>
       </c>
       <c r="C484" t="str">
-        <v>2026-08-01 22:49:26</v>
+        <v>2026-08-01 22:33:23</v>
       </c>
       <c r="D484" t="str">
         <v>SI</v>
@@ -7184,7 +7184,7 @@
         <v>6606</v>
       </c>
       <c r="C485" t="str">
-        <v>2026-08-01 23:14:34</v>
+        <v>2026-08-01 22:49:26</v>
       </c>
       <c r="D485" t="str">
         <v>SI</v>
@@ -7198,7 +7198,7 @@
         <v>6606</v>
       </c>
       <c r="C486" t="str">
-        <v>2026-08-02 01:37:57</v>
+        <v>2026-08-01 23:14:34</v>
       </c>
       <c r="D486" t="str">
         <v>SI</v>
@@ -7212,7 +7212,7 @@
         <v>6606</v>
       </c>
       <c r="C487" t="str">
-        <v>2026-08-02 03:03:17</v>
+        <v>2026-08-02 01:37:57</v>
       </c>
       <c r="D487" t="str">
         <v>SI</v>
@@ -7226,7 +7226,7 @@
         <v>6606</v>
       </c>
       <c r="C488" t="str">
-        <v>2026-08-02 03:29:10</v>
+        <v>2026-08-02 03:03:17</v>
       </c>
       <c r="D488" t="str">
         <v>SI</v>
@@ -7240,7 +7240,7 @@
         <v>6606</v>
       </c>
       <c r="C489" t="str">
-        <v>2026-08-02 03:52:59</v>
+        <v>2026-08-02 03:29:10</v>
       </c>
       <c r="D489" t="str">
         <v>SI</v>
@@ -7254,7 +7254,7 @@
         <v>6606</v>
       </c>
       <c r="C490" t="str">
-        <v>2026-08-02 04:18:35</v>
+        <v>2026-08-02 03:52:59</v>
       </c>
       <c r="D490" t="str">
         <v>SI</v>
@@ -7268,7 +7268,7 @@
         <v>6606</v>
       </c>
       <c r="C491" t="str">
-        <v>2026-08-02 04:55:17</v>
+        <v>2026-08-02 04:18:35</v>
       </c>
       <c r="D491" t="str">
         <v>SI</v>
@@ -7282,7 +7282,7 @@
         <v>6606</v>
       </c>
       <c r="C492" t="str">
-        <v>2026-08-02 10:56:07</v>
+        <v>2026-08-02 04:55:17</v>
       </c>
       <c r="D492" t="str">
         <v>SI</v>
@@ -7296,7 +7296,7 @@
         <v>6606</v>
       </c>
       <c r="C493" t="str">
-        <v>2026-08-02 11:19:33</v>
+        <v>2026-08-02 10:56:07</v>
       </c>
       <c r="D493" t="str">
         <v>SI</v>
@@ -7310,7 +7310,7 @@
         <v>6606</v>
       </c>
       <c r="C494" t="str">
-        <v>2026-08-02 13:50:09</v>
+        <v>2026-08-02 11:19:33</v>
       </c>
       <c r="D494" t="str">
         <v>SI</v>
@@ -7324,7 +7324,7 @@
         <v>6606</v>
       </c>
       <c r="C495" t="str">
-        <v>2026-08-02 14:30:05</v>
+        <v>2026-08-02 13:50:09</v>
       </c>
       <c r="D495" t="str">
         <v>SI</v>
@@ -7338,7 +7338,7 @@
         <v>6606</v>
       </c>
       <c r="C496" t="str">
-        <v>2026-08-02 15:05:29</v>
+        <v>2026-08-02 14:30:05</v>
       </c>
       <c r="D496" t="str">
         <v>SI</v>
@@ -7352,7 +7352,7 @@
         <v>6606</v>
       </c>
       <c r="C497" t="str">
-        <v>2026-08-02 16:42:09</v>
+        <v>2026-08-02 15:05:29</v>
       </c>
       <c r="D497" t="str">
         <v>SI</v>
@@ -7366,7 +7366,7 @@
         <v>6606</v>
       </c>
       <c r="C498" t="str">
-        <v>2026-08-02 17:43:26</v>
+        <v>2026-08-02 16:42:09</v>
       </c>
       <c r="D498" t="str">
         <v>SI</v>
@@ -7380,7 +7380,7 @@
         <v>6606</v>
       </c>
       <c r="C499" t="str">
-        <v>2026-08-02 18:57:23</v>
+        <v>2026-08-02 17:43:26</v>
       </c>
       <c r="D499" t="str">
         <v>SI</v>
@@ -7394,7 +7394,7 @@
         <v>6606</v>
       </c>
       <c r="C500" t="str">
-        <v>2026-08-02 19:39:49</v>
+        <v>2026-08-02 18:57:23</v>
       </c>
       <c r="D500" t="str">
         <v>SI</v>
@@ -7408,7 +7408,7 @@
         <v>6606</v>
       </c>
       <c r="C501" t="str">
-        <v>2026-08-02 20:14:59</v>
+        <v>2026-08-02 19:39:49</v>
       </c>
       <c r="D501" t="str">
         <v>SI</v>
@@ -7422,7 +7422,7 @@
         <v>6606</v>
       </c>
       <c r="C502" t="str">
-        <v>2026-08-02 20:30:26</v>
+        <v>2026-08-02 20:14:59</v>
       </c>
       <c r="D502" t="str">
         <v>SI</v>
@@ -7436,7 +7436,7 @@
         <v>6606</v>
       </c>
       <c r="C503" t="str">
-        <v>2026-08-02 20:38:11</v>
+        <v>2026-08-02 20:30:26</v>
       </c>
       <c r="D503" t="str">
         <v>SI</v>
@@ -7450,7 +7450,7 @@
         <v>6606</v>
       </c>
       <c r="C504" t="str">
-        <v>2026-08-02 21:40:07</v>
+        <v>2026-08-02 20:38:11</v>
       </c>
       <c r="D504" t="str">
         <v>SI</v>
@@ -7464,7 +7464,7 @@
         <v>6606</v>
       </c>
       <c r="C505" t="str">
-        <v>2026-08-02 22:41:45</v>
+        <v>2026-08-02 21:40:07</v>
       </c>
       <c r="D505" t="str">
         <v>SI</v>
@@ -7472,16 +7472,16 @@
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B506">
-        <v>6580</v>
+        <v>6606</v>
       </c>
       <c r="C506" t="str">
-        <v>2026-07-30 15:06:09</v>
+        <v>2026-08-02 22:41:45</v>
       </c>
       <c r="D506" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="507">
@@ -7492,7 +7492,7 @@
         <v>6580</v>
       </c>
       <c r="C507" t="str">
-        <v>2026-07-30 15:49:59</v>
+        <v>2026-07-30 15:06:09</v>
       </c>
       <c r="D507" t="str">
         <v>NO</v>
@@ -7506,7 +7506,7 @@
         <v>6580</v>
       </c>
       <c r="C508" t="str">
-        <v>2026-07-30 16:24:09</v>
+        <v>2026-07-30 15:49:59</v>
       </c>
       <c r="D508" t="str">
         <v>NO</v>
@@ -7520,7 +7520,7 @@
         <v>6580</v>
       </c>
       <c r="C509" t="str">
-        <v>2026-07-30 17:01:57</v>
+        <v>2026-07-30 16:24:09</v>
       </c>
       <c r="D509" t="str">
         <v>NO</v>
@@ -7534,7 +7534,7 @@
         <v>6580</v>
       </c>
       <c r="C510" t="str">
-        <v>2026-07-30 17:55:23</v>
+        <v>2026-07-30 17:01:57</v>
       </c>
       <c r="D510" t="str">
         <v>NO</v>
@@ -7548,7 +7548,7 @@
         <v>6580</v>
       </c>
       <c r="C511" t="str">
-        <v>2026-07-30 18:49:05</v>
+        <v>2026-07-30 17:55:23</v>
       </c>
       <c r="D511" t="str">
         <v>NO</v>
@@ -7562,10 +7562,10 @@
         <v>6580</v>
       </c>
       <c r="C512" t="str">
-        <v>2026-07-30 19:11:11</v>
+        <v>2026-07-30 18:49:05</v>
       </c>
       <c r="D512" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="513">
@@ -7576,7 +7576,7 @@
         <v>6580</v>
       </c>
       <c r="C513" t="str">
-        <v>2026-07-30 20:02:33</v>
+        <v>2026-07-30 19:11:11</v>
       </c>
       <c r="D513" t="str">
         <v>SI</v>
@@ -7590,10 +7590,10 @@
         <v>6580</v>
       </c>
       <c r="C514" t="str">
-        <v>2026-07-31 12:16:04</v>
+        <v>2026-07-30 20:02:33</v>
       </c>
       <c r="D514" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="515">
@@ -7604,7 +7604,7 @@
         <v>6580</v>
       </c>
       <c r="C515" t="str">
-        <v>2026-07-31 15:21:22</v>
+        <v>2026-07-31 12:16:04</v>
       </c>
       <c r="D515" t="str">
         <v>NO</v>
@@ -7618,7 +7618,7 @@
         <v>6580</v>
       </c>
       <c r="C516" t="str">
-        <v>2026-07-31 17:26:48</v>
+        <v>2026-07-31 15:21:22</v>
       </c>
       <c r="D516" t="str">
         <v>NO</v>
@@ -7632,7 +7632,7 @@
         <v>6580</v>
       </c>
       <c r="C517" t="str">
-        <v>2026-07-31 17:58:53</v>
+        <v>2026-07-31 17:26:48</v>
       </c>
       <c r="D517" t="str">
         <v>NO</v>
@@ -7646,24 +7646,24 @@
         <v>6580</v>
       </c>
       <c r="C518" t="str">
-        <v>2026-07-31 19:10:57</v>
+        <v>2026-07-31 17:58:53</v>
       </c>
       <c r="D518" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B519">
-        <v>6594</v>
+        <v>6580</v>
       </c>
       <c r="C519" t="str">
-        <v>2026-07-30 14:53:24</v>
+        <v>2026-07-31 19:10:57</v>
       </c>
       <c r="D519" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="520">
@@ -7674,7 +7674,7 @@
         <v>6594</v>
       </c>
       <c r="C520" t="str">
-        <v>2026-07-30 14:55:39</v>
+        <v>2026-07-30 14:53:24</v>
       </c>
       <c r="D520" t="str">
         <v>NO</v>
@@ -7688,7 +7688,7 @@
         <v>6594</v>
       </c>
       <c r="C521" t="str">
-        <v>2026-07-30 14:58:32</v>
+        <v>2026-07-30 14:55:39</v>
       </c>
       <c r="D521" t="str">
         <v>NO</v>
@@ -7702,7 +7702,7 @@
         <v>6594</v>
       </c>
       <c r="C522" t="str">
-        <v>2026-07-30 14:59:13</v>
+        <v>2026-07-30 14:58:32</v>
       </c>
       <c r="D522" t="str">
         <v>NO</v>
@@ -7716,7 +7716,7 @@
         <v>6594</v>
       </c>
       <c r="C523" t="str">
-        <v>2026-07-30 15:28:55</v>
+        <v>2026-07-30 14:59:13</v>
       </c>
       <c r="D523" t="str">
         <v>NO</v>
@@ -7730,7 +7730,7 @@
         <v>6594</v>
       </c>
       <c r="C524" t="str">
-        <v>2026-07-30 15:57:45</v>
+        <v>2026-07-30 15:28:55</v>
       </c>
       <c r="D524" t="str">
         <v>NO</v>
@@ -7744,7 +7744,7 @@
         <v>6594</v>
       </c>
       <c r="C525" t="str">
-        <v>2026-07-30 16:11:17</v>
+        <v>2026-07-30 15:57:45</v>
       </c>
       <c r="D525" t="str">
         <v>NO</v>
@@ -7758,7 +7758,7 @@
         <v>6594</v>
       </c>
       <c r="C526" t="str">
-        <v>2026-07-30 16:36:40</v>
+        <v>2026-07-30 16:11:17</v>
       </c>
       <c r="D526" t="str">
         <v>NO</v>
@@ -7772,10 +7772,10 @@
         <v>6594</v>
       </c>
       <c r="C527" t="str">
-        <v>2026-07-30 22:46:03</v>
+        <v>2026-07-30 16:36:40</v>
       </c>
       <c r="D527" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="528">
@@ -7786,7 +7786,7 @@
         <v>6594</v>
       </c>
       <c r="C528" t="str">
-        <v>2026-07-30 23:18:28</v>
+        <v>2026-07-30 22:46:03</v>
       </c>
       <c r="D528" t="str">
         <v>SI</v>
@@ -7800,7 +7800,7 @@
         <v>6594</v>
       </c>
       <c r="C529" t="str">
-        <v>2026-07-30 23:18:45</v>
+        <v>2026-07-30 23:18:28</v>
       </c>
       <c r="D529" t="str">
         <v>SI</v>
@@ -7814,10 +7814,10 @@
         <v>6594</v>
       </c>
       <c r="C530" t="str">
-        <v>2026-07-31 15:17:56</v>
+        <v>2026-07-30 23:18:45</v>
       </c>
       <c r="D530" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="531">
@@ -7828,7 +7828,7 @@
         <v>6594</v>
       </c>
       <c r="C531" t="str">
-        <v>2026-07-31 16:20:16</v>
+        <v>2026-07-31 15:17:56</v>
       </c>
       <c r="D531" t="str">
         <v>NO</v>
@@ -7842,7 +7842,7 @@
         <v>6594</v>
       </c>
       <c r="C532" t="str">
-        <v>2026-07-31 16:34:12</v>
+        <v>2026-07-31 16:20:16</v>
       </c>
       <c r="D532" t="str">
         <v>NO</v>
@@ -7856,7 +7856,7 @@
         <v>6594</v>
       </c>
       <c r="C533" t="str">
-        <v>2026-07-31 16:42:58</v>
+        <v>2026-07-31 16:34:12</v>
       </c>
       <c r="D533" t="str">
         <v>NO</v>
@@ -7870,7 +7870,7 @@
         <v>6594</v>
       </c>
       <c r="C534" t="str">
-        <v>2026-07-31 17:37:12</v>
+        <v>2026-07-31 16:42:58</v>
       </c>
       <c r="D534" t="str">
         <v>NO</v>
@@ -7884,7 +7884,7 @@
         <v>6594</v>
       </c>
       <c r="C535" t="str">
-        <v>2026-07-31 18:29:12</v>
+        <v>2026-07-31 17:37:12</v>
       </c>
       <c r="D535" t="str">
         <v>NO</v>
@@ -7892,13 +7892,13 @@
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B536">
-        <v>6605</v>
+        <v>6594</v>
       </c>
       <c r="C536" t="str">
-        <v>2026-07-27 12:23:18</v>
+        <v>2026-07-31 18:29:12</v>
       </c>
       <c r="D536" t="str">
         <v>NO</v>
@@ -7912,7 +7912,7 @@
         <v>6605</v>
       </c>
       <c r="C537" t="str">
-        <v>2026-07-27 12:59:41</v>
+        <v>2026-07-27 12:23:18</v>
       </c>
       <c r="D537" t="str">
         <v>NO</v>
@@ -7926,7 +7926,7 @@
         <v>6605</v>
       </c>
       <c r="C538" t="str">
-        <v>2026-07-27 14:06:21</v>
+        <v>2026-07-27 12:59:41</v>
       </c>
       <c r="D538" t="str">
         <v>NO</v>
@@ -7940,7 +7940,7 @@
         <v>6605</v>
       </c>
       <c r="C539" t="str">
-        <v>2026-07-27 14:46:08</v>
+        <v>2026-07-27 14:06:21</v>
       </c>
       <c r="D539" t="str">
         <v>NO</v>
@@ -7954,7 +7954,7 @@
         <v>6605</v>
       </c>
       <c r="C540" t="str">
-        <v>2026-07-27 15:00:51</v>
+        <v>2026-07-27 14:46:08</v>
       </c>
       <c r="D540" t="str">
         <v>NO</v>
@@ -7968,7 +7968,7 @@
         <v>6605</v>
       </c>
       <c r="C541" t="str">
-        <v>2026-07-27 15:16:35</v>
+        <v>2026-07-27 15:00:51</v>
       </c>
       <c r="D541" t="str">
         <v>NO</v>
@@ -7982,7 +7982,7 @@
         <v>6605</v>
       </c>
       <c r="C542" t="str">
-        <v>2026-07-27 15:23:03</v>
+        <v>2026-07-27 15:16:35</v>
       </c>
       <c r="D542" t="str">
         <v>NO</v>
@@ -7996,7 +7996,7 @@
         <v>6605</v>
       </c>
       <c r="C543" t="str">
-        <v>2026-07-27 16:10:31</v>
+        <v>2026-07-27 15:23:03</v>
       </c>
       <c r="D543" t="str">
         <v>NO</v>
@@ -8010,7 +8010,7 @@
         <v>6605</v>
       </c>
       <c r="C544" t="str">
-        <v>2026-07-27 16:33:04</v>
+        <v>2026-07-27 16:10:31</v>
       </c>
       <c r="D544" t="str">
         <v>NO</v>
@@ -8024,7 +8024,7 @@
         <v>6605</v>
       </c>
       <c r="C545" t="str">
-        <v>2026-07-27 18:09:08</v>
+        <v>2026-07-27 16:33:04</v>
       </c>
       <c r="D545" t="str">
         <v>NO</v>
@@ -8038,7 +8038,7 @@
         <v>6605</v>
       </c>
       <c r="C546" t="str">
-        <v>2026-07-27 18:56:54</v>
+        <v>2026-07-27 18:09:08</v>
       </c>
       <c r="D546" t="str">
         <v>NO</v>
@@ -8052,7 +8052,7 @@
         <v>6605</v>
       </c>
       <c r="C547" t="str">
-        <v>2026-07-27 18:58:15</v>
+        <v>2026-07-27 18:56:54</v>
       </c>
       <c r="D547" t="str">
         <v>NO</v>
@@ -8066,10 +8066,10 @@
         <v>6605</v>
       </c>
       <c r="C548" t="str">
-        <v>2026-07-27 19:15:58</v>
+        <v>2026-07-27 18:58:15</v>
       </c>
       <c r="D548" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="549">
@@ -8080,7 +8080,7 @@
         <v>6605</v>
       </c>
       <c r="C549" t="str">
-        <v>2026-07-27 19:36:05</v>
+        <v>2026-07-27 19:15:58</v>
       </c>
       <c r="D549" t="str">
         <v>SI</v>
@@ -8094,7 +8094,7 @@
         <v>6605</v>
       </c>
       <c r="C550" t="str">
-        <v>2026-07-27 20:59:34</v>
+        <v>2026-07-27 19:36:05</v>
       </c>
       <c r="D550" t="str">
         <v>SI</v>
@@ -8108,7 +8108,7 @@
         <v>6605</v>
       </c>
       <c r="C551" t="str">
-        <v>2026-07-27 21:00:44</v>
+        <v>2026-07-27 20:59:34</v>
       </c>
       <c r="D551" t="str">
         <v>SI</v>
@@ -8122,7 +8122,7 @@
         <v>6605</v>
       </c>
       <c r="C552" t="str">
-        <v>2026-07-27 21:35:15</v>
+        <v>2026-07-27 21:00:44</v>
       </c>
       <c r="D552" t="str">
         <v>SI</v>
@@ -8136,10 +8136,10 @@
         <v>6605</v>
       </c>
       <c r="C553" t="str">
-        <v>2026-07-28 12:02:44</v>
+        <v>2026-07-27 21:35:15</v>
       </c>
       <c r="D553" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="554">
@@ -8150,7 +8150,7 @@
         <v>6605</v>
       </c>
       <c r="C554" t="str">
-        <v>2026-07-28 12:24:41</v>
+        <v>2026-07-28 12:02:44</v>
       </c>
       <c r="D554" t="str">
         <v>NO</v>
@@ -8164,7 +8164,7 @@
         <v>6605</v>
       </c>
       <c r="C555" t="str">
-        <v>2026-07-28 12:51:52</v>
+        <v>2026-07-28 12:24:41</v>
       </c>
       <c r="D555" t="str">
         <v>NO</v>
@@ -8178,7 +8178,7 @@
         <v>6605</v>
       </c>
       <c r="C556" t="str">
-        <v>2026-07-28 14:03:29</v>
+        <v>2026-07-28 12:51:52</v>
       </c>
       <c r="D556" t="str">
         <v>NO</v>
@@ -8192,7 +8192,7 @@
         <v>6605</v>
       </c>
       <c r="C557" t="str">
-        <v>2026-07-28 14:16:22</v>
+        <v>2026-07-28 14:03:29</v>
       </c>
       <c r="D557" t="str">
         <v>NO</v>
@@ -8206,7 +8206,7 @@
         <v>6605</v>
       </c>
       <c r="C558" t="str">
-        <v>2026-07-28 14:53:18</v>
+        <v>2026-07-28 14:16:22</v>
       </c>
       <c r="D558" t="str">
         <v>NO</v>
@@ -8220,7 +8220,7 @@
         <v>6605</v>
       </c>
       <c r="C559" t="str">
-        <v>2026-07-28 15:27:37</v>
+        <v>2026-07-28 14:53:18</v>
       </c>
       <c r="D559" t="str">
         <v>NO</v>
@@ -8234,7 +8234,7 @@
         <v>6605</v>
       </c>
       <c r="C560" t="str">
-        <v>2026-07-28 16:24:15</v>
+        <v>2026-07-28 15:27:37</v>
       </c>
       <c r="D560" t="str">
         <v>NO</v>
@@ -8248,7 +8248,7 @@
         <v>6605</v>
       </c>
       <c r="C561" t="str">
-        <v>2026-07-28 16:26:48</v>
+        <v>2026-07-28 16:24:15</v>
       </c>
       <c r="D561" t="str">
         <v>NO</v>
@@ -8262,7 +8262,7 @@
         <v>6605</v>
       </c>
       <c r="C562" t="str">
-        <v>2026-07-28 16:49:26</v>
+        <v>2026-07-28 16:26:48</v>
       </c>
       <c r="D562" t="str">
         <v>NO</v>
@@ -8276,7 +8276,7 @@
         <v>6605</v>
       </c>
       <c r="C563" t="str">
-        <v>2026-07-28 17:08:36</v>
+        <v>2026-07-28 16:49:26</v>
       </c>
       <c r="D563" t="str">
         <v>NO</v>
@@ -8290,7 +8290,7 @@
         <v>6605</v>
       </c>
       <c r="C564" t="str">
-        <v>2026-07-28 17:31:22</v>
+        <v>2026-07-28 17:08:36</v>
       </c>
       <c r="D564" t="str">
         <v>NO</v>
@@ -8304,7 +8304,7 @@
         <v>6605</v>
       </c>
       <c r="C565" t="str">
-        <v>2026-07-28 17:59:58</v>
+        <v>2026-07-28 17:31:22</v>
       </c>
       <c r="D565" t="str">
         <v>NO</v>
@@ -8318,10 +8318,10 @@
         <v>6605</v>
       </c>
       <c r="C566" t="str">
-        <v>2026-07-28 20:24:56</v>
+        <v>2026-07-28 17:59:58</v>
       </c>
       <c r="D566" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="567">
@@ -8332,7 +8332,7 @@
         <v>6605</v>
       </c>
       <c r="C567" t="str">
-        <v>2026-07-28 20:55:33</v>
+        <v>2026-07-28 20:24:56</v>
       </c>
       <c r="D567" t="str">
         <v>SI</v>
@@ -8346,7 +8346,7 @@
         <v>6605</v>
       </c>
       <c r="C568" t="str">
-        <v>2026-07-28 21:34:07</v>
+        <v>2026-07-28 20:55:33</v>
       </c>
       <c r="D568" t="str">
         <v>SI</v>
@@ -8360,10 +8360,10 @@
         <v>6605</v>
       </c>
       <c r="C569" t="str">
-        <v>2026-07-29 12:03:36</v>
+        <v>2026-07-28 21:34:07</v>
       </c>
       <c r="D569" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="570">
@@ -8374,7 +8374,7 @@
         <v>6605</v>
       </c>
       <c r="C570" t="str">
-        <v>2026-07-29 12:48:43</v>
+        <v>2026-07-29 12:03:36</v>
       </c>
       <c r="D570" t="str">
         <v>NO</v>
@@ -8388,7 +8388,7 @@
         <v>6605</v>
       </c>
       <c r="C571" t="str">
-        <v>2026-07-29 18:00:08</v>
+        <v>2026-07-29 12:48:43</v>
       </c>
       <c r="D571" t="str">
         <v>NO</v>
@@ -8402,7 +8402,7 @@
         <v>6605</v>
       </c>
       <c r="C572" t="str">
-        <v>2026-07-29 18:47:55</v>
+        <v>2026-07-29 18:00:08</v>
       </c>
       <c r="D572" t="str">
         <v>NO</v>
@@ -8416,10 +8416,10 @@
         <v>6605</v>
       </c>
       <c r="C573" t="str">
-        <v>2026-07-29 20:07:38</v>
+        <v>2026-07-29 18:47:55</v>
       </c>
       <c r="D573" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="574">
@@ -8430,7 +8430,7 @@
         <v>6605</v>
       </c>
       <c r="C574" t="str">
-        <v>2026-07-29 20:12:08</v>
+        <v>2026-07-29 20:07:38</v>
       </c>
       <c r="D574" t="str">
         <v>SI</v>
@@ -8444,7 +8444,7 @@
         <v>6605</v>
       </c>
       <c r="C575" t="str">
-        <v>2026-07-29 20:12:39</v>
+        <v>2026-07-29 20:12:08</v>
       </c>
       <c r="D575" t="str">
         <v>SI</v>
@@ -8458,7 +8458,7 @@
         <v>6605</v>
       </c>
       <c r="C576" t="str">
-        <v>2026-07-29 20:13:46</v>
+        <v>2026-07-29 20:12:39</v>
       </c>
       <c r="D576" t="str">
         <v>SI</v>
@@ -8472,7 +8472,7 @@
         <v>6605</v>
       </c>
       <c r="C577" t="str">
-        <v>2026-07-29 20:44:12</v>
+        <v>2026-07-29 20:13:46</v>
       </c>
       <c r="D577" t="str">
         <v>SI</v>
@@ -8486,10 +8486,10 @@
         <v>6605</v>
       </c>
       <c r="C578" t="str">
-        <v>2026-07-30 12:00:52</v>
+        <v>2026-07-29 20:44:12</v>
       </c>
       <c r="D578" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="579">
@@ -8500,7 +8500,7 @@
         <v>6605</v>
       </c>
       <c r="C579" t="str">
-        <v>2026-07-30 16:58:42</v>
+        <v>2026-07-30 12:00:52</v>
       </c>
       <c r="D579" t="str">
         <v>NO</v>
@@ -8514,7 +8514,7 @@
         <v>6605</v>
       </c>
       <c r="C580" t="str">
-        <v>2026-07-30 17:28:04</v>
+        <v>2026-07-30 16:58:42</v>
       </c>
       <c r="D580" t="str">
         <v>NO</v>
@@ -8528,10 +8528,10 @@
         <v>6605</v>
       </c>
       <c r="C581" t="str">
-        <v>2026-07-30 19:43:02</v>
+        <v>2026-07-30 17:28:04</v>
       </c>
       <c r="D581" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="582">
@@ -8542,7 +8542,7 @@
         <v>6605</v>
       </c>
       <c r="C582" t="str">
-        <v>2026-07-30 20:11:55</v>
+        <v>2026-07-30 19:43:02</v>
       </c>
       <c r="D582" t="str">
         <v>SI</v>
@@ -8556,7 +8556,7 @@
         <v>6605</v>
       </c>
       <c r="C583" t="str">
-        <v>2026-07-30 20:18:27</v>
+        <v>2026-07-30 20:11:55</v>
       </c>
       <c r="D583" t="str">
         <v>SI</v>
@@ -8570,7 +8570,7 @@
         <v>6605</v>
       </c>
       <c r="C584" t="str">
-        <v>2026-07-30 20:22:29</v>
+        <v>2026-07-30 20:18:27</v>
       </c>
       <c r="D584" t="str">
         <v>SI</v>
@@ -8584,10 +8584,10 @@
         <v>6605</v>
       </c>
       <c r="C585" t="str">
-        <v>2026-07-31 12:33:45</v>
+        <v>2026-07-30 20:22:29</v>
       </c>
       <c r="D585" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="586">
@@ -8598,7 +8598,7 @@
         <v>6605</v>
       </c>
       <c r="C586" t="str">
-        <v>2026-07-31 13:20:10</v>
+        <v>2026-07-31 12:33:45</v>
       </c>
       <c r="D586" t="str">
         <v>NO</v>
@@ -8612,7 +8612,7 @@
         <v>6605</v>
       </c>
       <c r="C587" t="str">
-        <v>2026-07-31 14:29:30</v>
+        <v>2026-07-31 13:20:10</v>
       </c>
       <c r="D587" t="str">
         <v>NO</v>
@@ -8626,7 +8626,7 @@
         <v>6605</v>
       </c>
       <c r="C588" t="str">
-        <v>2026-07-31 15:16:54</v>
+        <v>2026-07-31 14:29:30</v>
       </c>
       <c r="D588" t="str">
         <v>NO</v>
@@ -8640,7 +8640,7 @@
         <v>6605</v>
       </c>
       <c r="C589" t="str">
-        <v>2026-07-31 15:22:22</v>
+        <v>2026-07-31 15:16:54</v>
       </c>
       <c r="D589" t="str">
         <v>NO</v>
@@ -8654,7 +8654,7 @@
         <v>6605</v>
       </c>
       <c r="C590" t="str">
-        <v>2026-07-31 18:14:33</v>
+        <v>2026-07-31 15:22:22</v>
       </c>
       <c r="D590" t="str">
         <v>NO</v>
@@ -8668,10 +8668,10 @@
         <v>6605</v>
       </c>
       <c r="C591" t="str">
-        <v>2026-07-31 19:00:03</v>
+        <v>2026-07-31 18:14:33</v>
       </c>
       <c r="D591" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="592">
@@ -8682,7 +8682,7 @@
         <v>6605</v>
       </c>
       <c r="C592" t="str">
-        <v>2026-07-31 19:21:29</v>
+        <v>2026-07-31 19:00:03</v>
       </c>
       <c r="D592" t="str">
         <v>SI</v>
@@ -8696,7 +8696,7 @@
         <v>6605</v>
       </c>
       <c r="C593" t="str">
-        <v>2026-07-31 19:55:38</v>
+        <v>2026-07-31 19:21:29</v>
       </c>
       <c r="D593" t="str">
         <v>SI</v>
@@ -8710,7 +8710,7 @@
         <v>6605</v>
       </c>
       <c r="C594" t="str">
-        <v>2026-07-31 20:40:58</v>
+        <v>2026-07-31 19:55:38</v>
       </c>
       <c r="D594" t="str">
         <v>SI</v>
@@ -8724,7 +8724,7 @@
         <v>6605</v>
       </c>
       <c r="C595" t="str">
-        <v>2026-07-31 20:53:44</v>
+        <v>2026-07-31 20:40:58</v>
       </c>
       <c r="D595" t="str">
         <v>SI</v>
@@ -8732,16 +8732,16 @@
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B596">
-        <v>6603</v>
+        <v>6605</v>
       </c>
       <c r="C596" t="str">
-        <v>2026-07-27 13:26:44</v>
+        <v>2026-07-31 20:53:44</v>
       </c>
       <c r="D596" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="597">
@@ -8752,7 +8752,7 @@
         <v>6603</v>
       </c>
       <c r="C597" t="str">
-        <v>2026-07-27 15:18:37</v>
+        <v>2026-07-27 13:26:44</v>
       </c>
       <c r="D597" t="str">
         <v>NO</v>
@@ -8766,7 +8766,7 @@
         <v>6603</v>
       </c>
       <c r="C598" t="str">
-        <v>2026-07-27 16:02:05</v>
+        <v>2026-07-27 15:18:37</v>
       </c>
       <c r="D598" t="str">
         <v>NO</v>
@@ -8780,7 +8780,7 @@
         <v>6603</v>
       </c>
       <c r="C599" t="str">
-        <v>2026-07-27 16:31:36</v>
+        <v>2026-07-27 16:02:05</v>
       </c>
       <c r="D599" t="str">
         <v>NO</v>
@@ -8794,10 +8794,10 @@
         <v>6603</v>
       </c>
       <c r="C600" t="str">
-        <v>2026-07-27 21:54:00</v>
+        <v>2026-07-27 16:31:36</v>
       </c>
       <c r="D600" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="601">
@@ -8808,7 +8808,7 @@
         <v>6603</v>
       </c>
       <c r="C601" t="str">
-        <v>2026-07-27 22:07:22</v>
+        <v>2026-07-27 21:54:00</v>
       </c>
       <c r="D601" t="str">
         <v>SI</v>
@@ -8822,10 +8822,10 @@
         <v>6603</v>
       </c>
       <c r="C602" t="str">
-        <v>2026-07-28 12:33:13</v>
+        <v>2026-07-27 22:07:22</v>
       </c>
       <c r="D602" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="603">
@@ -8836,10 +8836,10 @@
         <v>6603</v>
       </c>
       <c r="C603" t="str">
-        <v>2026-07-28 20:31:27</v>
+        <v>2026-07-28 12:33:13</v>
       </c>
       <c r="D603" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="604">
@@ -8850,7 +8850,7 @@
         <v>6603</v>
       </c>
       <c r="C604" t="str">
-        <v>2026-07-28 21:35:11</v>
+        <v>2026-07-28 20:31:27</v>
       </c>
       <c r="D604" t="str">
         <v>SI</v>
@@ -8864,7 +8864,7 @@
         <v>6603</v>
       </c>
       <c r="C605" t="str">
-        <v>2026-07-28 22:54:44</v>
+        <v>2026-07-28 21:35:11</v>
       </c>
       <c r="D605" t="str">
         <v>SI</v>
@@ -8878,10 +8878,10 @@
         <v>6603</v>
       </c>
       <c r="C606" t="str">
-        <v>2026-07-29 11:11:16</v>
+        <v>2026-07-28 22:54:44</v>
       </c>
       <c r="D606" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="607">
@@ -8892,7 +8892,7 @@
         <v>6603</v>
       </c>
       <c r="C607" t="str">
-        <v>2026-07-29 13:54:29</v>
+        <v>2026-07-29 11:11:16</v>
       </c>
       <c r="D607" t="str">
         <v>NO</v>
@@ -8906,7 +8906,7 @@
         <v>6603</v>
       </c>
       <c r="C608" t="str">
-        <v>2026-07-29 14:15:19</v>
+        <v>2026-07-29 13:54:29</v>
       </c>
       <c r="D608" t="str">
         <v>NO</v>
@@ -8920,7 +8920,7 @@
         <v>6603</v>
       </c>
       <c r="C609" t="str">
-        <v>2026-07-29 17:31:23</v>
+        <v>2026-07-29 14:15:19</v>
       </c>
       <c r="D609" t="str">
         <v>NO</v>
@@ -8934,10 +8934,10 @@
         <v>6603</v>
       </c>
       <c r="C610" t="str">
-        <v>2026-07-29 20:31:06</v>
+        <v>2026-07-29 17:31:23</v>
       </c>
       <c r="D610" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="611">
@@ -8948,7 +8948,7 @@
         <v>6603</v>
       </c>
       <c r="C611" t="str">
-        <v>2026-07-29 20:47:12</v>
+        <v>2026-07-29 20:31:06</v>
       </c>
       <c r="D611" t="str">
         <v>SI</v>
@@ -8962,7 +8962,7 @@
         <v>6603</v>
       </c>
       <c r="C612" t="str">
-        <v>2026-07-29 20:48:38</v>
+        <v>2026-07-29 20:47:12</v>
       </c>
       <c r="D612" t="str">
         <v>SI</v>
@@ -8976,7 +8976,7 @@
         <v>6603</v>
       </c>
       <c r="C613" t="str">
-        <v>2026-07-29 21:10:58</v>
+        <v>2026-07-29 20:48:38</v>
       </c>
       <c r="D613" t="str">
         <v>SI</v>
@@ -8990,10 +8990,10 @@
         <v>6603</v>
       </c>
       <c r="C614" t="str">
-        <v>2026-07-30 12:08:29</v>
+        <v>2026-07-29 21:10:58</v>
       </c>
       <c r="D614" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="615">
@@ -9004,7 +9004,7 @@
         <v>6603</v>
       </c>
       <c r="C615" t="str">
-        <v>2026-07-30 13:52:22</v>
+        <v>2026-07-30 12:08:29</v>
       </c>
       <c r="D615" t="str">
         <v>NO</v>
@@ -9018,7 +9018,7 @@
         <v>6603</v>
       </c>
       <c r="C616" t="str">
-        <v>2026-07-30 15:14:08</v>
+        <v>2026-07-30 13:52:22</v>
       </c>
       <c r="D616" t="str">
         <v>NO</v>
@@ -9032,7 +9032,7 @@
         <v>6603</v>
       </c>
       <c r="C617" t="str">
-        <v>2026-07-30 17:11:48</v>
+        <v>2026-07-30 15:14:08</v>
       </c>
       <c r="D617" t="str">
         <v>NO</v>
@@ -9046,7 +9046,7 @@
         <v>6603</v>
       </c>
       <c r="C618" t="str">
-        <v>2026-07-30 17:49:33</v>
+        <v>2026-07-30 17:11:48</v>
       </c>
       <c r="D618" t="str">
         <v>NO</v>
@@ -9060,10 +9060,10 @@
         <v>6603</v>
       </c>
       <c r="C619" t="str">
-        <v>2026-07-30 20:46:24</v>
+        <v>2026-07-30 17:49:33</v>
       </c>
       <c r="D619" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="620">
@@ -9074,7 +9074,7 @@
         <v>6603</v>
       </c>
       <c r="C620" t="str">
-        <v>2026-07-30 21:15:15</v>
+        <v>2026-07-30 20:46:24</v>
       </c>
       <c r="D620" t="str">
         <v>SI</v>
@@ -9088,10 +9088,10 @@
         <v>6603</v>
       </c>
       <c r="C621" t="str">
-        <v>2026-07-31 10:56:47</v>
+        <v>2026-07-30 21:15:15</v>
       </c>
       <c r="D621" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="622">
@@ -9102,7 +9102,7 @@
         <v>6603</v>
       </c>
       <c r="C622" t="str">
-        <v>2026-07-31 15:00:45</v>
+        <v>2026-07-31 10:56:47</v>
       </c>
       <c r="D622" t="str">
         <v>NO</v>
@@ -9116,7 +9116,7 @@
         <v>6603</v>
       </c>
       <c r="C623" t="str">
-        <v>2026-07-31 15:14:21</v>
+        <v>2026-07-31 15:00:45</v>
       </c>
       <c r="D623" t="str">
         <v>NO</v>
@@ -9130,10 +9130,10 @@
         <v>6603</v>
       </c>
       <c r="C624" t="str">
-        <v>2026-07-31 20:25:59</v>
+        <v>2026-07-31 15:14:21</v>
       </c>
       <c r="D624" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="625">
@@ -9144,7 +9144,7 @@
         <v>6603</v>
       </c>
       <c r="C625" t="str">
-        <v>2026-07-31 21:33:43</v>
+        <v>2026-07-31 20:25:59</v>
       </c>
       <c r="D625" t="str">
         <v>SI</v>
@@ -9152,16 +9152,16 @@
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B626">
-        <v>6607</v>
+        <v>6603</v>
       </c>
       <c r="C626" t="str">
-        <v>2026-07-27 10:15:18</v>
+        <v>2026-07-31 21:33:43</v>
       </c>
       <c r="D626" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="627">
@@ -9172,7 +9172,7 @@
         <v>6607</v>
       </c>
       <c r="C627" t="str">
-        <v>2026-07-27 12:40:57</v>
+        <v>2026-07-27 10:15:18</v>
       </c>
       <c r="D627" t="str">
         <v>NO</v>
@@ -9186,7 +9186,7 @@
         <v>6607</v>
       </c>
       <c r="C628" t="str">
-        <v>2026-07-27 13:32:29</v>
+        <v>2026-07-27 12:40:57</v>
       </c>
       <c r="D628" t="str">
         <v>NO</v>
@@ -9200,7 +9200,7 @@
         <v>6607</v>
       </c>
       <c r="C629" t="str">
-        <v>2026-07-27 14:12:37</v>
+        <v>2026-07-27 13:32:29</v>
       </c>
       <c r="D629" t="str">
         <v>NO</v>
@@ -9214,10 +9214,10 @@
         <v>6607</v>
       </c>
       <c r="C630" t="str">
-        <v>2026-07-27 21:11:55</v>
+        <v>2026-07-27 14:12:37</v>
       </c>
       <c r="D630" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="631">
@@ -9228,7 +9228,7 @@
         <v>6607</v>
       </c>
       <c r="C631" t="str">
-        <v>2026-07-27 22:11:20</v>
+        <v>2026-07-27 21:11:55</v>
       </c>
       <c r="D631" t="str">
         <v>SI</v>
@@ -9242,7 +9242,7 @@
         <v>6607</v>
       </c>
       <c r="C632" t="str">
-        <v>2026-07-27 22:25:56</v>
+        <v>2026-07-27 22:11:20</v>
       </c>
       <c r="D632" t="str">
         <v>SI</v>
@@ -9256,7 +9256,7 @@
         <v>6607</v>
       </c>
       <c r="C633" t="str">
-        <v>2026-07-27 22:47:36</v>
+        <v>2026-07-27 22:25:56</v>
       </c>
       <c r="D633" t="str">
         <v>SI</v>
@@ -9270,7 +9270,7 @@
         <v>6607</v>
       </c>
       <c r="C634" t="str">
-        <v>2026-07-27 22:57:02</v>
+        <v>2026-07-27 22:47:36</v>
       </c>
       <c r="D634" t="str">
         <v>SI</v>
@@ -9284,7 +9284,7 @@
         <v>6607</v>
       </c>
       <c r="C635" t="str">
-        <v>2026-07-27 23:14:58</v>
+        <v>2026-07-27 22:57:02</v>
       </c>
       <c r="D635" t="str">
         <v>SI</v>
@@ -9298,7 +9298,7 @@
         <v>6607</v>
       </c>
       <c r="C636" t="str">
-        <v>2026-07-27 23:16:48</v>
+        <v>2026-07-27 23:14:58</v>
       </c>
       <c r="D636" t="str">
         <v>SI</v>
@@ -9312,7 +9312,7 @@
         <v>6607</v>
       </c>
       <c r="C637" t="str">
-        <v>2026-07-27 23:58:16</v>
+        <v>2026-07-27 23:16:48</v>
       </c>
       <c r="D637" t="str">
         <v>SI</v>
@@ -9326,10 +9326,10 @@
         <v>6607</v>
       </c>
       <c r="C638" t="str">
-        <v>2026-07-28 10:32:48</v>
+        <v>2026-07-27 23:58:16</v>
       </c>
       <c r="D638" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="639">
@@ -9340,7 +9340,7 @@
         <v>6607</v>
       </c>
       <c r="C639" t="str">
-        <v>2026-07-28 12:03:40</v>
+        <v>2026-07-28 10:32:48</v>
       </c>
       <c r="D639" t="str">
         <v>NO</v>
@@ -9354,7 +9354,7 @@
         <v>6607</v>
       </c>
       <c r="C640" t="str">
-        <v>2026-07-28 12:51:12</v>
+        <v>2026-07-28 12:03:40</v>
       </c>
       <c r="D640" t="str">
         <v>NO</v>
@@ -9368,7 +9368,7 @@
         <v>6607</v>
       </c>
       <c r="C641" t="str">
-        <v>2026-07-28 13:32:34</v>
+        <v>2026-07-28 12:51:12</v>
       </c>
       <c r="D641" t="str">
         <v>NO</v>
@@ -9382,10 +9382,10 @@
         <v>6607</v>
       </c>
       <c r="C642" t="str">
-        <v>2026-07-28 21:27:56</v>
+        <v>2026-07-28 13:32:34</v>
       </c>
       <c r="D642" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="643">
@@ -9396,7 +9396,7 @@
         <v>6607</v>
       </c>
       <c r="C643" t="str">
-        <v>2026-07-28 22:19:35</v>
+        <v>2026-07-28 21:27:56</v>
       </c>
       <c r="D643" t="str">
         <v>SI</v>
@@ -9410,7 +9410,7 @@
         <v>6607</v>
       </c>
       <c r="C644" t="str">
-        <v>2026-07-28 22:29:10</v>
+        <v>2026-07-28 22:19:35</v>
       </c>
       <c r="D644" t="str">
         <v>SI</v>
@@ -9424,7 +9424,7 @@
         <v>6607</v>
       </c>
       <c r="C645" t="str">
-        <v>2026-07-28 22:43:42</v>
+        <v>2026-07-28 22:29:10</v>
       </c>
       <c r="D645" t="str">
         <v>SI</v>
@@ -9438,7 +9438,7 @@
         <v>6607</v>
       </c>
       <c r="C646" t="str">
-        <v>2026-07-28 23:06:44</v>
+        <v>2026-07-28 22:43:42</v>
       </c>
       <c r="D646" t="str">
         <v>SI</v>
@@ -9452,7 +9452,7 @@
         <v>6607</v>
       </c>
       <c r="C647" t="str">
-        <v>2026-07-28 23:09:44</v>
+        <v>2026-07-28 23:06:44</v>
       </c>
       <c r="D647" t="str">
         <v>SI</v>
@@ -9466,7 +9466,7 @@
         <v>6607</v>
       </c>
       <c r="C648" t="str">
-        <v>2026-07-28 23:55:28</v>
+        <v>2026-07-28 23:09:44</v>
       </c>
       <c r="D648" t="str">
         <v>SI</v>
@@ -9480,7 +9480,7 @@
         <v>6607</v>
       </c>
       <c r="C649" t="str">
-        <v>2026-07-28 23:56:00</v>
+        <v>2026-07-28 23:55:28</v>
       </c>
       <c r="D649" t="str">
         <v>SI</v>
@@ -9494,10 +9494,10 @@
         <v>6607</v>
       </c>
       <c r="C650" t="str">
-        <v>2026-07-29 10:34:32</v>
+        <v>2026-07-28 23:56:00</v>
       </c>
       <c r="D650" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="651">
@@ -9508,7 +9508,7 @@
         <v>6607</v>
       </c>
       <c r="C651" t="str">
-        <v>2026-07-29 11:54:06</v>
+        <v>2026-07-29 10:34:32</v>
       </c>
       <c r="D651" t="str">
         <v>NO</v>
@@ -9522,7 +9522,7 @@
         <v>6607</v>
       </c>
       <c r="C652" t="str">
-        <v>2026-07-29 12:48:04</v>
+        <v>2026-07-29 11:54:06</v>
       </c>
       <c r="D652" t="str">
         <v>NO</v>
@@ -9536,7 +9536,7 @@
         <v>6607</v>
       </c>
       <c r="C653" t="str">
-        <v>2026-07-29 13:34:33</v>
+        <v>2026-07-29 12:48:04</v>
       </c>
       <c r="D653" t="str">
         <v>NO</v>
@@ -9550,10 +9550,10 @@
         <v>6607</v>
       </c>
       <c r="C654" t="str">
-        <v>2026-07-29 21:09:21</v>
+        <v>2026-07-29 13:34:33</v>
       </c>
       <c r="D654" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="655">
@@ -9564,7 +9564,7 @@
         <v>6607</v>
       </c>
       <c r="C655" t="str">
-        <v>2026-07-29 22:00:56</v>
+        <v>2026-07-29 21:09:21</v>
       </c>
       <c r="D655" t="str">
         <v>SI</v>
@@ -9578,7 +9578,7 @@
         <v>6607</v>
       </c>
       <c r="C656" t="str">
-        <v>2026-07-29 22:06:24</v>
+        <v>2026-07-29 22:00:56</v>
       </c>
       <c r="D656" t="str">
         <v>SI</v>
@@ -9592,7 +9592,7 @@
         <v>6607</v>
       </c>
       <c r="C657" t="str">
-        <v>2026-07-29 22:23:29</v>
+        <v>2026-07-29 22:06:24</v>
       </c>
       <c r="D657" t="str">
         <v>SI</v>
@@ -9606,7 +9606,7 @@
         <v>6607</v>
       </c>
       <c r="C658" t="str">
-        <v>2026-07-29 22:31:09</v>
+        <v>2026-07-29 22:23:29</v>
       </c>
       <c r="D658" t="str">
         <v>SI</v>
@@ -9620,7 +9620,7 @@
         <v>6607</v>
       </c>
       <c r="C659" t="str">
-        <v>2026-07-29 22:40:01</v>
+        <v>2026-07-29 22:31:09</v>
       </c>
       <c r="D659" t="str">
         <v>SI</v>
@@ -9634,7 +9634,7 @@
         <v>6607</v>
       </c>
       <c r="C660" t="str">
-        <v>2026-07-30 01:11:17</v>
+        <v>2026-07-29 22:40:01</v>
       </c>
       <c r="D660" t="str">
         <v>SI</v>
@@ -9648,7 +9648,7 @@
         <v>6607</v>
       </c>
       <c r="C661" t="str">
-        <v>2026-07-30 01:13:47</v>
+        <v>2026-07-30 01:11:17</v>
       </c>
       <c r="D661" t="str">
         <v>SI</v>
@@ -9662,10 +9662,10 @@
         <v>6607</v>
       </c>
       <c r="C662" t="str">
-        <v>2026-07-30 10:26:30</v>
+        <v>2026-07-30 01:13:47</v>
       </c>
       <c r="D662" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="663">
@@ -9676,7 +9676,7 @@
         <v>6607</v>
       </c>
       <c r="C663" t="str">
-        <v>2026-07-30 11:52:10</v>
+        <v>2026-07-30 10:26:30</v>
       </c>
       <c r="D663" t="str">
         <v>NO</v>
@@ -9690,7 +9690,7 @@
         <v>6607</v>
       </c>
       <c r="C664" t="str">
-        <v>2026-07-30 12:57:02</v>
+        <v>2026-07-30 11:52:10</v>
       </c>
       <c r="D664" t="str">
         <v>NO</v>
@@ -9704,7 +9704,7 @@
         <v>6607</v>
       </c>
       <c r="C665" t="str">
-        <v>2026-07-30 13:26:22</v>
+        <v>2026-07-30 12:57:02</v>
       </c>
       <c r="D665" t="str">
         <v>NO</v>
@@ -9718,7 +9718,7 @@
         <v>6607</v>
       </c>
       <c r="C666" t="str">
-        <v>2026-07-30 13:47:30</v>
+        <v>2026-07-30 13:26:22</v>
       </c>
       <c r="D666" t="str">
         <v>NO</v>
@@ -9732,7 +9732,7 @@
         <v>6607</v>
       </c>
       <c r="C667" t="str">
-        <v>2026-07-30 13:53:56</v>
+        <v>2026-07-30 13:47:30</v>
       </c>
       <c r="D667" t="str">
         <v>NO</v>
@@ -9746,7 +9746,7 @@
         <v>6607</v>
       </c>
       <c r="C668" t="str">
-        <v>2026-07-30 14:23:32</v>
+        <v>2026-07-30 13:53:56</v>
       </c>
       <c r="D668" t="str">
         <v>NO</v>
@@ -9760,10 +9760,10 @@
         <v>6607</v>
       </c>
       <c r="C669" t="str">
-        <v>2026-07-30 21:02:29</v>
+        <v>2026-07-30 14:23:32</v>
       </c>
       <c r="D669" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="670">
@@ -9774,7 +9774,7 @@
         <v>6607</v>
       </c>
       <c r="C670" t="str">
-        <v>2026-07-30 22:10:21</v>
+        <v>2026-07-30 21:02:29</v>
       </c>
       <c r="D670" t="str">
         <v>SI</v>
@@ -9788,7 +9788,7 @@
         <v>6607</v>
       </c>
       <c r="C671" t="str">
-        <v>2026-07-30 22:16:49</v>
+        <v>2026-07-30 22:10:21</v>
       </c>
       <c r="D671" t="str">
         <v>SI</v>
@@ -9802,7 +9802,7 @@
         <v>6607</v>
       </c>
       <c r="C672" t="str">
-        <v>2026-07-30 22:26:33</v>
+        <v>2026-07-30 22:16:49</v>
       </c>
       <c r="D672" t="str">
         <v>SI</v>
@@ -9816,7 +9816,7 @@
         <v>6607</v>
       </c>
       <c r="C673" t="str">
-        <v>2026-07-30 22:42:57</v>
+        <v>2026-07-30 22:26:33</v>
       </c>
       <c r="D673" t="str">
         <v>SI</v>
@@ -9830,7 +9830,7 @@
         <v>6607</v>
       </c>
       <c r="C674" t="str">
-        <v>2026-07-31 01:07:35</v>
+        <v>2026-07-30 22:42:57</v>
       </c>
       <c r="D674" t="str">
         <v>SI</v>
@@ -9844,7 +9844,7 @@
         <v>6607</v>
       </c>
       <c r="C675" t="str">
-        <v>2026-07-31 01:13:06</v>
+        <v>2026-07-31 01:07:35</v>
       </c>
       <c r="D675" t="str">
         <v>SI</v>
@@ -9858,7 +9858,7 @@
         <v>6607</v>
       </c>
       <c r="C676" t="str">
-        <v>2026-07-31 01:26:32</v>
+        <v>2026-07-31 01:13:06</v>
       </c>
       <c r="D676" t="str">
         <v>SI</v>
@@ -9872,7 +9872,7 @@
         <v>6607</v>
       </c>
       <c r="C677" t="str">
-        <v>2026-07-31 01:29:58</v>
+        <v>2026-07-31 01:26:32</v>
       </c>
       <c r="D677" t="str">
         <v>SI</v>
@@ -9886,10 +9886,10 @@
         <v>6607</v>
       </c>
       <c r="C678" t="str">
-        <v>2026-07-31 10:26:33</v>
+        <v>2026-07-31 01:29:58</v>
       </c>
       <c r="D678" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="679">
@@ -9900,7 +9900,7 @@
         <v>6607</v>
       </c>
       <c r="C679" t="str">
-        <v>2026-07-31 12:04:40</v>
+        <v>2026-07-31 10:26:33</v>
       </c>
       <c r="D679" t="str">
         <v>NO</v>
@@ -9914,7 +9914,7 @@
         <v>6607</v>
       </c>
       <c r="C680" t="str">
-        <v>2026-07-31 12:53:57</v>
+        <v>2026-07-31 12:04:40</v>
       </c>
       <c r="D680" t="str">
         <v>NO</v>
@@ -9928,7 +9928,7 @@
         <v>6607</v>
       </c>
       <c r="C681" t="str">
-        <v>2026-07-31 13:03:36</v>
+        <v>2026-07-31 12:53:57</v>
       </c>
       <c r="D681" t="str">
         <v>NO</v>
@@ -9942,7 +9942,7 @@
         <v>6607</v>
       </c>
       <c r="C682" t="str">
-        <v>2026-07-31 13:11:30</v>
+        <v>2026-07-31 13:03:36</v>
       </c>
       <c r="D682" t="str">
         <v>NO</v>
@@ -9956,7 +9956,7 @@
         <v>6607</v>
       </c>
       <c r="C683" t="str">
-        <v>2026-07-31 13:51:37</v>
+        <v>2026-07-31 13:11:30</v>
       </c>
       <c r="D683" t="str">
         <v>NO</v>
@@ -9970,10 +9970,10 @@
         <v>6607</v>
       </c>
       <c r="C684" t="str">
-        <v>2026-07-31 20:44:34</v>
+        <v>2026-07-31 13:51:37</v>
       </c>
       <c r="D684" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="685">
@@ -9984,7 +9984,7 @@
         <v>6607</v>
       </c>
       <c r="C685" t="str">
-        <v>2026-07-31 20:55:13</v>
+        <v>2026-07-31 20:44:34</v>
       </c>
       <c r="D685" t="str">
         <v>SI</v>
@@ -9998,7 +9998,7 @@
         <v>6607</v>
       </c>
       <c r="C686" t="str">
-        <v>2026-07-31 22:19:08</v>
+        <v>2026-07-31 20:55:13</v>
       </c>
       <c r="D686" t="str">
         <v>SI</v>
@@ -10012,7 +10012,7 @@
         <v>6607</v>
       </c>
       <c r="C687" t="str">
-        <v>2026-07-31 22:27:10</v>
+        <v>2026-07-31 22:19:08</v>
       </c>
       <c r="D687" t="str">
         <v>SI</v>
@@ -10026,7 +10026,7 @@
         <v>6607</v>
       </c>
       <c r="C688" t="str">
-        <v>2026-07-31 22:36:00</v>
+        <v>2026-07-31 22:27:10</v>
       </c>
       <c r="D688" t="str">
         <v>SI</v>
@@ -10040,7 +10040,7 @@
         <v>6607</v>
       </c>
       <c r="C689" t="str">
-        <v>2026-08-02 20:53:54</v>
+        <v>2026-07-31 22:36:00</v>
       </c>
       <c r="D689" t="str">
         <v>SI</v>
@@ -10054,7 +10054,7 @@
         <v>6607</v>
       </c>
       <c r="C690" t="str">
-        <v>2026-08-02 21:33:19</v>
+        <v>2026-08-02 20:53:54</v>
       </c>
       <c r="D690" t="str">
         <v>SI</v>
@@ -10068,7 +10068,7 @@
         <v>6607</v>
       </c>
       <c r="C691" t="str">
-        <v>2026-08-02 22:04:48</v>
+        <v>2026-08-02 21:33:19</v>
       </c>
       <c r="D691" t="str">
         <v>SI</v>
@@ -10076,16 +10076,16 @@
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B692">
-        <v>6602</v>
+        <v>6607</v>
       </c>
       <c r="C692" t="str">
-        <v>2026-07-27 10:53:20</v>
+        <v>2026-08-02 22:04:48</v>
       </c>
       <c r="D692" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="693">
@@ -10096,7 +10096,7 @@
         <v>6602</v>
       </c>
       <c r="C693" t="str">
-        <v>2026-07-27 16:47:17</v>
+        <v>2026-07-27 10:53:20</v>
       </c>
       <c r="D693" t="str">
         <v>NO</v>
@@ -10110,7 +10110,7 @@
         <v>6602</v>
       </c>
       <c r="C694" t="str">
-        <v>2026-07-27 17:12:38</v>
+        <v>2026-07-27 16:47:17</v>
       </c>
       <c r="D694" t="str">
         <v>NO</v>
@@ -10124,7 +10124,7 @@
         <v>6602</v>
       </c>
       <c r="C695" t="str">
-        <v>2026-07-27 17:33:58</v>
+        <v>2026-07-27 17:12:38</v>
       </c>
       <c r="D695" t="str">
         <v>NO</v>
@@ -10138,7 +10138,7 @@
         <v>6602</v>
       </c>
       <c r="C696" t="str">
-        <v>2026-07-27 17:39:26</v>
+        <v>2026-07-27 17:33:58</v>
       </c>
       <c r="D696" t="str">
         <v>NO</v>
@@ -10152,7 +10152,7 @@
         <v>6602</v>
       </c>
       <c r="C697" t="str">
-        <v>2026-07-27 17:51:27</v>
+        <v>2026-07-27 17:39:26</v>
       </c>
       <c r="D697" t="str">
         <v>NO</v>
@@ -10166,7 +10166,7 @@
         <v>6602</v>
       </c>
       <c r="C698" t="str">
-        <v>2026-07-27 18:02:36</v>
+        <v>2026-07-27 17:51:27</v>
       </c>
       <c r="D698" t="str">
         <v>NO</v>
@@ -10180,10 +10180,10 @@
         <v>6602</v>
       </c>
       <c r="C699" t="str">
-        <v>2026-07-27 22:09:06</v>
+        <v>2026-07-27 18:02:36</v>
       </c>
       <c r="D699" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="700">
@@ -10194,7 +10194,7 @@
         <v>6602</v>
       </c>
       <c r="C700" t="str">
-        <v>2026-07-28 00:16:39</v>
+        <v>2026-07-27 22:09:06</v>
       </c>
       <c r="D700" t="str">
         <v>SI</v>
@@ -10208,10 +10208,10 @@
         <v>6602</v>
       </c>
       <c r="C701" t="str">
-        <v>2026-07-28 11:06:47</v>
+        <v>2026-07-28 00:16:39</v>
       </c>
       <c r="D701" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="702">
@@ -10222,7 +10222,7 @@
         <v>6602</v>
       </c>
       <c r="C702" t="str">
-        <v>2026-07-28 13:07:25</v>
+        <v>2026-07-28 11:06:47</v>
       </c>
       <c r="D702" t="str">
         <v>NO</v>
@@ -10236,10 +10236,10 @@
         <v>6602</v>
       </c>
       <c r="C703" t="str">
-        <v>2026-07-28 19:51:05</v>
+        <v>2026-07-28 13:07:25</v>
       </c>
       <c r="D703" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="704">
@@ -10250,7 +10250,7 @@
         <v>6602</v>
       </c>
       <c r="C704" t="str">
-        <v>2026-07-28 22:32:30</v>
+        <v>2026-07-28 19:51:05</v>
       </c>
       <c r="D704" t="str">
         <v>SI</v>
@@ -10264,10 +10264,10 @@
         <v>6602</v>
       </c>
       <c r="C705" t="str">
-        <v>2026-07-29 11:09:49</v>
+        <v>2026-07-28 22:32:30</v>
       </c>
       <c r="D705" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="706">
@@ -10278,7 +10278,7 @@
         <v>6602</v>
       </c>
       <c r="C706" t="str">
-        <v>2026-07-29 11:10:00</v>
+        <v>2026-07-29 11:09:49</v>
       </c>
       <c r="D706" t="str">
         <v>NO</v>
@@ -10292,7 +10292,7 @@
         <v>6602</v>
       </c>
       <c r="C707" t="str">
-        <v>2026-07-29 15:07:50</v>
+        <v>2026-07-29 11:10:00</v>
       </c>
       <c r="D707" t="str">
         <v>NO</v>
@@ -10306,7 +10306,7 @@
         <v>6602</v>
       </c>
       <c r="C708" t="str">
-        <v>2026-07-29 15:59:05</v>
+        <v>2026-07-29 15:07:50</v>
       </c>
       <c r="D708" t="str">
         <v>NO</v>
@@ -10320,7 +10320,7 @@
         <v>6602</v>
       </c>
       <c r="C709" t="str">
-        <v>2026-07-29 17:06:13</v>
+        <v>2026-07-29 15:59:05</v>
       </c>
       <c r="D709" t="str">
         <v>NO</v>
@@ -10334,7 +10334,7 @@
         <v>6602</v>
       </c>
       <c r="C710" t="str">
-        <v>2026-07-29 17:17:17</v>
+        <v>2026-07-29 17:06:13</v>
       </c>
       <c r="D710" t="str">
         <v>NO</v>
@@ -10348,7 +10348,7 @@
         <v>6602</v>
       </c>
       <c r="C711" t="str">
-        <v>2026-07-29 18:32:27</v>
+        <v>2026-07-29 17:17:17</v>
       </c>
       <c r="D711" t="str">
         <v>NO</v>
@@ -10362,7 +10362,7 @@
         <v>6602</v>
       </c>
       <c r="C712" t="str">
-        <v>2026-07-29 18:33:25</v>
+        <v>2026-07-29 18:32:27</v>
       </c>
       <c r="D712" t="str">
         <v>NO</v>
@@ -10376,7 +10376,7 @@
         <v>6602</v>
       </c>
       <c r="C713" t="str">
-        <v>2026-07-29 18:34:13</v>
+        <v>2026-07-29 18:33:25</v>
       </c>
       <c r="D713" t="str">
         <v>NO</v>
@@ -10390,7 +10390,7 @@
         <v>6602</v>
       </c>
       <c r="C714" t="str">
-        <v>2026-07-29 18:45:41</v>
+        <v>2026-07-29 18:34:13</v>
       </c>
       <c r="D714" t="str">
         <v>NO</v>
@@ -10404,10 +10404,10 @@
         <v>6602</v>
       </c>
       <c r="C715" t="str">
-        <v>2026-07-29 19:33:49</v>
+        <v>2026-07-29 18:45:41</v>
       </c>
       <c r="D715" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="716">
@@ -10418,7 +10418,7 @@
         <v>6602</v>
       </c>
       <c r="C716" t="str">
-        <v>2026-07-29 21:18:25</v>
+        <v>2026-07-29 19:33:49</v>
       </c>
       <c r="D716" t="str">
         <v>SI</v>
@@ -10432,7 +10432,7 @@
         <v>6602</v>
       </c>
       <c r="C717" t="str">
-        <v>2026-07-29 22:37:23</v>
+        <v>2026-07-29 21:18:25</v>
       </c>
       <c r="D717" t="str">
         <v>SI</v>
@@ -10446,7 +10446,7 @@
         <v>6602</v>
       </c>
       <c r="C718" t="str">
-        <v>2026-07-29 22:37:31</v>
+        <v>2026-07-29 22:37:23</v>
       </c>
       <c r="D718" t="str">
         <v>SI</v>
@@ -10460,10 +10460,10 @@
         <v>6602</v>
       </c>
       <c r="C719" t="str">
-        <v>2026-07-30 11:06:27</v>
+        <v>2026-07-29 22:37:31</v>
       </c>
       <c r="D719" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="720">
@@ -10474,7 +10474,7 @@
         <v>6602</v>
       </c>
       <c r="C720" t="str">
-        <v>2026-07-30 15:16:13</v>
+        <v>2026-07-30 11:06:27</v>
       </c>
       <c r="D720" t="str">
         <v>NO</v>
@@ -10488,7 +10488,7 @@
         <v>6602</v>
       </c>
       <c r="C721" t="str">
-        <v>2026-07-30 18:48:57</v>
+        <v>2026-07-30 15:16:13</v>
       </c>
       <c r="D721" t="str">
         <v>NO</v>
@@ -10502,10 +10502,10 @@
         <v>6602</v>
       </c>
       <c r="C722" t="str">
-        <v>2026-07-30 20:39:13</v>
+        <v>2026-07-30 18:48:57</v>
       </c>
       <c r="D722" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="723">
@@ -10516,7 +10516,7 @@
         <v>6602</v>
       </c>
       <c r="C723" t="str">
-        <v>2026-07-30 20:45:51</v>
+        <v>2026-07-30 20:39:13</v>
       </c>
       <c r="D723" t="str">
         <v>SI</v>
@@ -10530,7 +10530,7 @@
         <v>6602</v>
       </c>
       <c r="C724" t="str">
-        <v>2026-07-30 21:22:41</v>
+        <v>2026-07-30 20:45:51</v>
       </c>
       <c r="D724" t="str">
         <v>SI</v>
@@ -10544,7 +10544,7 @@
         <v>6602</v>
       </c>
       <c r="C725" t="str">
-        <v>2026-07-30 23:04:31</v>
+        <v>2026-07-30 21:22:41</v>
       </c>
       <c r="D725" t="str">
         <v>SI</v>
@@ -10558,10 +10558,10 @@
         <v>6602</v>
       </c>
       <c r="C726" t="str">
-        <v>2026-07-31 11:12:15</v>
+        <v>2026-07-30 23:04:31</v>
       </c>
       <c r="D726" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="727">
@@ -10572,7 +10572,7 @@
         <v>6602</v>
       </c>
       <c r="C727" t="str">
-        <v>2026-07-31 12:40:29</v>
+        <v>2026-07-31 11:12:15</v>
       </c>
       <c r="D727" t="str">
         <v>NO</v>
@@ -10586,7 +10586,7 @@
         <v>6602</v>
       </c>
       <c r="C728" t="str">
-        <v>2026-07-31 14:09:39</v>
+        <v>2026-07-31 12:40:29</v>
       </c>
       <c r="D728" t="str">
         <v>NO</v>
@@ -10600,7 +10600,7 @@
         <v>6602</v>
       </c>
       <c r="C729" t="str">
-        <v>2026-07-31 14:38:13</v>
+        <v>2026-07-31 14:09:39</v>
       </c>
       <c r="D729" t="str">
         <v>NO</v>
@@ -10614,7 +10614,7 @@
         <v>6602</v>
       </c>
       <c r="C730" t="str">
-        <v>2026-07-31 16:38:52</v>
+        <v>2026-07-31 14:38:13</v>
       </c>
       <c r="D730" t="str">
         <v>NO</v>
@@ -10628,10 +10628,10 @@
         <v>6602</v>
       </c>
       <c r="C731" t="str">
-        <v>2026-07-31 19:07:18</v>
+        <v>2026-07-31 16:38:52</v>
       </c>
       <c r="D731" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="732">
@@ -10642,7 +10642,7 @@
         <v>6602</v>
       </c>
       <c r="C732" t="str">
-        <v>2026-07-31 19:32:34</v>
+        <v>2026-07-31 19:07:18</v>
       </c>
       <c r="D732" t="str">
         <v>SI</v>
@@ -10656,7 +10656,7 @@
         <v>6602</v>
       </c>
       <c r="C733" t="str">
-        <v>2026-07-31 20:36:50</v>
+        <v>2026-07-31 19:32:34</v>
       </c>
       <c r="D733" t="str">
         <v>SI</v>
@@ -10670,7 +10670,7 @@
         <v>6602</v>
       </c>
       <c r="C734" t="str">
-        <v>2026-07-31 20:58:24</v>
+        <v>2026-07-31 20:36:50</v>
       </c>
       <c r="D734" t="str">
         <v>SI</v>
@@ -10684,7 +10684,7 @@
         <v>6602</v>
       </c>
       <c r="C735" t="str">
-        <v>2026-07-31 21:32:52</v>
+        <v>2026-07-31 20:58:24</v>
       </c>
       <c r="D735" t="str">
         <v>SI</v>
@@ -10698,7 +10698,7 @@
         <v>6602</v>
       </c>
       <c r="C736" t="str">
-        <v>2026-07-31 21:40:44</v>
+        <v>2026-07-31 21:32:52</v>
       </c>
       <c r="D736" t="str">
         <v>SI</v>
@@ -10706,16 +10706,16 @@
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B737">
-        <v>6612</v>
+        <v>6602</v>
       </c>
       <c r="C737" t="str">
-        <v>2026-07-27 12:14:30</v>
+        <v>2026-07-31 21:40:44</v>
       </c>
       <c r="D737" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="738">
@@ -10726,7 +10726,7 @@
         <v>6612</v>
       </c>
       <c r="C738" t="str">
-        <v>2026-07-27 12:24:15</v>
+        <v>2026-07-27 12:14:30</v>
       </c>
       <c r="D738" t="str">
         <v>NO</v>
@@ -10740,7 +10740,7 @@
         <v>6612</v>
       </c>
       <c r="C739" t="str">
-        <v>2026-07-27 12:24:51</v>
+        <v>2026-07-27 12:24:15</v>
       </c>
       <c r="D739" t="str">
         <v>NO</v>
@@ -10754,7 +10754,7 @@
         <v>6612</v>
       </c>
       <c r="C740" t="str">
-        <v>2026-07-27 15:48:33</v>
+        <v>2026-07-27 12:24:51</v>
       </c>
       <c r="D740" t="str">
         <v>NO</v>
@@ -10768,7 +10768,7 @@
         <v>6612</v>
       </c>
       <c r="C741" t="str">
-        <v>2026-07-27 16:33:35</v>
+        <v>2026-07-27 15:48:33</v>
       </c>
       <c r="D741" t="str">
         <v>NO</v>
@@ -10782,7 +10782,7 @@
         <v>6612</v>
       </c>
       <c r="C742" t="str">
-        <v>2026-07-27 18:07:12</v>
+        <v>2026-07-27 16:33:35</v>
       </c>
       <c r="D742" t="str">
         <v>NO</v>
@@ -10796,10 +10796,10 @@
         <v>6612</v>
       </c>
       <c r="C743" t="str">
-        <v>2026-07-27 20:46:15</v>
+        <v>2026-07-27 18:07:12</v>
       </c>
       <c r="D743" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="744">
@@ -10810,7 +10810,7 @@
         <v>6612</v>
       </c>
       <c r="C744" t="str">
-        <v>2026-07-27 20:47:16</v>
+        <v>2026-07-27 20:46:15</v>
       </c>
       <c r="D744" t="str">
         <v>SI</v>
@@ -10824,10 +10824,10 @@
         <v>6612</v>
       </c>
       <c r="C745" t="str">
-        <v>2026-07-28 12:01:41</v>
+        <v>2026-07-27 20:47:16</v>
       </c>
       <c r="D745" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="746">
@@ -10838,7 +10838,7 @@
         <v>6612</v>
       </c>
       <c r="C746" t="str">
-        <v>2026-07-28 14:36:56</v>
+        <v>2026-07-28 12:01:41</v>
       </c>
       <c r="D746" t="str">
         <v>NO</v>
@@ -10852,7 +10852,7 @@
         <v>6612</v>
       </c>
       <c r="C747" t="str">
-        <v>2026-07-28 15:28:54</v>
+        <v>2026-07-28 14:36:56</v>
       </c>
       <c r="D747" t="str">
         <v>NO</v>
@@ -10866,7 +10866,7 @@
         <v>6612</v>
       </c>
       <c r="C748" t="str">
-        <v>2026-07-28 18:01:48</v>
+        <v>2026-07-28 15:28:54</v>
       </c>
       <c r="D748" t="str">
         <v>NO</v>
@@ -10880,7 +10880,7 @@
         <v>6612</v>
       </c>
       <c r="C749" t="str">
-        <v>2026-07-28 18:07:29</v>
+        <v>2026-07-28 18:01:48</v>
       </c>
       <c r="D749" t="str">
         <v>NO</v>
@@ -10894,7 +10894,7 @@
         <v>6612</v>
       </c>
       <c r="C750" t="str">
-        <v>2026-07-28 18:22:58</v>
+        <v>2026-07-28 18:07:29</v>
       </c>
       <c r="D750" t="str">
         <v>NO</v>
@@ -10908,10 +10908,10 @@
         <v>6612</v>
       </c>
       <c r="C751" t="str">
-        <v>2026-07-28 20:08:01</v>
+        <v>2026-07-28 18:22:58</v>
       </c>
       <c r="D751" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="752">
@@ -10922,7 +10922,7 @@
         <v>6612</v>
       </c>
       <c r="C752" t="str">
-        <v>2026-07-28 20:10:41</v>
+        <v>2026-07-28 20:08:01</v>
       </c>
       <c r="D752" t="str">
         <v>SI</v>
@@ -10936,7 +10936,7 @@
         <v>6612</v>
       </c>
       <c r="C753" t="str">
-        <v>2026-07-28 20:29:00</v>
+        <v>2026-07-28 20:10:41</v>
       </c>
       <c r="D753" t="str">
         <v>SI</v>
@@ -10950,7 +10950,7 @@
         <v>6612</v>
       </c>
       <c r="C754" t="str">
-        <v>2026-07-28 20:31:42</v>
+        <v>2026-07-28 20:29:00</v>
       </c>
       <c r="D754" t="str">
         <v>SI</v>
@@ -10964,7 +10964,7 @@
         <v>6612</v>
       </c>
       <c r="C755" t="str">
-        <v>2026-07-28 20:54:17</v>
+        <v>2026-07-28 20:31:42</v>
       </c>
       <c r="D755" t="str">
         <v>SI</v>
@@ -10978,7 +10978,7 @@
         <v>6612</v>
       </c>
       <c r="C756" t="str">
-        <v>2026-07-28 20:54:30</v>
+        <v>2026-07-28 20:54:17</v>
       </c>
       <c r="D756" t="str">
         <v>SI</v>
@@ -10992,10 +10992,10 @@
         <v>6612</v>
       </c>
       <c r="C757" t="str">
-        <v>2026-07-29 11:59:03</v>
+        <v>2026-07-28 20:54:30</v>
       </c>
       <c r="D757" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="758">
@@ -11006,7 +11006,7 @@
         <v>6612</v>
       </c>
       <c r="C758" t="str">
-        <v>2026-07-29 16:04:41</v>
+        <v>2026-07-29 11:59:03</v>
       </c>
       <c r="D758" t="str">
         <v>NO</v>
@@ -11020,7 +11020,7 @@
         <v>6612</v>
       </c>
       <c r="C759" t="str">
-        <v>2026-07-29 16:41:39</v>
+        <v>2026-07-29 16:04:41</v>
       </c>
       <c r="D759" t="str">
         <v>NO</v>
@@ -11034,7 +11034,7 @@
         <v>6612</v>
       </c>
       <c r="C760" t="str">
-        <v>2026-07-29 18:08:31</v>
+        <v>2026-07-29 16:41:39</v>
       </c>
       <c r="D760" t="str">
         <v>NO</v>
@@ -11048,7 +11048,7 @@
         <v>6612</v>
       </c>
       <c r="C761" t="str">
-        <v>2026-07-29 18:09:18</v>
+        <v>2026-07-29 18:08:31</v>
       </c>
       <c r="D761" t="str">
         <v>NO</v>
@@ -11062,7 +11062,7 @@
         <v>6612</v>
       </c>
       <c r="C762" t="str">
-        <v>2026-07-29 18:10:20</v>
+        <v>2026-07-29 18:09:18</v>
       </c>
       <c r="D762" t="str">
         <v>NO</v>
@@ -11076,7 +11076,7 @@
         <v>6612</v>
       </c>
       <c r="C763" t="str">
-        <v>2026-07-29 18:12:42</v>
+        <v>2026-07-29 18:10:20</v>
       </c>
       <c r="D763" t="str">
         <v>NO</v>
@@ -11090,10 +11090,10 @@
         <v>6612</v>
       </c>
       <c r="C764" t="str">
-        <v>2026-07-29 19:40:24</v>
+        <v>2026-07-29 18:12:42</v>
       </c>
       <c r="D764" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="765">
@@ -11104,7 +11104,7 @@
         <v>6612</v>
       </c>
       <c r="C765" t="str">
-        <v>2026-07-29 21:00:32</v>
+        <v>2026-07-29 19:40:24</v>
       </c>
       <c r="D765" t="str">
         <v>SI</v>
@@ -11118,10 +11118,10 @@
         <v>6612</v>
       </c>
       <c r="C766" t="str">
-        <v>2026-07-30 11:57:39</v>
+        <v>2026-07-29 21:00:32</v>
       </c>
       <c r="D766" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="767">
@@ -11132,7 +11132,7 @@
         <v>6612</v>
       </c>
       <c r="C767" t="str">
-        <v>2026-07-30 11:58:08</v>
+        <v>2026-07-30 11:57:39</v>
       </c>
       <c r="D767" t="str">
         <v>NO</v>
@@ -11146,7 +11146,7 @@
         <v>6612</v>
       </c>
       <c r="C768" t="str">
-        <v>2026-07-30 11:58:59</v>
+        <v>2026-07-30 11:58:08</v>
       </c>
       <c r="D768" t="str">
         <v>NO</v>
@@ -11160,7 +11160,7 @@
         <v>6612</v>
       </c>
       <c r="C769" t="str">
-        <v>2026-07-30 18:01:14</v>
+        <v>2026-07-30 11:58:59</v>
       </c>
       <c r="D769" t="str">
         <v>NO</v>
@@ -11174,7 +11174,7 @@
         <v>6612</v>
       </c>
       <c r="C770" t="str">
-        <v>2026-07-31 12:03:35</v>
+        <v>2026-07-30 18:01:14</v>
       </c>
       <c r="D770" t="str">
         <v>NO</v>
@@ -11188,7 +11188,7 @@
         <v>6612</v>
       </c>
       <c r="C771" t="str">
-        <v>2026-07-31 13:30:19</v>
+        <v>2026-07-31 12:03:35</v>
       </c>
       <c r="D771" t="str">
         <v>NO</v>
@@ -11202,7 +11202,7 @@
         <v>6612</v>
       </c>
       <c r="C772" t="str">
-        <v>2026-07-31 15:16:59</v>
+        <v>2026-07-31 13:30:19</v>
       </c>
       <c r="D772" t="str">
         <v>NO</v>
@@ -11216,7 +11216,7 @@
         <v>6612</v>
       </c>
       <c r="C773" t="str">
-        <v>2026-07-31 16:40:44</v>
+        <v>2026-07-31 15:16:59</v>
       </c>
       <c r="D773" t="str">
         <v>NO</v>
@@ -11230,7 +11230,7 @@
         <v>6612</v>
       </c>
       <c r="C774" t="str">
-        <v>2026-07-31 18:19:17</v>
+        <v>2026-07-31 16:40:44</v>
       </c>
       <c r="D774" t="str">
         <v>NO</v>
@@ -11244,24 +11244,24 @@
         <v>6612</v>
       </c>
       <c r="C775" t="str">
-        <v>2026-07-31 21:14:25</v>
+        <v>2026-07-31 18:19:17</v>
       </c>
       <c r="D775" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B776">
-        <v>6599</v>
+        <v>6612</v>
       </c>
       <c r="C776" t="str">
-        <v>2026-07-27 11:58:07</v>
+        <v>2026-07-31 21:14:25</v>
       </c>
       <c r="D776" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="777">
@@ -11272,7 +11272,7 @@
         <v>6599</v>
       </c>
       <c r="C777" t="str">
-        <v>2026-07-27 13:28:50</v>
+        <v>2026-07-27 11:58:07</v>
       </c>
       <c r="D777" t="str">
         <v>NO</v>
@@ -11286,7 +11286,7 @@
         <v>6599</v>
       </c>
       <c r="C778" t="str">
-        <v>2026-07-27 15:38:45</v>
+        <v>2026-07-27 13:28:50</v>
       </c>
       <c r="D778" t="str">
         <v>NO</v>
@@ -11300,7 +11300,7 @@
         <v>6599</v>
       </c>
       <c r="C779" t="str">
-        <v>2026-07-27 15:46:40</v>
+        <v>2026-07-27 15:38:45</v>
       </c>
       <c r="D779" t="str">
         <v>NO</v>
@@ -11314,10 +11314,10 @@
         <v>6599</v>
       </c>
       <c r="C780" t="str">
-        <v>2026-07-27 19:22:16</v>
+        <v>2026-07-27 15:46:40</v>
       </c>
       <c r="D780" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="781">
@@ -11328,7 +11328,7 @@
         <v>6599</v>
       </c>
       <c r="C781" t="str">
-        <v>2026-07-27 19:42:12</v>
+        <v>2026-07-27 19:22:16</v>
       </c>
       <c r="D781" t="str">
         <v>SI</v>
@@ -11342,7 +11342,7 @@
         <v>6599</v>
       </c>
       <c r="C782" t="str">
-        <v>2026-07-27 20:20:14</v>
+        <v>2026-07-27 19:42:12</v>
       </c>
       <c r="D782" t="str">
         <v>SI</v>
@@ -11356,7 +11356,7 @@
         <v>6599</v>
       </c>
       <c r="C783" t="str">
-        <v>2026-07-27 21:14:52</v>
+        <v>2026-07-27 20:20:14</v>
       </c>
       <c r="D783" t="str">
         <v>SI</v>
@@ -11370,10 +11370,10 @@
         <v>6599</v>
       </c>
       <c r="C784" t="str">
-        <v>2026-07-28 11:55:34</v>
+        <v>2026-07-27 21:14:52</v>
       </c>
       <c r="D784" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="785">
@@ -11384,7 +11384,7 @@
         <v>6599</v>
       </c>
       <c r="C785" t="str">
-        <v>2026-07-28 13:28:57</v>
+        <v>2026-07-28 11:55:34</v>
       </c>
       <c r="D785" t="str">
         <v>NO</v>
@@ -11398,7 +11398,7 @@
         <v>6599</v>
       </c>
       <c r="C786" t="str">
-        <v>2026-07-28 14:21:39</v>
+        <v>2026-07-28 13:28:57</v>
       </c>
       <c r="D786" t="str">
         <v>NO</v>
@@ -11412,7 +11412,7 @@
         <v>6599</v>
       </c>
       <c r="C787" t="str">
-        <v>2026-07-28 14:58:11</v>
+        <v>2026-07-28 14:21:39</v>
       </c>
       <c r="D787" t="str">
         <v>NO</v>
@@ -11426,7 +11426,7 @@
         <v>6599</v>
       </c>
       <c r="C788" t="str">
-        <v>2026-07-28 15:17:31</v>
+        <v>2026-07-28 14:58:11</v>
       </c>
       <c r="D788" t="str">
         <v>NO</v>
@@ -11440,7 +11440,7 @@
         <v>6599</v>
       </c>
       <c r="C789" t="str">
-        <v>2026-07-28 15:22:14</v>
+        <v>2026-07-28 15:17:31</v>
       </c>
       <c r="D789" t="str">
         <v>NO</v>
@@ -11454,7 +11454,7 @@
         <v>6599</v>
       </c>
       <c r="C790" t="str">
-        <v>2026-07-28 15:41:17</v>
+        <v>2026-07-28 15:22:14</v>
       </c>
       <c r="D790" t="str">
         <v>NO</v>
@@ -11468,7 +11468,7 @@
         <v>6599</v>
       </c>
       <c r="C791" t="str">
-        <v>2026-07-28 16:56:53</v>
+        <v>2026-07-28 15:41:17</v>
       </c>
       <c r="D791" t="str">
         <v>NO</v>
@@ -11482,7 +11482,7 @@
         <v>6599</v>
       </c>
       <c r="C792" t="str">
-        <v>2026-07-28 18:27:17</v>
+        <v>2026-07-28 16:56:53</v>
       </c>
       <c r="D792" t="str">
         <v>NO</v>
@@ -11496,7 +11496,7 @@
         <v>6599</v>
       </c>
       <c r="C793" t="str">
-        <v>2026-07-28 18:44:25</v>
+        <v>2026-07-28 18:27:17</v>
       </c>
       <c r="D793" t="str">
         <v>NO</v>
@@ -11510,7 +11510,7 @@
         <v>6599</v>
       </c>
       <c r="C794" t="str">
-        <v>2026-07-28 18:50:03</v>
+        <v>2026-07-28 18:44:25</v>
       </c>
       <c r="D794" t="str">
         <v>NO</v>
@@ -11524,10 +11524,10 @@
         <v>6599</v>
       </c>
       <c r="C795" t="str">
-        <v>2026-07-28 19:04:14</v>
+        <v>2026-07-28 18:50:03</v>
       </c>
       <c r="D795" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="796">
@@ -11538,7 +11538,7 @@
         <v>6599</v>
       </c>
       <c r="C796" t="str">
-        <v>2026-07-28 19:33:10</v>
+        <v>2026-07-28 19:04:14</v>
       </c>
       <c r="D796" t="str">
         <v>SI</v>
@@ -11552,7 +11552,7 @@
         <v>6599</v>
       </c>
       <c r="C797" t="str">
-        <v>2026-07-28 19:58:47</v>
+        <v>2026-07-28 19:33:10</v>
       </c>
       <c r="D797" t="str">
         <v>SI</v>
@@ -11566,7 +11566,7 @@
         <v>6599</v>
       </c>
       <c r="C798" t="str">
-        <v>2026-07-28 20:50:44</v>
+        <v>2026-07-28 19:58:47</v>
       </c>
       <c r="D798" t="str">
         <v>SI</v>
@@ -11580,10 +11580,10 @@
         <v>6599</v>
       </c>
       <c r="C799" t="str">
-        <v>2026-07-29 11:52:15</v>
+        <v>2026-07-28 20:50:44</v>
       </c>
       <c r="D799" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="800">
@@ -11594,10 +11594,10 @@
         <v>6599</v>
       </c>
       <c r="C800" t="str">
-        <v>2026-07-29 19:49:43</v>
+        <v>2026-07-29 11:52:15</v>
       </c>
       <c r="D800" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="801">
@@ -11608,7 +11608,7 @@
         <v>6599</v>
       </c>
       <c r="C801" t="str">
-        <v>2026-07-29 20:07:00</v>
+        <v>2026-07-29 19:49:43</v>
       </c>
       <c r="D801" t="str">
         <v>SI</v>
@@ -11622,10 +11622,10 @@
         <v>6599</v>
       </c>
       <c r="C802" t="str">
-        <v>2026-07-30 11:48:14</v>
+        <v>2026-07-29 20:07:00</v>
       </c>
       <c r="D802" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="803">
@@ -11636,7 +11636,7 @@
         <v>6599</v>
       </c>
       <c r="C803" t="str">
-        <v>2026-07-30 12:39:39</v>
+        <v>2026-07-30 11:48:14</v>
       </c>
       <c r="D803" t="str">
         <v>NO</v>
@@ -11650,7 +11650,7 @@
         <v>6599</v>
       </c>
       <c r="C804" t="str">
-        <v>2026-07-30 13:44:54</v>
+        <v>2026-07-30 12:39:39</v>
       </c>
       <c r="D804" t="str">
         <v>NO</v>
@@ -11664,10 +11664,10 @@
         <v>6599</v>
       </c>
       <c r="C805" t="str">
-        <v>2026-07-30 19:46:43</v>
+        <v>2026-07-30 13:44:54</v>
       </c>
       <c r="D805" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="806">
@@ -11678,7 +11678,7 @@
         <v>6599</v>
       </c>
       <c r="C806" t="str">
-        <v>2026-07-30 20:12:22</v>
+        <v>2026-07-30 19:46:43</v>
       </c>
       <c r="D806" t="str">
         <v>SI</v>
@@ -11692,10 +11692,10 @@
         <v>6599</v>
       </c>
       <c r="C807" t="str">
-        <v>2026-07-31 12:03:01</v>
+        <v>2026-07-30 20:12:22</v>
       </c>
       <c r="D807" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="808">
@@ -11706,7 +11706,7 @@
         <v>6599</v>
       </c>
       <c r="C808" t="str">
-        <v>2026-07-31 13:24:27</v>
+        <v>2026-07-31 12:03:01</v>
       </c>
       <c r="D808" t="str">
         <v>NO</v>
@@ -11720,7 +11720,7 @@
         <v>6599</v>
       </c>
       <c r="C809" t="str">
-        <v>2026-07-31 16:52:14</v>
+        <v>2026-07-31 13:24:27</v>
       </c>
       <c r="D809" t="str">
         <v>NO</v>
@@ -11734,10 +11734,10 @@
         <v>6599</v>
       </c>
       <c r="C810" t="str">
-        <v>2026-07-31 19:04:09</v>
+        <v>2026-07-31 16:52:14</v>
       </c>
       <c r="D810" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="811">
@@ -11748,7 +11748,7 @@
         <v>6599</v>
       </c>
       <c r="C811" t="str">
-        <v>2026-07-31 20:59:43</v>
+        <v>2026-07-31 19:04:09</v>
       </c>
       <c r="D811" t="str">
         <v>SI</v>
@@ -11762,7 +11762,7 @@
         <v>6599</v>
       </c>
       <c r="C812" t="str">
-        <v>2026-07-31 21:24:55</v>
+        <v>2026-07-31 20:59:43</v>
       </c>
       <c r="D812" t="str">
         <v>SI</v>
@@ -11770,16 +11770,16 @@
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>GV FOSERO SJHW-18 V OLIVARES</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B813">
-        <v>6592</v>
+        <v>6599</v>
       </c>
       <c r="C813" t="str">
-        <v>2026-07-27 08:27:58</v>
+        <v>2026-07-31 21:24:55</v>
       </c>
       <c r="D813" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="814">
@@ -11790,7 +11790,7 @@
         <v>6592</v>
       </c>
       <c r="C814" t="str">
-        <v>2026-07-27 08:28:48</v>
+        <v>2026-07-27 08:27:58</v>
       </c>
       <c r="D814" t="str">
         <v>NO</v>
@@ -11804,7 +11804,7 @@
         <v>6592</v>
       </c>
       <c r="C815" t="str">
-        <v>2026-07-27 10:34:32</v>
+        <v>2026-07-27 08:28:48</v>
       </c>
       <c r="D815" t="str">
         <v>NO</v>
@@ -11818,7 +11818,7 @@
         <v>6592</v>
       </c>
       <c r="C816" t="str">
-        <v>2026-07-27 11:07:30</v>
+        <v>2026-07-27 10:34:32</v>
       </c>
       <c r="D816" t="str">
         <v>NO</v>
@@ -11832,7 +11832,7 @@
         <v>6592</v>
       </c>
       <c r="C817" t="str">
-        <v>2026-07-27 12:14:42</v>
+        <v>2026-07-27 11:07:30</v>
       </c>
       <c r="D817" t="str">
         <v>NO</v>
@@ -11846,7 +11846,7 @@
         <v>6592</v>
       </c>
       <c r="C818" t="str">
-        <v>2026-07-27 15:00:59</v>
+        <v>2026-07-27 12:14:42</v>
       </c>
       <c r="D818" t="str">
         <v>NO</v>
@@ -11860,7 +11860,7 @@
         <v>6592</v>
       </c>
       <c r="C819" t="str">
-        <v>2026-07-27 15:46:40</v>
+        <v>2026-07-27 15:00:59</v>
       </c>
       <c r="D819" t="str">
         <v>NO</v>
@@ -11874,7 +11874,7 @@
         <v>6592</v>
       </c>
       <c r="C820" t="str">
-        <v>2026-07-27 15:50:16</v>
+        <v>2026-07-27 15:46:40</v>
       </c>
       <c r="D820" t="str">
         <v>NO</v>
@@ -11888,7 +11888,7 @@
         <v>6592</v>
       </c>
       <c r="C821" t="str">
-        <v>2026-07-27 18:28:35</v>
+        <v>2026-07-27 15:50:16</v>
       </c>
       <c r="D821" t="str">
         <v>NO</v>
@@ -11902,10 +11902,10 @@
         <v>6592</v>
       </c>
       <c r="C822" t="str">
-        <v>2026-07-27 19:12:51</v>
+        <v>2026-07-27 18:28:35</v>
       </c>
       <c r="D822" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="823">
@@ -11916,7 +11916,7 @@
         <v>6592</v>
       </c>
       <c r="C823" t="str">
-        <v>2026-07-27 19:13:43</v>
+        <v>2026-07-27 19:12:51</v>
       </c>
       <c r="D823" t="str">
         <v>SI</v>
@@ -11930,7 +11930,7 @@
         <v>6592</v>
       </c>
       <c r="C824" t="str">
-        <v>2026-07-27 19:16:39</v>
+        <v>2026-07-27 19:13:43</v>
       </c>
       <c r="D824" t="str">
         <v>SI</v>
@@ -11944,7 +11944,7 @@
         <v>6592</v>
       </c>
       <c r="C825" t="str">
-        <v>2026-07-27 19:36:25</v>
+        <v>2026-07-27 19:16:39</v>
       </c>
       <c r="D825" t="str">
         <v>SI</v>
@@ -11958,7 +11958,7 @@
         <v>6592</v>
       </c>
       <c r="C826" t="str">
-        <v>2026-07-27 19:37:17</v>
+        <v>2026-07-27 19:36:25</v>
       </c>
       <c r="D826" t="str">
         <v>SI</v>
@@ -11972,7 +11972,7 @@
         <v>6592</v>
       </c>
       <c r="C827" t="str">
-        <v>2026-07-27 20:45:35</v>
+        <v>2026-07-27 19:37:17</v>
       </c>
       <c r="D827" t="str">
         <v>SI</v>
@@ -11986,7 +11986,7 @@
         <v>6592</v>
       </c>
       <c r="C828" t="str">
-        <v>2026-07-28 21:47:14</v>
+        <v>2026-07-27 20:45:35</v>
       </c>
       <c r="D828" t="str">
         <v>SI</v>
@@ -12000,7 +12000,7 @@
         <v>6592</v>
       </c>
       <c r="C829" t="str">
-        <v>2026-07-31 21:25:46</v>
+        <v>2026-07-28 21:47:14</v>
       </c>
       <c r="D829" t="str">
         <v>SI</v>
@@ -12014,7 +12014,7 @@
         <v>6592</v>
       </c>
       <c r="C830" t="str">
-        <v>2026-08-02 19:45:05</v>
+        <v>2026-07-31 21:25:46</v>
       </c>
       <c r="D830" t="str">
         <v>SI</v>
@@ -12022,16 +12022,16 @@
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B831">
-        <v>6595</v>
+        <v>6592</v>
       </c>
       <c r="C831" t="str">
-        <v>2026-07-27 10:52:15</v>
+        <v>2026-08-02 19:45:05</v>
       </c>
       <c r="D831" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="832">
@@ -12042,7 +12042,7 @@
         <v>6595</v>
       </c>
       <c r="C832" t="str">
-        <v>2026-07-27 11:37:44</v>
+        <v>2026-07-27 10:52:15</v>
       </c>
       <c r="D832" t="str">
         <v>NO</v>
@@ -12056,7 +12056,7 @@
         <v>6595</v>
       </c>
       <c r="C833" t="str">
-        <v>2026-07-27 13:41:03</v>
+        <v>2026-07-27 11:37:44</v>
       </c>
       <c r="D833" t="str">
         <v>NO</v>
@@ -12070,7 +12070,7 @@
         <v>6595</v>
       </c>
       <c r="C834" t="str">
-        <v>2026-07-27 15:07:40</v>
+        <v>2026-07-27 13:41:03</v>
       </c>
       <c r="D834" t="str">
         <v>NO</v>
@@ -12084,7 +12084,7 @@
         <v>6595</v>
       </c>
       <c r="C835" t="str">
-        <v>2026-07-27 17:24:01</v>
+        <v>2026-07-27 15:07:40</v>
       </c>
       <c r="D835" t="str">
         <v>NO</v>
@@ -12098,7 +12098,7 @@
         <v>6595</v>
       </c>
       <c r="C836" t="str">
-        <v>2026-07-27 18:17:28</v>
+        <v>2026-07-27 17:24:01</v>
       </c>
       <c r="D836" t="str">
         <v>NO</v>
@@ -12112,7 +12112,7 @@
         <v>6595</v>
       </c>
       <c r="C837" t="str">
-        <v>2026-07-27 18:40:44</v>
+        <v>2026-07-27 18:17:28</v>
       </c>
       <c r="D837" t="str">
         <v>NO</v>
@@ -12126,10 +12126,10 @@
         <v>6595</v>
       </c>
       <c r="C838" t="str">
-        <v>2026-07-27 19:33:35</v>
+        <v>2026-07-27 18:40:44</v>
       </c>
       <c r="D838" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="839">
@@ -12140,10 +12140,10 @@
         <v>6595</v>
       </c>
       <c r="C839" t="str">
-        <v>2026-07-28 11:09:44</v>
+        <v>2026-07-27 19:33:35</v>
       </c>
       <c r="D839" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="840">
@@ -12154,7 +12154,7 @@
         <v>6595</v>
       </c>
       <c r="C840" t="str">
-        <v>2026-07-28 13:20:12</v>
+        <v>2026-07-28 11:09:44</v>
       </c>
       <c r="D840" t="str">
         <v>NO</v>
@@ -12168,7 +12168,7 @@
         <v>6595</v>
       </c>
       <c r="C841" t="str">
-        <v>2026-07-28 14:46:13</v>
+        <v>2026-07-28 13:20:12</v>
       </c>
       <c r="D841" t="str">
         <v>NO</v>
@@ -12182,7 +12182,7 @@
         <v>6595</v>
       </c>
       <c r="C842" t="str">
-        <v>2026-07-28 15:34:47</v>
+        <v>2026-07-28 14:46:13</v>
       </c>
       <c r="D842" t="str">
         <v>NO</v>
@@ -12196,7 +12196,7 @@
         <v>6595</v>
       </c>
       <c r="C843" t="str">
-        <v>2026-07-28 15:48:58</v>
+        <v>2026-07-28 15:34:47</v>
       </c>
       <c r="D843" t="str">
         <v>NO</v>
@@ -12210,7 +12210,7 @@
         <v>6595</v>
       </c>
       <c r="C844" t="str">
-        <v>2026-07-28 17:37:15</v>
+        <v>2026-07-28 15:48:58</v>
       </c>
       <c r="D844" t="str">
         <v>NO</v>
@@ -12224,7 +12224,7 @@
         <v>6595</v>
       </c>
       <c r="C845" t="str">
-        <v>2026-07-28 18:10:09</v>
+        <v>2026-07-28 17:37:15</v>
       </c>
       <c r="D845" t="str">
         <v>NO</v>
@@ -12238,10 +12238,10 @@
         <v>6595</v>
       </c>
       <c r="C846" t="str">
-        <v>2026-07-28 19:12:38</v>
+        <v>2026-07-28 18:10:09</v>
       </c>
       <c r="D846" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="847">
@@ -12252,7 +12252,7 @@
         <v>6595</v>
       </c>
       <c r="C847" t="str">
-        <v>2026-07-28 19:50:42</v>
+        <v>2026-07-28 19:12:38</v>
       </c>
       <c r="D847" t="str">
         <v>SI</v>
@@ -12266,7 +12266,7 @@
         <v>6595</v>
       </c>
       <c r="C848" t="str">
-        <v>2026-07-28 20:36:59</v>
+        <v>2026-07-28 19:50:42</v>
       </c>
       <c r="D848" t="str">
         <v>SI</v>
@@ -12280,7 +12280,7 @@
         <v>6595</v>
       </c>
       <c r="C849" t="str">
-        <v>2026-07-28 21:12:19</v>
+        <v>2026-07-28 20:36:59</v>
       </c>
       <c r="D849" t="str">
         <v>SI</v>
@@ -12294,10 +12294,10 @@
         <v>6595</v>
       </c>
       <c r="C850" t="str">
-        <v>2026-07-29 11:07:51</v>
+        <v>2026-07-28 21:12:19</v>
       </c>
       <c r="D850" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="851">
@@ -12308,7 +12308,7 @@
         <v>6595</v>
       </c>
       <c r="C851" t="str">
-        <v>2026-07-29 13:24:51</v>
+        <v>2026-07-29 11:07:51</v>
       </c>
       <c r="D851" t="str">
         <v>NO</v>
@@ -12322,7 +12322,7 @@
         <v>6595</v>
       </c>
       <c r="C852" t="str">
-        <v>2026-07-29 13:33:27</v>
+        <v>2026-07-29 13:24:51</v>
       </c>
       <c r="D852" t="str">
         <v>NO</v>
@@ -12336,7 +12336,7 @@
         <v>6595</v>
       </c>
       <c r="C853" t="str">
-        <v>2026-07-29 14:05:53</v>
+        <v>2026-07-29 13:33:27</v>
       </c>
       <c r="D853" t="str">
         <v>NO</v>
@@ -12350,7 +12350,7 @@
         <v>6595</v>
       </c>
       <c r="C854" t="str">
-        <v>2026-07-29 15:23:46</v>
+        <v>2026-07-29 14:05:53</v>
       </c>
       <c r="D854" t="str">
         <v>NO</v>
@@ -12364,7 +12364,7 @@
         <v>6595</v>
       </c>
       <c r="C855" t="str">
-        <v>2026-07-29 15:36:39</v>
+        <v>2026-07-29 15:23:46</v>
       </c>
       <c r="D855" t="str">
         <v>NO</v>
@@ -12378,7 +12378,7 @@
         <v>6595</v>
       </c>
       <c r="C856" t="str">
-        <v>2026-07-29 17:04:49</v>
+        <v>2026-07-29 15:36:39</v>
       </c>
       <c r="D856" t="str">
         <v>NO</v>
@@ -12392,7 +12392,7 @@
         <v>6595</v>
       </c>
       <c r="C857" t="str">
-        <v>2026-07-29 18:03:19</v>
+        <v>2026-07-29 17:04:49</v>
       </c>
       <c r="D857" t="str">
         <v>NO</v>
@@ -12406,10 +12406,10 @@
         <v>6595</v>
       </c>
       <c r="C858" t="str">
-        <v>2026-07-29 19:30:33</v>
+        <v>2026-07-29 18:03:19</v>
       </c>
       <c r="D858" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="859">
@@ -12420,7 +12420,7 @@
         <v>6595</v>
       </c>
       <c r="C859" t="str">
-        <v>2026-07-29 20:17:57</v>
+        <v>2026-07-29 19:30:33</v>
       </c>
       <c r="D859" t="str">
         <v>SI</v>
@@ -12434,7 +12434,7 @@
         <v>6595</v>
       </c>
       <c r="C860" t="str">
-        <v>2026-07-29 20:47:59</v>
+        <v>2026-07-29 20:17:57</v>
       </c>
       <c r="D860" t="str">
         <v>SI</v>
@@ -12448,7 +12448,7 @@
         <v>6595</v>
       </c>
       <c r="C861" t="str">
-        <v>2026-07-29 22:00:35</v>
+        <v>2026-07-29 20:47:59</v>
       </c>
       <c r="D861" t="str">
         <v>SI</v>
@@ -12462,10 +12462,10 @@
         <v>6595</v>
       </c>
       <c r="C862" t="str">
-        <v>2026-07-30 11:13:58</v>
+        <v>2026-07-29 22:00:35</v>
       </c>
       <c r="D862" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="863">
@@ -12476,7 +12476,7 @@
         <v>6595</v>
       </c>
       <c r="C863" t="str">
-        <v>2026-07-30 12:23:49</v>
+        <v>2026-07-30 11:13:58</v>
       </c>
       <c r="D863" t="str">
         <v>NO</v>
@@ -12490,7 +12490,7 @@
         <v>6595</v>
       </c>
       <c r="C864" t="str">
-        <v>2026-07-30 12:34:11</v>
+        <v>2026-07-30 12:23:49</v>
       </c>
       <c r="D864" t="str">
         <v>NO</v>
@@ -12504,7 +12504,7 @@
         <v>6595</v>
       </c>
       <c r="C865" t="str">
-        <v>2026-07-30 14:27:54</v>
+        <v>2026-07-30 12:34:11</v>
       </c>
       <c r="D865" t="str">
         <v>NO</v>
@@ -12518,7 +12518,7 @@
         <v>6595</v>
       </c>
       <c r="C866" t="str">
-        <v>2026-07-30 15:44:25</v>
+        <v>2026-07-30 14:27:54</v>
       </c>
       <c r="D866" t="str">
         <v>NO</v>
@@ -12532,7 +12532,7 @@
         <v>6595</v>
       </c>
       <c r="C867" t="str">
-        <v>2026-07-30 16:40:21</v>
+        <v>2026-07-30 15:44:25</v>
       </c>
       <c r="D867" t="str">
         <v>NO</v>
@@ -12546,7 +12546,7 @@
         <v>6595</v>
       </c>
       <c r="C868" t="str">
-        <v>2026-07-30 16:54:42</v>
+        <v>2026-07-30 16:40:21</v>
       </c>
       <c r="D868" t="str">
         <v>NO</v>
@@ -12560,7 +12560,7 @@
         <v>6595</v>
       </c>
       <c r="C869" t="str">
-        <v>2026-07-30 17:37:42</v>
+        <v>2026-07-30 16:54:42</v>
       </c>
       <c r="D869" t="str">
         <v>NO</v>
@@ -12574,7 +12574,7 @@
         <v>6595</v>
       </c>
       <c r="C870" t="str">
-        <v>2026-07-30 18:04:16</v>
+        <v>2026-07-30 17:37:42</v>
       </c>
       <c r="D870" t="str">
         <v>NO</v>
@@ -12588,7 +12588,7 @@
         <v>6595</v>
       </c>
       <c r="C871" t="str">
-        <v>2026-07-30 18:52:06</v>
+        <v>2026-07-30 18:04:16</v>
       </c>
       <c r="D871" t="str">
         <v>NO</v>
@@ -12602,10 +12602,10 @@
         <v>6595</v>
       </c>
       <c r="C872" t="str">
-        <v>2026-07-30 22:51:55</v>
+        <v>2026-07-30 18:52:06</v>
       </c>
       <c r="D872" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="873">
@@ -12616,10 +12616,10 @@
         <v>6595</v>
       </c>
       <c r="C873" t="str">
-        <v>2026-07-31 11:27:20</v>
+        <v>2026-07-30 22:51:55</v>
       </c>
       <c r="D873" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="874">
@@ -12630,7 +12630,7 @@
         <v>6595</v>
       </c>
       <c r="C874" t="str">
-        <v>2026-07-31 15:44:20</v>
+        <v>2026-07-31 11:27:20</v>
       </c>
       <c r="D874" t="str">
         <v>NO</v>
@@ -12644,7 +12644,7 @@
         <v>6595</v>
       </c>
       <c r="C875" t="str">
-        <v>2026-07-31 17:30:48</v>
+        <v>2026-07-31 15:44:20</v>
       </c>
       <c r="D875" t="str">
         <v>NO</v>
@@ -12658,10 +12658,10 @@
         <v>6595</v>
       </c>
       <c r="C876" t="str">
-        <v>2026-07-31 21:15:58</v>
+        <v>2026-07-31 17:30:48</v>
       </c>
       <c r="D876" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="877">
@@ -12672,7 +12672,7 @@
         <v>6595</v>
       </c>
       <c r="C877" t="str">
-        <v>2026-07-31 22:31:20</v>
+        <v>2026-07-31 21:15:58</v>
       </c>
       <c r="D877" t="str">
         <v>SI</v>
@@ -12680,16 +12680,16 @@
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>GV SHDV-50 C CARDENAS</v>
+        <v>GV PEUGEOT THJY-73 J PONCE</v>
       </c>
       <c r="B878">
-        <v>6585</v>
+        <v>6595</v>
       </c>
       <c r="C878" t="str">
-        <v>2026-07-27 11:10:46</v>
+        <v>2026-07-31 22:31:20</v>
       </c>
       <c r="D878" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="879">
@@ -12700,7 +12700,7 @@
         <v>6585</v>
       </c>
       <c r="C879" t="str">
-        <v>2026-07-27 14:11:11</v>
+        <v>2026-07-27 11:10:46</v>
       </c>
       <c r="D879" t="str">
         <v>NO</v>
@@ -12714,7 +12714,7 @@
         <v>6585</v>
       </c>
       <c r="C880" t="str">
-        <v>2026-07-27 14:25:28</v>
+        <v>2026-07-27 14:11:11</v>
       </c>
       <c r="D880" t="str">
         <v>NO</v>
@@ -12728,7 +12728,7 @@
         <v>6585</v>
       </c>
       <c r="C881" t="str">
-        <v>2026-07-27 17:01:23</v>
+        <v>2026-07-27 14:25:28</v>
       </c>
       <c r="D881" t="str">
         <v>NO</v>
@@ -12742,7 +12742,7 @@
         <v>6585</v>
       </c>
       <c r="C882" t="str">
-        <v>2026-07-27 18:17:30</v>
+        <v>2026-07-27 17:01:23</v>
       </c>
       <c r="D882" t="str">
         <v>NO</v>
@@ -12756,7 +12756,7 @@
         <v>6585</v>
       </c>
       <c r="C883" t="str">
-        <v>2026-07-27 18:26:52</v>
+        <v>2026-07-27 18:17:30</v>
       </c>
       <c r="D883" t="str">
         <v>NO</v>
@@ -12770,7 +12770,7 @@
         <v>6585</v>
       </c>
       <c r="C884" t="str">
-        <v>2026-07-28 11:04:23</v>
+        <v>2026-07-27 18:26:52</v>
       </c>
       <c r="D884" t="str">
         <v>NO</v>
@@ -12784,7 +12784,7 @@
         <v>6585</v>
       </c>
       <c r="C885" t="str">
-        <v>2026-07-28 12:45:40</v>
+        <v>2026-07-28 11:04:23</v>
       </c>
       <c r="D885" t="str">
         <v>NO</v>
@@ -12798,7 +12798,7 @@
         <v>6585</v>
       </c>
       <c r="C886" t="str">
-        <v>2026-07-28 14:25:03</v>
+        <v>2026-07-28 12:45:40</v>
       </c>
       <c r="D886" t="str">
         <v>NO</v>
@@ -12812,7 +12812,7 @@
         <v>6585</v>
       </c>
       <c r="C887" t="str">
-        <v>2026-07-28 14:48:49</v>
+        <v>2026-07-28 14:25:03</v>
       </c>
       <c r="D887" t="str">
         <v>NO</v>
@@ -12826,7 +12826,7 @@
         <v>6585</v>
       </c>
       <c r="C888" t="str">
-        <v>2026-07-28 16:40:19</v>
+        <v>2026-07-28 14:48:49</v>
       </c>
       <c r="D888" t="str">
         <v>NO</v>
@@ -12840,7 +12840,7 @@
         <v>6585</v>
       </c>
       <c r="C889" t="str">
-        <v>2026-07-28 16:42:03</v>
+        <v>2026-07-28 16:40:19</v>
       </c>
       <c r="D889" t="str">
         <v>NO</v>
@@ -12854,7 +12854,7 @@
         <v>6585</v>
       </c>
       <c r="C890" t="str">
-        <v>2026-07-28 16:46:47</v>
+        <v>2026-07-28 16:42:03</v>
       </c>
       <c r="D890" t="str">
         <v>NO</v>
@@ -12868,7 +12868,7 @@
         <v>6585</v>
       </c>
       <c r="C891" t="str">
-        <v>2026-07-28 17:30:15</v>
+        <v>2026-07-28 16:46:47</v>
       </c>
       <c r="D891" t="str">
         <v>NO</v>
@@ -12882,10 +12882,10 @@
         <v>6585</v>
       </c>
       <c r="C892" t="str">
-        <v>2026-07-28 21:53:10</v>
+        <v>2026-07-28 17:30:15</v>
       </c>
       <c r="D892" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="893">
@@ -12896,10 +12896,10 @@
         <v>6585</v>
       </c>
       <c r="C893" t="str">
-        <v>2026-07-29 11:25:55</v>
+        <v>2026-07-28 21:53:10</v>
       </c>
       <c r="D893" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="894">
@@ -12910,7 +12910,7 @@
         <v>6585</v>
       </c>
       <c r="C894" t="str">
-        <v>2026-07-29 14:53:13</v>
+        <v>2026-07-29 11:25:55</v>
       </c>
       <c r="D894" t="str">
         <v>NO</v>
@@ -12924,7 +12924,7 @@
         <v>6585</v>
       </c>
       <c r="C895" t="str">
-        <v>2026-07-29 17:02:03</v>
+        <v>2026-07-29 14:53:13</v>
       </c>
       <c r="D895" t="str">
         <v>NO</v>
@@ -12938,7 +12938,7 @@
         <v>6585</v>
       </c>
       <c r="C896" t="str">
-        <v>2026-07-29 17:58:15</v>
+        <v>2026-07-29 17:02:03</v>
       </c>
       <c r="D896" t="str">
         <v>NO</v>
@@ -12952,10 +12952,10 @@
         <v>6585</v>
       </c>
       <c r="C897" t="str">
-        <v>2026-07-29 20:49:41</v>
+        <v>2026-07-29 17:58:15</v>
       </c>
       <c r="D897" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="898">
@@ -12966,7 +12966,7 @@
         <v>6585</v>
       </c>
       <c r="C898" t="str">
-        <v>2026-07-29 21:00:58</v>
+        <v>2026-07-29 20:49:41</v>
       </c>
       <c r="D898" t="str">
         <v>SI</v>
@@ -12980,10 +12980,10 @@
         <v>6585</v>
       </c>
       <c r="C899" t="str">
-        <v>2026-07-30 11:12:09</v>
+        <v>2026-07-29 21:00:58</v>
       </c>
       <c r="D899" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="900">
@@ -12994,7 +12994,7 @@
         <v>6585</v>
       </c>
       <c r="C900" t="str">
-        <v>2026-07-30 12:17:25</v>
+        <v>2026-07-30 11:12:09</v>
       </c>
       <c r="D900" t="str">
         <v>NO</v>
@@ -13008,7 +13008,7 @@
         <v>6585</v>
       </c>
       <c r="C901" t="str">
-        <v>2026-07-30 14:52:40</v>
+        <v>2026-07-30 12:17:25</v>
       </c>
       <c r="D901" t="str">
         <v>NO</v>
@@ -13022,7 +13022,7 @@
         <v>6585</v>
       </c>
       <c r="C902" t="str">
-        <v>2026-07-30 15:43:06</v>
+        <v>2026-07-30 14:52:40</v>
       </c>
       <c r="D902" t="str">
         <v>NO</v>
@@ -13036,7 +13036,7 @@
         <v>6585</v>
       </c>
       <c r="C903" t="str">
-        <v>2026-07-30 17:32:22</v>
+        <v>2026-07-30 15:43:06</v>
       </c>
       <c r="D903" t="str">
         <v>NO</v>
@@ -13050,7 +13050,7 @@
         <v>6585</v>
       </c>
       <c r="C904" t="str">
-        <v>2026-07-30 17:40:10</v>
+        <v>2026-07-30 17:32:22</v>
       </c>
       <c r="D904" t="str">
         <v>NO</v>
@@ -13064,7 +13064,7 @@
         <v>6585</v>
       </c>
       <c r="C905" t="str">
-        <v>2026-07-30 18:12:42</v>
+        <v>2026-07-30 17:40:10</v>
       </c>
       <c r="D905" t="str">
         <v>NO</v>
@@ -13078,7 +13078,7 @@
         <v>6585</v>
       </c>
       <c r="C906" t="str">
-        <v>2026-07-30 18:21:26</v>
+        <v>2026-07-30 18:12:42</v>
       </c>
       <c r="D906" t="str">
         <v>NO</v>
@@ -13092,10 +13092,10 @@
         <v>6585</v>
       </c>
       <c r="C907" t="str">
-        <v>2026-07-30 21:08:18</v>
+        <v>2026-07-30 18:21:26</v>
       </c>
       <c r="D907" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="908">
@@ -13106,7 +13106,7 @@
         <v>6585</v>
       </c>
       <c r="C908" t="str">
-        <v>2026-07-30 22:08:20</v>
+        <v>2026-07-30 21:08:18</v>
       </c>
       <c r="D908" t="str">
         <v>SI</v>
@@ -13120,10 +13120,10 @@
         <v>6585</v>
       </c>
       <c r="C909" t="str">
-        <v>2026-07-31 16:43:38</v>
+        <v>2026-07-30 22:08:20</v>
       </c>
       <c r="D909" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="910">
@@ -13134,7 +13134,7 @@
         <v>6585</v>
       </c>
       <c r="C910" t="str">
-        <v>2026-07-31 17:17:44</v>
+        <v>2026-07-31 16:43:38</v>
       </c>
       <c r="D910" t="str">
         <v>NO</v>
@@ -13148,7 +13148,7 @@
         <v>6585</v>
       </c>
       <c r="C911" t="str">
-        <v>2026-07-31 18:20:16</v>
+        <v>2026-07-31 17:17:44</v>
       </c>
       <c r="D911" t="str">
         <v>NO</v>
@@ -13162,21 +13162,21 @@
         <v>6585</v>
       </c>
       <c r="C912" t="str">
-        <v>2026-07-31 21:17:11</v>
+        <v>2026-07-31 18:20:16</v>
       </c>
       <c r="D912" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV SHDV-50 C CARDENAS</v>
       </c>
       <c r="B913">
-        <v>6588</v>
+        <v>6585</v>
       </c>
       <c r="C913" t="str">
-        <v>2026-07-27 04:03:27</v>
+        <v>2026-07-31 21:17:11</v>
       </c>
       <c r="D913" t="str">
         <v>SI</v>
@@ -13190,10 +13190,10 @@
         <v>6588</v>
       </c>
       <c r="C914" t="str">
-        <v>2026-07-27 09:52:40</v>
+        <v>2026-07-27 04:03:27</v>
       </c>
       <c r="D914" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="915">
@@ -13204,7 +13204,7 @@
         <v>6588</v>
       </c>
       <c r="C915" t="str">
-        <v>2026-07-27 12:10:44</v>
+        <v>2026-07-27 09:52:40</v>
       </c>
       <c r="D915" t="str">
         <v>NO</v>
@@ -13218,7 +13218,7 @@
         <v>6588</v>
       </c>
       <c r="C916" t="str">
-        <v>2026-07-27 12:31:02</v>
+        <v>2026-07-27 12:10:44</v>
       </c>
       <c r="D916" t="str">
         <v>NO</v>
@@ -13232,7 +13232,7 @@
         <v>6588</v>
       </c>
       <c r="C917" t="str">
-        <v>2026-07-27 13:44:52</v>
+        <v>2026-07-27 12:31:02</v>
       </c>
       <c r="D917" t="str">
         <v>NO</v>
@@ -13246,7 +13246,7 @@
         <v>6588</v>
       </c>
       <c r="C918" t="str">
-        <v>2026-07-27 15:53:50</v>
+        <v>2026-07-27 13:44:52</v>
       </c>
       <c r="D918" t="str">
         <v>NO</v>
@@ -13260,7 +13260,7 @@
         <v>6588</v>
       </c>
       <c r="C919" t="str">
-        <v>2026-07-27 17:51:53</v>
+        <v>2026-07-27 15:53:50</v>
       </c>
       <c r="D919" t="str">
         <v>NO</v>
@@ -13274,10 +13274,10 @@
         <v>6588</v>
       </c>
       <c r="C920" t="str">
-        <v>2026-07-27 21:15:14</v>
+        <v>2026-07-27 17:51:53</v>
       </c>
       <c r="D920" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="921">
@@ -13288,7 +13288,7 @@
         <v>6588</v>
       </c>
       <c r="C921" t="str">
-        <v>2026-07-27 21:40:06</v>
+        <v>2026-07-27 21:15:14</v>
       </c>
       <c r="D921" t="str">
         <v>SI</v>
@@ -13302,7 +13302,7 @@
         <v>6588</v>
       </c>
       <c r="C922" t="str">
-        <v>2026-07-27 22:00:06</v>
+        <v>2026-07-27 21:40:06</v>
       </c>
       <c r="D922" t="str">
         <v>SI</v>
@@ -13316,7 +13316,7 @@
         <v>6588</v>
       </c>
       <c r="C923" t="str">
-        <v>2026-07-28 00:13:15</v>
+        <v>2026-07-27 22:00:06</v>
       </c>
       <c r="D923" t="str">
         <v>SI</v>
@@ -13330,7 +13330,7 @@
         <v>6588</v>
       </c>
       <c r="C924" t="str">
-        <v>2026-07-28 04:12:33</v>
+        <v>2026-07-28 00:13:15</v>
       </c>
       <c r="D924" t="str">
         <v>SI</v>
@@ -13344,7 +13344,7 @@
         <v>6588</v>
       </c>
       <c r="C925" t="str">
-        <v>2026-07-28 04:39:19</v>
+        <v>2026-07-28 04:12:33</v>
       </c>
       <c r="D925" t="str">
         <v>SI</v>
@@ -13358,7 +13358,7 @@
         <v>6588</v>
       </c>
       <c r="C926" t="str">
-        <v>2026-07-28 05:13:27</v>
+        <v>2026-07-28 04:39:19</v>
       </c>
       <c r="D926" t="str">
         <v>SI</v>
@@ -13372,10 +13372,10 @@
         <v>6588</v>
       </c>
       <c r="C927" t="str">
-        <v>2026-07-28 11:30:47</v>
+        <v>2026-07-28 05:13:27</v>
       </c>
       <c r="D927" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="928">
@@ -13386,7 +13386,7 @@
         <v>6588</v>
       </c>
       <c r="C928" t="str">
-        <v>2026-07-28 11:40:05</v>
+        <v>2026-07-28 11:30:47</v>
       </c>
       <c r="D928" t="str">
         <v>NO</v>
@@ -13400,7 +13400,7 @@
         <v>6588</v>
       </c>
       <c r="C929" t="str">
-        <v>2026-07-28 12:28:08</v>
+        <v>2026-07-28 11:40:05</v>
       </c>
       <c r="D929" t="str">
         <v>NO</v>
@@ -13414,7 +13414,7 @@
         <v>6588</v>
       </c>
       <c r="C930" t="str">
-        <v>2026-07-28 12:40:34</v>
+        <v>2026-07-28 12:28:08</v>
       </c>
       <c r="D930" t="str">
         <v>NO</v>
@@ -13428,7 +13428,7 @@
         <v>6588</v>
       </c>
       <c r="C931" t="str">
-        <v>2026-07-28 14:22:24</v>
+        <v>2026-07-28 12:40:34</v>
       </c>
       <c r="D931" t="str">
         <v>NO</v>
@@ -13442,7 +13442,7 @@
         <v>6588</v>
       </c>
       <c r="C932" t="str">
-        <v>2026-07-28 16:42:24</v>
+        <v>2026-07-28 14:22:24</v>
       </c>
       <c r="D932" t="str">
         <v>NO</v>
@@ -13456,7 +13456,7 @@
         <v>6588</v>
       </c>
       <c r="C933" t="str">
-        <v>2026-07-28 17:52:40</v>
+        <v>2026-07-28 16:42:24</v>
       </c>
       <c r="D933" t="str">
         <v>NO</v>
@@ -13470,10 +13470,10 @@
         <v>6588</v>
       </c>
       <c r="C934" t="str">
-        <v>2026-07-28 21:13:58</v>
+        <v>2026-07-28 17:52:40</v>
       </c>
       <c r="D934" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="935">
@@ -13484,10 +13484,10 @@
         <v>6588</v>
       </c>
       <c r="C935" t="str">
-        <v>2026-07-29 10:23:59</v>
+        <v>2026-07-28 21:13:58</v>
       </c>
       <c r="D935" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="936">
@@ -13498,7 +13498,7 @@
         <v>6588</v>
       </c>
       <c r="C936" t="str">
-        <v>2026-07-29 10:47:10</v>
+        <v>2026-07-29 10:23:59</v>
       </c>
       <c r="D936" t="str">
         <v>NO</v>
@@ -13512,7 +13512,7 @@
         <v>6588</v>
       </c>
       <c r="C937" t="str">
-        <v>2026-07-29 12:32:50</v>
+        <v>2026-07-29 10:47:10</v>
       </c>
       <c r="D937" t="str">
         <v>NO</v>
@@ -13526,7 +13526,7 @@
         <v>6588</v>
       </c>
       <c r="C938" t="str">
-        <v>2026-07-29 13:10:03</v>
+        <v>2026-07-29 12:32:50</v>
       </c>
       <c r="D938" t="str">
         <v>NO</v>
@@ -13540,7 +13540,7 @@
         <v>6588</v>
       </c>
       <c r="C939" t="str">
-        <v>2026-07-29 13:20:52</v>
+        <v>2026-07-29 13:10:03</v>
       </c>
       <c r="D939" t="str">
         <v>NO</v>
@@ -13554,7 +13554,7 @@
         <v>6588</v>
       </c>
       <c r="C940" t="str">
-        <v>2026-07-29 18:31:30</v>
+        <v>2026-07-29 13:20:52</v>
       </c>
       <c r="D940" t="str">
         <v>NO</v>
@@ -13568,10 +13568,10 @@
         <v>6588</v>
       </c>
       <c r="C941" t="str">
-        <v>2026-07-29 19:32:32</v>
+        <v>2026-07-29 18:31:30</v>
       </c>
       <c r="D941" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="942">
@@ -13582,7 +13582,7 @@
         <v>6588</v>
       </c>
       <c r="C942" t="str">
-        <v>2026-07-29 19:32:56</v>
+        <v>2026-07-29 19:32:32</v>
       </c>
       <c r="D942" t="str">
         <v>SI</v>
@@ -13596,7 +13596,7 @@
         <v>6588</v>
       </c>
       <c r="C943" t="str">
-        <v>2026-07-29 19:59:18</v>
+        <v>2026-07-29 19:32:56</v>
       </c>
       <c r="D943" t="str">
         <v>SI</v>
@@ -13610,7 +13610,7 @@
         <v>6588</v>
       </c>
       <c r="C944" t="str">
-        <v>2026-07-29 20:21:38</v>
+        <v>2026-07-29 19:59:18</v>
       </c>
       <c r="D944" t="str">
         <v>SI</v>
@@ -13624,7 +13624,7 @@
         <v>6588</v>
       </c>
       <c r="C945" t="str">
-        <v>2026-07-29 22:09:01</v>
+        <v>2026-07-29 20:21:38</v>
       </c>
       <c r="D945" t="str">
         <v>SI</v>
@@ -13638,7 +13638,7 @@
         <v>6588</v>
       </c>
       <c r="C946" t="str">
-        <v>2026-07-29 23:54:17</v>
+        <v>2026-07-29 22:09:01</v>
       </c>
       <c r="D946" t="str">
         <v>SI</v>
@@ -13652,7 +13652,7 @@
         <v>6588</v>
       </c>
       <c r="C947" t="str">
-        <v>2026-07-30 00:30:19</v>
+        <v>2026-07-29 23:54:17</v>
       </c>
       <c r="D947" t="str">
         <v>SI</v>
@@ -13666,7 +13666,7 @@
         <v>6588</v>
       </c>
       <c r="C948" t="str">
-        <v>2026-07-30 03:47:57</v>
+        <v>2026-07-30 00:30:19</v>
       </c>
       <c r="D948" t="str">
         <v>SI</v>
@@ -13680,7 +13680,7 @@
         <v>6588</v>
       </c>
       <c r="C949" t="str">
-        <v>2026-07-30 03:50:01</v>
+        <v>2026-07-30 03:47:57</v>
       </c>
       <c r="D949" t="str">
         <v>SI</v>
@@ -13694,10 +13694,10 @@
         <v>6588</v>
       </c>
       <c r="C950" t="str">
-        <v>2026-07-30 07:59:01</v>
+        <v>2026-07-30 03:50:01</v>
       </c>
       <c r="D950" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="951">
@@ -13708,7 +13708,7 @@
         <v>6588</v>
       </c>
       <c r="C951" t="str">
-        <v>2026-07-30 09:36:17</v>
+        <v>2026-07-30 07:59:01</v>
       </c>
       <c r="D951" t="str">
         <v>NO</v>
@@ -13722,7 +13722,7 @@
         <v>6588</v>
       </c>
       <c r="C952" t="str">
-        <v>2026-07-30 12:10:00</v>
+        <v>2026-07-30 09:36:17</v>
       </c>
       <c r="D952" t="str">
         <v>NO</v>
@@ -13736,7 +13736,7 @@
         <v>6588</v>
       </c>
       <c r="C953" t="str">
-        <v>2026-07-30 13:19:52</v>
+        <v>2026-07-30 12:10:00</v>
       </c>
       <c r="D953" t="str">
         <v>NO</v>
@@ -13750,7 +13750,7 @@
         <v>6588</v>
       </c>
       <c r="C954" t="str">
-        <v>2026-07-30 15:34:31</v>
+        <v>2026-07-30 13:19:52</v>
       </c>
       <c r="D954" t="str">
         <v>NO</v>
@@ -13764,7 +13764,7 @@
         <v>6588</v>
       </c>
       <c r="C955" t="str">
-        <v>2026-07-30 18:10:13</v>
+        <v>2026-07-30 15:34:31</v>
       </c>
       <c r="D955" t="str">
         <v>NO</v>
@@ -13778,7 +13778,7 @@
         <v>6588</v>
       </c>
       <c r="C956" t="str">
-        <v>2026-07-30 18:28:10</v>
+        <v>2026-07-30 18:10:13</v>
       </c>
       <c r="D956" t="str">
         <v>NO</v>
@@ -13792,7 +13792,7 @@
         <v>6588</v>
       </c>
       <c r="C957" t="str">
-        <v>2026-07-30 18:36:26</v>
+        <v>2026-07-30 18:28:10</v>
       </c>
       <c r="D957" t="str">
         <v>NO</v>
@@ -13806,10 +13806,10 @@
         <v>6588</v>
       </c>
       <c r="C958" t="str">
-        <v>2026-07-30 20:38:08</v>
+        <v>2026-07-30 18:36:26</v>
       </c>
       <c r="D958" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="959">
@@ -13820,7 +13820,7 @@
         <v>6588</v>
       </c>
       <c r="C959" t="str">
-        <v>2026-07-30 20:47:01</v>
+        <v>2026-07-30 20:38:08</v>
       </c>
       <c r="D959" t="str">
         <v>SI</v>
@@ -13834,7 +13834,7 @@
         <v>6588</v>
       </c>
       <c r="C960" t="str">
-        <v>2026-07-30 20:52:17</v>
+        <v>2026-07-30 20:47:01</v>
       </c>
       <c r="D960" t="str">
         <v>SI</v>
@@ -13848,7 +13848,7 @@
         <v>6588</v>
       </c>
       <c r="C961" t="str">
-        <v>2026-07-30 21:18:02</v>
+        <v>2026-07-30 20:52:17</v>
       </c>
       <c r="D961" t="str">
         <v>SI</v>
@@ -13862,7 +13862,7 @@
         <v>6588</v>
       </c>
       <c r="C962" t="str">
-        <v>2026-07-30 21:18:53</v>
+        <v>2026-07-30 21:18:02</v>
       </c>
       <c r="D962" t="str">
         <v>SI</v>
@@ -13876,7 +13876,7 @@
         <v>6588</v>
       </c>
       <c r="C963" t="str">
-        <v>2026-07-30 21:34:24</v>
+        <v>2026-07-30 21:18:53</v>
       </c>
       <c r="D963" t="str">
         <v>SI</v>
@@ -13890,7 +13890,7 @@
         <v>6588</v>
       </c>
       <c r="C964" t="str">
-        <v>2026-07-30 21:57:29</v>
+        <v>2026-07-30 21:34:24</v>
       </c>
       <c r="D964" t="str">
         <v>SI</v>
@@ -13904,7 +13904,7 @@
         <v>6588</v>
       </c>
       <c r="C965" t="str">
-        <v>2026-07-30 22:22:57</v>
+        <v>2026-07-30 21:57:29</v>
       </c>
       <c r="D965" t="str">
         <v>SI</v>
@@ -13918,7 +13918,7 @@
         <v>6588</v>
       </c>
       <c r="C966" t="str">
-        <v>2026-07-30 23:09:42</v>
+        <v>2026-07-30 22:22:57</v>
       </c>
       <c r="D966" t="str">
         <v>SI</v>
@@ -13932,7 +13932,7 @@
         <v>6588</v>
       </c>
       <c r="C967" t="str">
-        <v>2026-07-30 23:32:35</v>
+        <v>2026-07-30 23:09:42</v>
       </c>
       <c r="D967" t="str">
         <v>SI</v>
@@ -13946,7 +13946,7 @@
         <v>6588</v>
       </c>
       <c r="C968" t="str">
-        <v>2026-07-30 23:47:45</v>
+        <v>2026-07-30 23:32:35</v>
       </c>
       <c r="D968" t="str">
         <v>SI</v>
@@ -13960,10 +13960,10 @@
         <v>6588</v>
       </c>
       <c r="C969" t="str">
-        <v>2026-07-31 11:00:54</v>
+        <v>2026-07-30 23:47:45</v>
       </c>
       <c r="D969" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="970">
@@ -13974,7 +13974,7 @@
         <v>6588</v>
       </c>
       <c r="C970" t="str">
-        <v>2026-07-31 13:28:30</v>
+        <v>2026-07-31 11:00:54</v>
       </c>
       <c r="D970" t="str">
         <v>NO</v>
@@ -13988,7 +13988,7 @@
         <v>6588</v>
       </c>
       <c r="C971" t="str">
-        <v>2026-07-31 15:59:37</v>
+        <v>2026-07-31 13:28:30</v>
       </c>
       <c r="D971" t="str">
         <v>NO</v>
@@ -14002,7 +14002,7 @@
         <v>6588</v>
       </c>
       <c r="C972" t="str">
-        <v>2026-07-31 17:39:00</v>
+        <v>2026-07-31 15:59:37</v>
       </c>
       <c r="D972" t="str">
         <v>NO</v>
@@ -14016,7 +14016,7 @@
         <v>6588</v>
       </c>
       <c r="C973" t="str">
-        <v>2026-07-31 18:01:20</v>
+        <v>2026-07-31 17:39:00</v>
       </c>
       <c r="D973" t="str">
         <v>NO</v>
@@ -14030,7 +14030,7 @@
         <v>6588</v>
       </c>
       <c r="C974" t="str">
-        <v>2026-07-31 18:49:32</v>
+        <v>2026-07-31 18:01:20</v>
       </c>
       <c r="D974" t="str">
         <v>NO</v>
@@ -14044,10 +14044,10 @@
         <v>6588</v>
       </c>
       <c r="C975" t="str">
-        <v>2026-07-31 20:07:01</v>
+        <v>2026-07-31 18:49:32</v>
       </c>
       <c r="D975" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="976">
@@ -14058,7 +14058,7 @@
         <v>6588</v>
       </c>
       <c r="C976" t="str">
-        <v>2026-08-01 01:44:01</v>
+        <v>2026-07-31 20:07:01</v>
       </c>
       <c r="D976" t="str">
         <v>SI</v>
@@ -14072,7 +14072,7 @@
         <v>6588</v>
       </c>
       <c r="C977" t="str">
-        <v>2026-08-01 02:12:27</v>
+        <v>2026-08-01 01:44:01</v>
       </c>
       <c r="D977" t="str">
         <v>SI</v>
@@ -14086,7 +14086,7 @@
         <v>6588</v>
       </c>
       <c r="C978" t="str">
-        <v>2026-08-01 04:13:08</v>
+        <v>2026-08-01 02:12:27</v>
       </c>
       <c r="D978" t="str">
         <v>SI</v>
@@ -14100,7 +14100,7 @@
         <v>6588</v>
       </c>
       <c r="C979" t="str">
-        <v>2026-08-01 04:20:12</v>
+        <v>2026-08-01 04:13:08</v>
       </c>
       <c r="D979" t="str">
         <v>SI</v>
@@ -14114,7 +14114,7 @@
         <v>6588</v>
       </c>
       <c r="C980" t="str">
-        <v>2026-08-01 04:49:59</v>
+        <v>2026-08-01 04:20:12</v>
       </c>
       <c r="D980" t="str">
         <v>SI</v>
@@ -14128,7 +14128,7 @@
         <v>6588</v>
       </c>
       <c r="C981" t="str">
-        <v>2026-08-01 05:02:45</v>
+        <v>2026-08-01 04:49:59</v>
       </c>
       <c r="D981" t="str">
         <v>SI</v>
@@ -14142,7 +14142,7 @@
         <v>6588</v>
       </c>
       <c r="C982" t="str">
-        <v>2026-08-01 05:30:54</v>
+        <v>2026-08-01 05:02:45</v>
       </c>
       <c r="D982" t="str">
         <v>SI</v>
@@ -14156,7 +14156,7 @@
         <v>6588</v>
       </c>
       <c r="C983" t="str">
-        <v>2026-08-01 06:59:28</v>
+        <v>2026-08-01 05:30:54</v>
       </c>
       <c r="D983" t="str">
         <v>SI</v>
@@ -14170,7 +14170,7 @@
         <v>6588</v>
       </c>
       <c r="C984" t="str">
-        <v>2026-08-01 09:22:46</v>
+        <v>2026-08-01 06:59:28</v>
       </c>
       <c r="D984" t="str">
         <v>SI</v>
@@ -14184,7 +14184,7 @@
         <v>6588</v>
       </c>
       <c r="C985" t="str">
-        <v>2026-08-01 11:50:16</v>
+        <v>2026-08-01 09:22:46</v>
       </c>
       <c r="D985" t="str">
         <v>SI</v>
@@ -14198,7 +14198,7 @@
         <v>6588</v>
       </c>
       <c r="C986" t="str">
-        <v>2026-08-02 02:07:08</v>
+        <v>2026-08-01 11:50:16</v>
       </c>
       <c r="D986" t="str">
         <v>SI</v>
@@ -14212,7 +14212,7 @@
         <v>6588</v>
       </c>
       <c r="C987" t="str">
-        <v>2026-08-02 02:50:16</v>
+        <v>2026-08-02 02:07:08</v>
       </c>
       <c r="D987" t="str">
         <v>SI</v>
@@ -14226,7 +14226,7 @@
         <v>6588</v>
       </c>
       <c r="C988" t="str">
-        <v>2026-08-02 04:46:58</v>
+        <v>2026-08-02 02:50:16</v>
       </c>
       <c r="D988" t="str">
         <v>SI</v>
@@ -14240,7 +14240,7 @@
         <v>6588</v>
       </c>
       <c r="C989" t="str">
-        <v>2026-08-02 05:28:06</v>
+        <v>2026-08-02 04:46:58</v>
       </c>
       <c r="D989" t="str">
         <v>SI</v>
@@ -14254,7 +14254,7 @@
         <v>6588</v>
       </c>
       <c r="C990" t="str">
-        <v>2026-08-02 11:17:30</v>
+        <v>2026-08-02 05:28:06</v>
       </c>
       <c r="D990" t="str">
         <v>SI</v>
@@ -14262,16 +14262,16 @@
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B991">
-        <v>6587</v>
+        <v>6588</v>
       </c>
       <c r="C991" t="str">
-        <v>2026-07-27 11:02:26</v>
+        <v>2026-08-02 11:17:30</v>
       </c>
       <c r="D991" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="992">
@@ -14282,7 +14282,7 @@
         <v>6587</v>
       </c>
       <c r="C992" t="str">
-        <v>2026-07-27 12:52:30</v>
+        <v>2026-07-27 11:02:26</v>
       </c>
       <c r="D992" t="str">
         <v>NO</v>
@@ -14296,7 +14296,7 @@
         <v>6587</v>
       </c>
       <c r="C993" t="str">
-        <v>2026-07-27 13:05:15</v>
+        <v>2026-07-27 12:52:30</v>
       </c>
       <c r="D993" t="str">
         <v>NO</v>
@@ -14310,7 +14310,7 @@
         <v>6587</v>
       </c>
       <c r="C994" t="str">
-        <v>2026-07-27 13:47:46</v>
+        <v>2026-07-27 13:05:15</v>
       </c>
       <c r="D994" t="str">
         <v>NO</v>
@@ -14324,7 +14324,7 @@
         <v>6587</v>
       </c>
       <c r="C995" t="str">
-        <v>2026-07-27 14:12:40</v>
+        <v>2026-07-27 13:47:46</v>
       </c>
       <c r="D995" t="str">
         <v>NO</v>
@@ -14338,7 +14338,7 @@
         <v>6587</v>
       </c>
       <c r="C996" t="str">
-        <v>2026-07-27 14:47:45</v>
+        <v>2026-07-27 14:12:40</v>
       </c>
       <c r="D996" t="str">
         <v>NO</v>
@@ -14352,7 +14352,7 @@
         <v>6587</v>
       </c>
       <c r="C997" t="str">
-        <v>2026-07-27 15:01:38</v>
+        <v>2026-07-27 14:47:45</v>
       </c>
       <c r="D997" t="str">
         <v>NO</v>
@@ -14366,7 +14366,7 @@
         <v>6587</v>
       </c>
       <c r="C998" t="str">
-        <v>2026-07-27 16:38:27</v>
+        <v>2026-07-27 15:01:38</v>
       </c>
       <c r="D998" t="str">
         <v>NO</v>
@@ -14380,7 +14380,7 @@
         <v>6587</v>
       </c>
       <c r="C999" t="str">
-        <v>2026-07-27 17:29:22</v>
+        <v>2026-07-27 16:38:27</v>
       </c>
       <c r="D999" t="str">
         <v>NO</v>
@@ -14394,10 +14394,10 @@
         <v>6587</v>
       </c>
       <c r="C1000" t="str">
-        <v>2026-07-27 20:46:36</v>
+        <v>2026-07-27 17:29:22</v>
       </c>
       <c r="D1000" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1001">
@@ -14408,7 +14408,7 @@
         <v>6587</v>
       </c>
       <c r="C1001" t="str">
-        <v>2026-07-27 21:07:06</v>
+        <v>2026-07-27 20:46:36</v>
       </c>
       <c r="D1001" t="str">
         <v>SI</v>
@@ -14422,7 +14422,7 @@
         <v>6587</v>
       </c>
       <c r="C1002" t="str">
-        <v>2026-07-27 21:37:31</v>
+        <v>2026-07-27 21:07:06</v>
       </c>
       <c r="D1002" t="str">
         <v>SI</v>
@@ -14436,7 +14436,7 @@
         <v>6587</v>
       </c>
       <c r="C1003" t="str">
-        <v>2026-07-27 21:50:36</v>
+        <v>2026-07-27 21:37:31</v>
       </c>
       <c r="D1003" t="str">
         <v>SI</v>
@@ -14450,7 +14450,7 @@
         <v>6587</v>
       </c>
       <c r="C1004" t="str">
-        <v>2026-07-27 22:05:22</v>
+        <v>2026-07-27 21:50:36</v>
       </c>
       <c r="D1004" t="str">
         <v>SI</v>
@@ -14464,7 +14464,7 @@
         <v>6587</v>
       </c>
       <c r="C1005" t="str">
-        <v>2026-07-28 00:12:45</v>
+        <v>2026-07-27 22:05:22</v>
       </c>
       <c r="D1005" t="str">
         <v>SI</v>
@@ -14478,7 +14478,7 @@
         <v>6587</v>
       </c>
       <c r="C1006" t="str">
-        <v>2026-07-28 01:41:47</v>
+        <v>2026-07-28 00:12:45</v>
       </c>
       <c r="D1006" t="str">
         <v>SI</v>
@@ -14492,10 +14492,10 @@
         <v>6587</v>
       </c>
       <c r="C1007" t="str">
-        <v>2026-07-28 10:59:42</v>
+        <v>2026-07-28 01:41:47</v>
       </c>
       <c r="D1007" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1008">
@@ -14506,7 +14506,7 @@
         <v>6587</v>
       </c>
       <c r="C1008" t="str">
-        <v>2026-07-28 15:52:49</v>
+        <v>2026-07-28 10:59:42</v>
       </c>
       <c r="D1008" t="str">
         <v>NO</v>
@@ -14520,7 +14520,7 @@
         <v>6587</v>
       </c>
       <c r="C1009" t="str">
-        <v>2026-07-28 16:16:43</v>
+        <v>2026-07-28 15:52:49</v>
       </c>
       <c r="D1009" t="str">
         <v>NO</v>
@@ -14534,7 +14534,7 @@
         <v>6587</v>
       </c>
       <c r="C1010" t="str">
-        <v>2026-07-28 17:33:01</v>
+        <v>2026-07-28 16:16:43</v>
       </c>
       <c r="D1010" t="str">
         <v>NO</v>
@@ -14548,7 +14548,7 @@
         <v>6587</v>
       </c>
       <c r="C1011" t="str">
-        <v>2026-07-28 17:57:50</v>
+        <v>2026-07-28 17:33:01</v>
       </c>
       <c r="D1011" t="str">
         <v>NO</v>
@@ -14562,7 +14562,7 @@
         <v>6587</v>
       </c>
       <c r="C1012" t="str">
-        <v>2026-07-28 18:22:55</v>
+        <v>2026-07-28 17:57:50</v>
       </c>
       <c r="D1012" t="str">
         <v>NO</v>
@@ -14576,10 +14576,10 @@
         <v>6587</v>
       </c>
       <c r="C1013" t="str">
-        <v>2026-07-28 20:50:49</v>
+        <v>2026-07-28 18:22:55</v>
       </c>
       <c r="D1013" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1014">
@@ -14590,7 +14590,7 @@
         <v>6587</v>
       </c>
       <c r="C1014" t="str">
-        <v>2026-07-29 00:17:59</v>
+        <v>2026-07-28 20:50:49</v>
       </c>
       <c r="D1014" t="str">
         <v>SI</v>
@@ -14604,7 +14604,7 @@
         <v>6587</v>
       </c>
       <c r="C1015" t="str">
-        <v>2026-07-29 01:51:11</v>
+        <v>2026-07-29 00:17:59</v>
       </c>
       <c r="D1015" t="str">
         <v>SI</v>
@@ -14618,10 +14618,10 @@
         <v>6587</v>
       </c>
       <c r="C1016" t="str">
-        <v>2026-07-29 10:59:49</v>
+        <v>2026-07-29 01:51:11</v>
       </c>
       <c r="D1016" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1017">
@@ -14632,7 +14632,7 @@
         <v>6587</v>
       </c>
       <c r="C1017" t="str">
-        <v>2026-07-29 13:01:05</v>
+        <v>2026-07-29 10:59:49</v>
       </c>
       <c r="D1017" t="str">
         <v>NO</v>
@@ -14646,7 +14646,7 @@
         <v>6587</v>
       </c>
       <c r="C1018" t="str">
-        <v>2026-07-29 13:30:25</v>
+        <v>2026-07-29 13:01:05</v>
       </c>
       <c r="D1018" t="str">
         <v>NO</v>
@@ -14660,7 +14660,7 @@
         <v>6587</v>
       </c>
       <c r="C1019" t="str">
-        <v>2026-07-29 14:28:01</v>
+        <v>2026-07-29 13:30:25</v>
       </c>
       <c r="D1019" t="str">
         <v>NO</v>
@@ -14674,7 +14674,7 @@
         <v>6587</v>
       </c>
       <c r="C1020" t="str">
-        <v>2026-07-29 17:29:51</v>
+        <v>2026-07-29 14:28:01</v>
       </c>
       <c r="D1020" t="str">
         <v>NO</v>
@@ -14688,7 +14688,7 @@
         <v>6587</v>
       </c>
       <c r="C1021" t="str">
-        <v>2026-07-29 17:42:06</v>
+        <v>2026-07-29 17:29:51</v>
       </c>
       <c r="D1021" t="str">
         <v>NO</v>
@@ -14702,7 +14702,7 @@
         <v>6587</v>
       </c>
       <c r="C1022" t="str">
-        <v>2026-07-29 18:04:17</v>
+        <v>2026-07-29 17:42:06</v>
       </c>
       <c r="D1022" t="str">
         <v>NO</v>
@@ -14716,10 +14716,10 @@
         <v>6587</v>
       </c>
       <c r="C1023" t="str">
-        <v>2026-07-29 19:10:34</v>
+        <v>2026-07-29 18:04:17</v>
       </c>
       <c r="D1023" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1024">
@@ -14730,7 +14730,7 @@
         <v>6587</v>
       </c>
       <c r="C1024" t="str">
-        <v>2026-07-29 20:57:34</v>
+        <v>2026-07-29 19:10:34</v>
       </c>
       <c r="D1024" t="str">
         <v>SI</v>
@@ -14744,7 +14744,7 @@
         <v>6587</v>
       </c>
       <c r="C1025" t="str">
-        <v>2026-07-29 22:38:30</v>
+        <v>2026-07-29 20:57:34</v>
       </c>
       <c r="D1025" t="str">
         <v>SI</v>
@@ -14758,7 +14758,7 @@
         <v>6587</v>
       </c>
       <c r="C1026" t="str">
-        <v>2026-07-30 00:29:29</v>
+        <v>2026-07-29 22:38:30</v>
       </c>
       <c r="D1026" t="str">
         <v>SI</v>
@@ -14772,7 +14772,7 @@
         <v>6587</v>
       </c>
       <c r="C1027" t="str">
-        <v>2026-07-30 01:55:41</v>
+        <v>2026-07-30 00:29:29</v>
       </c>
       <c r="D1027" t="str">
         <v>SI</v>
@@ -14786,10 +14786,10 @@
         <v>6587</v>
       </c>
       <c r="C1028" t="str">
-        <v>2026-07-30 10:22:57</v>
+        <v>2026-07-30 01:55:41</v>
       </c>
       <c r="D1028" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1029">
@@ -14800,7 +14800,7 @@
         <v>6587</v>
       </c>
       <c r="C1029" t="str">
-        <v>2026-07-30 12:15:41</v>
+        <v>2026-07-30 10:22:57</v>
       </c>
       <c r="D1029" t="str">
         <v>NO</v>
@@ -14814,7 +14814,7 @@
         <v>6587</v>
       </c>
       <c r="C1030" t="str">
-        <v>2026-07-30 12:37:27</v>
+        <v>2026-07-30 12:15:41</v>
       </c>
       <c r="D1030" t="str">
         <v>NO</v>
@@ -14828,7 +14828,7 @@
         <v>6587</v>
       </c>
       <c r="C1031" t="str">
-        <v>2026-07-30 13:13:25</v>
+        <v>2026-07-30 12:37:27</v>
       </c>
       <c r="D1031" t="str">
         <v>NO</v>
@@ -14842,7 +14842,7 @@
         <v>6587</v>
       </c>
       <c r="C1032" t="str">
-        <v>2026-07-30 14:25:06</v>
+        <v>2026-07-30 13:13:25</v>
       </c>
       <c r="D1032" t="str">
         <v>NO</v>
@@ -14856,7 +14856,7 @@
         <v>6587</v>
       </c>
       <c r="C1033" t="str">
-        <v>2026-07-30 16:40:20</v>
+        <v>2026-07-30 14:25:06</v>
       </c>
       <c r="D1033" t="str">
         <v>NO</v>
@@ -14870,7 +14870,7 @@
         <v>6587</v>
       </c>
       <c r="C1034" t="str">
-        <v>2026-07-30 18:24:08</v>
+        <v>2026-07-30 16:40:20</v>
       </c>
       <c r="D1034" t="str">
         <v>NO</v>
@@ -14884,7 +14884,7 @@
         <v>6587</v>
       </c>
       <c r="C1035" t="str">
-        <v>2026-07-30 18:32:51</v>
+        <v>2026-07-30 18:24:08</v>
       </c>
       <c r="D1035" t="str">
         <v>NO</v>
@@ -14898,10 +14898,10 @@
         <v>6587</v>
       </c>
       <c r="C1036" t="str">
-        <v>2026-07-30 19:43:05</v>
+        <v>2026-07-30 18:32:51</v>
       </c>
       <c r="D1036" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1037">
@@ -14912,7 +14912,7 @@
         <v>6587</v>
       </c>
       <c r="C1037" t="str">
-        <v>2026-07-31 01:53:32</v>
+        <v>2026-07-30 19:43:05</v>
       </c>
       <c r="D1037" t="str">
         <v>SI</v>
@@ -14926,7 +14926,7 @@
         <v>6587</v>
       </c>
       <c r="C1038" t="str">
-        <v>2026-07-31 04:03:42</v>
+        <v>2026-07-31 01:53:32</v>
       </c>
       <c r="D1038" t="str">
         <v>SI</v>
@@ -14940,7 +14940,7 @@
         <v>6587</v>
       </c>
       <c r="C1039" t="str">
-        <v>2026-07-31 04:59:02</v>
+        <v>2026-07-31 04:03:42</v>
       </c>
       <c r="D1039" t="str">
         <v>SI</v>
@@ -14954,7 +14954,7 @@
         <v>6587</v>
       </c>
       <c r="C1040" t="str">
-        <v>2026-07-31 05:50:00</v>
+        <v>2026-07-31 04:59:02</v>
       </c>
       <c r="D1040" t="str">
         <v>SI</v>
@@ -14968,10 +14968,10 @@
         <v>6587</v>
       </c>
       <c r="C1041" t="str">
-        <v>2026-07-31 08:18:48</v>
+        <v>2026-07-31 05:50:00</v>
       </c>
       <c r="D1041" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1042">
@@ -14982,7 +14982,7 @@
         <v>6587</v>
       </c>
       <c r="C1042" t="str">
-        <v>2026-07-31 09:30:26</v>
+        <v>2026-07-31 08:18:48</v>
       </c>
       <c r="D1042" t="str">
         <v>NO</v>
@@ -14996,7 +14996,7 @@
         <v>6587</v>
       </c>
       <c r="C1043" t="str">
-        <v>2026-07-31 11:48:25</v>
+        <v>2026-07-31 09:30:26</v>
       </c>
       <c r="D1043" t="str">
         <v>NO</v>
@@ -15010,7 +15010,7 @@
         <v>6587</v>
       </c>
       <c r="C1044" t="str">
-        <v>2026-07-31 12:08:39</v>
+        <v>2026-07-31 11:48:25</v>
       </c>
       <c r="D1044" t="str">
         <v>NO</v>
@@ -15024,7 +15024,7 @@
         <v>6587</v>
       </c>
       <c r="C1045" t="str">
-        <v>2026-07-31 17:16:50</v>
+        <v>2026-07-31 12:08:39</v>
       </c>
       <c r="D1045" t="str">
         <v>NO</v>
@@ -15038,10 +15038,10 @@
         <v>6587</v>
       </c>
       <c r="C1046" t="str">
-        <v>2026-08-01 10:17:05</v>
+        <v>2026-07-31 17:16:50</v>
       </c>
       <c r="D1046" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1047">
@@ -15052,7 +15052,7 @@
         <v>6587</v>
       </c>
       <c r="C1047" t="str">
-        <v>2026-08-01 10:58:03</v>
+        <v>2026-08-01 10:17:05</v>
       </c>
       <c r="D1047" t="str">
         <v>SI</v>
@@ -15066,7 +15066,7 @@
         <v>6587</v>
       </c>
       <c r="C1048" t="str">
-        <v>2026-08-01 11:59:52</v>
+        <v>2026-08-01 10:58:03</v>
       </c>
       <c r="D1048" t="str">
         <v>SI</v>
@@ -15080,7 +15080,7 @@
         <v>6587</v>
       </c>
       <c r="C1049" t="str">
-        <v>2026-08-01 12:32:30</v>
+        <v>2026-08-01 11:59:52</v>
       </c>
       <c r="D1049" t="str">
         <v>SI</v>
@@ -15094,7 +15094,7 @@
         <v>6587</v>
       </c>
       <c r="C1050" t="str">
-        <v>2026-08-01 14:49:16</v>
+        <v>2026-08-01 12:32:30</v>
       </c>
       <c r="D1050" t="str">
         <v>SI</v>
@@ -15108,7 +15108,7 @@
         <v>6587</v>
       </c>
       <c r="C1051" t="str">
-        <v>2026-08-01 15:59:49</v>
+        <v>2026-08-01 14:49:16</v>
       </c>
       <c r="D1051" t="str">
         <v>SI</v>
@@ -15122,7 +15122,7 @@
         <v>6587</v>
       </c>
       <c r="C1052" t="str">
-        <v>2026-08-01 18:21:19</v>
+        <v>2026-08-01 15:59:49</v>
       </c>
       <c r="D1052" t="str">
         <v>SI</v>
@@ -15136,7 +15136,7 @@
         <v>6587</v>
       </c>
       <c r="C1053" t="str">
-        <v>2026-08-01 19:59:53</v>
+        <v>2026-08-01 18:21:19</v>
       </c>
       <c r="D1053" t="str">
         <v>SI</v>
@@ -15150,7 +15150,7 @@
         <v>6587</v>
       </c>
       <c r="C1054" t="str">
-        <v>2026-08-02 10:12:32</v>
+        <v>2026-08-01 19:59:53</v>
       </c>
       <c r="D1054" t="str">
         <v>SI</v>
@@ -15164,7 +15164,7 @@
         <v>6587</v>
       </c>
       <c r="C1055" t="str">
-        <v>2026-08-02 14:54:05</v>
+        <v>2026-08-02 10:12:32</v>
       </c>
       <c r="D1055" t="str">
         <v>SI</v>
@@ -15178,7 +15178,7 @@
         <v>6587</v>
       </c>
       <c r="C1056" t="str">
-        <v>2026-08-02 20:11:17</v>
+        <v>2026-08-02 14:54:05</v>
       </c>
       <c r="D1056" t="str">
         <v>SI</v>
@@ -15192,7 +15192,7 @@
         <v>6587</v>
       </c>
       <c r="C1057" t="str">
-        <v>2026-08-02 20:39:05</v>
+        <v>2026-08-02 20:11:17</v>
       </c>
       <c r="D1057" t="str">
         <v>SI</v>
@@ -15200,16 +15200,16 @@
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B1058">
-        <v>6582</v>
+        <v>6587</v>
       </c>
       <c r="C1058" t="str">
-        <v>2026-07-30 15:14:24</v>
+        <v>2026-08-02 20:39:05</v>
       </c>
       <c r="D1058" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1059">
@@ -15220,7 +15220,7 @@
         <v>6582</v>
       </c>
       <c r="C1059" t="str">
-        <v>2026-07-30 15:19:26</v>
+        <v>2026-07-30 15:14:24</v>
       </c>
       <c r="D1059" t="str">
         <v>NO</v>
@@ -15234,7 +15234,7 @@
         <v>6582</v>
       </c>
       <c r="C1060" t="str">
-        <v>2026-07-30 16:24:49</v>
+        <v>2026-07-30 15:19:26</v>
       </c>
       <c r="D1060" t="str">
         <v>NO</v>
@@ -15248,7 +15248,7 @@
         <v>6582</v>
       </c>
       <c r="C1061" t="str">
-        <v>2026-07-30 18:10:08</v>
+        <v>2026-07-30 16:24:49</v>
       </c>
       <c r="D1061" t="str">
         <v>NO</v>
@@ -15262,10 +15262,10 @@
         <v>6582</v>
       </c>
       <c r="C1062" t="str">
-        <v>2026-07-30 19:25:20</v>
+        <v>2026-07-30 18:10:08</v>
       </c>
       <c r="D1062" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1063">
@@ -15276,7 +15276,7 @@
         <v>6582</v>
       </c>
       <c r="C1063" t="str">
-        <v>2026-07-30 20:17:33</v>
+        <v>2026-07-30 19:25:20</v>
       </c>
       <c r="D1063" t="str">
         <v>SI</v>
@@ -15290,7 +15290,7 @@
         <v>6582</v>
       </c>
       <c r="C1064" t="str">
-        <v>2026-07-30 21:09:05</v>
+        <v>2026-07-30 20:17:33</v>
       </c>
       <c r="D1064" t="str">
         <v>SI</v>
@@ -15304,7 +15304,7 @@
         <v>6582</v>
       </c>
       <c r="C1065" t="str">
-        <v>2026-07-30 21:18:55</v>
+        <v>2026-07-30 21:09:05</v>
       </c>
       <c r="D1065" t="str">
         <v>SI</v>
@@ -15318,7 +15318,7 @@
         <v>6582</v>
       </c>
       <c r="C1066" t="str">
-        <v>2026-07-30 22:28:53</v>
+        <v>2026-07-30 21:18:55</v>
       </c>
       <c r="D1066" t="str">
         <v>SI</v>
@@ -15332,7 +15332,7 @@
         <v>6582</v>
       </c>
       <c r="C1067" t="str">
-        <v>2026-07-30 22:31:56</v>
+        <v>2026-07-30 22:28:53</v>
       </c>
       <c r="D1067" t="str">
         <v>SI</v>
@@ -15346,7 +15346,7 @@
         <v>6582</v>
       </c>
       <c r="C1068" t="str">
-        <v>2026-07-30 23:24:11</v>
+        <v>2026-07-30 22:31:56</v>
       </c>
       <c r="D1068" t="str">
         <v>SI</v>
@@ -15360,7 +15360,7 @@
         <v>6582</v>
       </c>
       <c r="C1069" t="str">
-        <v>2026-07-31 00:43:04</v>
+        <v>2026-07-30 23:24:11</v>
       </c>
       <c r="D1069" t="str">
         <v>SI</v>
@@ -15374,7 +15374,7 @@
         <v>6582</v>
       </c>
       <c r="C1070" t="str">
-        <v>2026-07-31 01:00:56</v>
+        <v>2026-07-31 00:43:04</v>
       </c>
       <c r="D1070" t="str">
         <v>SI</v>
@@ -15388,7 +15388,7 @@
         <v>6582</v>
       </c>
       <c r="C1071" t="str">
-        <v>2026-07-31 02:01:57</v>
+        <v>2026-07-31 01:00:56</v>
       </c>
       <c r="D1071" t="str">
         <v>SI</v>
@@ -15402,7 +15402,7 @@
         <v>6582</v>
       </c>
       <c r="C1072" t="str">
-        <v>2026-07-31 02:47:26</v>
+        <v>2026-07-31 02:01:57</v>
       </c>
       <c r="D1072" t="str">
         <v>SI</v>
@@ -15416,7 +15416,7 @@
         <v>6582</v>
       </c>
       <c r="C1073" t="str">
-        <v>2026-07-31 03:33:00</v>
+        <v>2026-07-31 02:47:26</v>
       </c>
       <c r="D1073" t="str">
         <v>SI</v>
@@ -15430,7 +15430,7 @@
         <v>6582</v>
       </c>
       <c r="C1074" t="str">
-        <v>2026-07-31 04:13:51</v>
+        <v>2026-07-31 03:33:00</v>
       </c>
       <c r="D1074" t="str">
         <v>SI</v>
@@ -15444,10 +15444,10 @@
         <v>6582</v>
       </c>
       <c r="C1075" t="str">
-        <v>2026-07-31 18:05:41</v>
+        <v>2026-07-31 04:13:51</v>
       </c>
       <c r="D1075" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1076">
@@ -15458,10 +15458,10 @@
         <v>6582</v>
       </c>
       <c r="C1076" t="str">
-        <v>2026-07-31 20:07:54</v>
+        <v>2026-07-31 18:05:41</v>
       </c>
       <c r="D1076" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1077">
@@ -15472,7 +15472,7 @@
         <v>6582</v>
       </c>
       <c r="C1077" t="str">
-        <v>2026-07-31 21:49:32</v>
+        <v>2026-07-31 20:07:54</v>
       </c>
       <c r="D1077" t="str">
         <v>SI</v>
@@ -15486,7 +15486,7 @@
         <v>6582</v>
       </c>
       <c r="C1078" t="str">
-        <v>2026-07-31 22:06:12</v>
+        <v>2026-07-31 21:49:32</v>
       </c>
       <c r="D1078" t="str">
         <v>SI</v>
@@ -15500,7 +15500,7 @@
         <v>6582</v>
       </c>
       <c r="C1079" t="str">
-        <v>2026-07-31 22:28:05</v>
+        <v>2026-07-31 22:06:12</v>
       </c>
       <c r="D1079" t="str">
         <v>SI</v>
@@ -15514,7 +15514,7 @@
         <v>6582</v>
       </c>
       <c r="C1080" t="str">
-        <v>2026-07-31 22:34:08</v>
+        <v>2026-07-31 22:28:05</v>
       </c>
       <c r="D1080" t="str">
         <v>SI</v>
@@ -15528,7 +15528,7 @@
         <v>6582</v>
       </c>
       <c r="C1081" t="str">
-        <v>2026-07-31 22:45:54</v>
+        <v>2026-07-31 22:34:08</v>
       </c>
       <c r="D1081" t="str">
         <v>SI</v>
@@ -15542,7 +15542,7 @@
         <v>6582</v>
       </c>
       <c r="C1082" t="str">
-        <v>2026-07-31 23:36:14</v>
+        <v>2026-07-31 22:45:54</v>
       </c>
       <c r="D1082" t="str">
         <v>SI</v>
@@ -15556,7 +15556,7 @@
         <v>6582</v>
       </c>
       <c r="C1083" t="str">
-        <v>2026-08-01 01:04:54</v>
+        <v>2026-07-31 23:36:14</v>
       </c>
       <c r="D1083" t="str">
         <v>SI</v>
@@ -15570,7 +15570,7 @@
         <v>6582</v>
       </c>
       <c r="C1084" t="str">
-        <v>2026-08-01 01:18:08</v>
+        <v>2026-08-01 01:04:54</v>
       </c>
       <c r="D1084" t="str">
         <v>SI</v>
@@ -15584,7 +15584,7 @@
         <v>6582</v>
       </c>
       <c r="C1085" t="str">
-        <v>2026-08-01 01:20:46</v>
+        <v>2026-08-01 01:18:08</v>
       </c>
       <c r="D1085" t="str">
         <v>SI</v>
@@ -15598,7 +15598,7 @@
         <v>6582</v>
       </c>
       <c r="C1086" t="str">
-        <v>2026-08-01 02:03:36</v>
+        <v>2026-08-01 01:20:46</v>
       </c>
       <c r="D1086" t="str">
         <v>SI</v>
@@ -15612,7 +15612,7 @@
         <v>6582</v>
       </c>
       <c r="C1087" t="str">
-        <v>2026-08-01 04:11:52</v>
+        <v>2026-08-01 02:03:36</v>
       </c>
       <c r="D1087" t="str">
         <v>SI</v>
@@ -15626,7 +15626,7 @@
         <v>6582</v>
       </c>
       <c r="C1088" t="str">
-        <v>2026-08-01 18:01:51</v>
+        <v>2026-08-01 04:11:52</v>
       </c>
       <c r="D1088" t="str">
         <v>SI</v>
@@ -15640,7 +15640,7 @@
         <v>6582</v>
       </c>
       <c r="C1089" t="str">
-        <v>2026-08-01 19:08:00</v>
+        <v>2026-08-01 18:01:51</v>
       </c>
       <c r="D1089" t="str">
         <v>SI</v>
@@ -15654,7 +15654,7 @@
         <v>6582</v>
       </c>
       <c r="C1090" t="str">
-        <v>2026-08-01 20:34:33</v>
+        <v>2026-08-01 19:08:00</v>
       </c>
       <c r="D1090" t="str">
         <v>SI</v>
@@ -15668,7 +15668,7 @@
         <v>6582</v>
       </c>
       <c r="C1091" t="str">
-        <v>2026-08-01 21:11:24</v>
+        <v>2026-08-01 20:34:33</v>
       </c>
       <c r="D1091" t="str">
         <v>SI</v>
@@ -15682,7 +15682,7 @@
         <v>6582</v>
       </c>
       <c r="C1092" t="str">
-        <v>2026-08-01 21:42:25</v>
+        <v>2026-08-01 21:11:24</v>
       </c>
       <c r="D1092" t="str">
         <v>SI</v>
@@ -15696,7 +15696,7 @@
         <v>6582</v>
       </c>
       <c r="C1093" t="str">
-        <v>2026-08-01 21:49:58</v>
+        <v>2026-08-01 21:42:25</v>
       </c>
       <c r="D1093" t="str">
         <v>SI</v>
@@ -15710,7 +15710,7 @@
         <v>6582</v>
       </c>
       <c r="C1094" t="str">
-        <v>2026-08-01 22:07:56</v>
+        <v>2026-08-01 21:49:58</v>
       </c>
       <c r="D1094" t="str">
         <v>SI</v>
@@ -15724,7 +15724,7 @@
         <v>6582</v>
       </c>
       <c r="C1095" t="str">
-        <v>2026-08-02 03:58:03</v>
+        <v>2026-08-01 22:07:56</v>
       </c>
       <c r="D1095" t="str">
         <v>SI</v>
@@ -15738,7 +15738,7 @@
         <v>6582</v>
       </c>
       <c r="C1096" t="str">
-        <v>2026-08-02 17:56:32</v>
+        <v>2026-08-02 03:58:03</v>
       </c>
       <c r="D1096" t="str">
         <v>SI</v>
@@ -15752,7 +15752,7 @@
         <v>6582</v>
       </c>
       <c r="C1097" t="str">
-        <v>2026-08-02 19:44:18</v>
+        <v>2026-08-02 17:56:32</v>
       </c>
       <c r="D1097" t="str">
         <v>SI</v>
@@ -15766,7 +15766,7 @@
         <v>6582</v>
       </c>
       <c r="C1098" t="str">
-        <v>2026-08-02 19:56:02</v>
+        <v>2026-08-02 19:44:18</v>
       </c>
       <c r="D1098" t="str">
         <v>SI</v>
@@ -15774,16 +15774,16 @@
     </row>
     <row r="1099">
       <c r="A1099" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B1099">
-        <v>6589</v>
+        <v>6582</v>
       </c>
       <c r="C1099" t="str">
-        <v>2026-07-27 10:26:43</v>
+        <v>2026-08-02 19:56:02</v>
       </c>
       <c r="D1099" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1100">
@@ -15794,7 +15794,7 @@
         <v>6589</v>
       </c>
       <c r="C1100" t="str">
-        <v>2026-07-27 12:43:49</v>
+        <v>2026-07-27 10:26:43</v>
       </c>
       <c r="D1100" t="str">
         <v>NO</v>
@@ -15808,7 +15808,7 @@
         <v>6589</v>
       </c>
       <c r="C1101" t="str">
-        <v>2026-07-27 13:00:17</v>
+        <v>2026-07-27 12:43:49</v>
       </c>
       <c r="D1101" t="str">
         <v>NO</v>
@@ -15822,7 +15822,7 @@
         <v>6589</v>
       </c>
       <c r="C1102" t="str">
-        <v>2026-07-27 13:02:19</v>
+        <v>2026-07-27 13:00:17</v>
       </c>
       <c r="D1102" t="str">
         <v>NO</v>
@@ -15836,7 +15836,7 @@
         <v>6589</v>
       </c>
       <c r="C1103" t="str">
-        <v>2026-07-27 13:47:45</v>
+        <v>2026-07-27 13:02:19</v>
       </c>
       <c r="D1103" t="str">
         <v>NO</v>
@@ -15850,7 +15850,7 @@
         <v>6589</v>
       </c>
       <c r="C1104" t="str">
-        <v>2026-07-27 14:32:45</v>
+        <v>2026-07-27 13:47:45</v>
       </c>
       <c r="D1104" t="str">
         <v>NO</v>
@@ -15864,7 +15864,7 @@
         <v>6589</v>
       </c>
       <c r="C1105" t="str">
-        <v>2026-07-27 14:34:19</v>
+        <v>2026-07-27 14:32:45</v>
       </c>
       <c r="D1105" t="str">
         <v>NO</v>
@@ -15878,7 +15878,7 @@
         <v>6589</v>
       </c>
       <c r="C1106" t="str">
-        <v>2026-07-27 14:39:29</v>
+        <v>2026-07-27 14:34:19</v>
       </c>
       <c r="D1106" t="str">
         <v>NO</v>
@@ -15892,7 +15892,7 @@
         <v>6589</v>
       </c>
       <c r="C1107" t="str">
-        <v>2026-07-27 14:44:31</v>
+        <v>2026-07-27 14:39:29</v>
       </c>
       <c r="D1107" t="str">
         <v>NO</v>
@@ -15906,7 +15906,7 @@
         <v>6589</v>
       </c>
       <c r="C1108" t="str">
-        <v>2026-07-27 14:47:30</v>
+        <v>2026-07-27 14:44:31</v>
       </c>
       <c r="D1108" t="str">
         <v>NO</v>
@@ -15920,7 +15920,7 @@
         <v>6589</v>
       </c>
       <c r="C1109" t="str">
-        <v>2026-07-27 15:44:58</v>
+        <v>2026-07-27 14:47:30</v>
       </c>
       <c r="D1109" t="str">
         <v>NO</v>
@@ -15934,7 +15934,7 @@
         <v>6589</v>
       </c>
       <c r="C1110" t="str">
-        <v>2026-07-27 16:51:32</v>
+        <v>2026-07-27 15:44:58</v>
       </c>
       <c r="D1110" t="str">
         <v>NO</v>
@@ -15948,7 +15948,7 @@
         <v>6589</v>
       </c>
       <c r="C1111" t="str">
-        <v>2026-07-27 17:06:21</v>
+        <v>2026-07-27 16:51:32</v>
       </c>
       <c r="D1111" t="str">
         <v>NO</v>
@@ -15962,7 +15962,7 @@
         <v>6589</v>
       </c>
       <c r="C1112" t="str">
-        <v>2026-07-27 17:47:39</v>
+        <v>2026-07-27 17:06:21</v>
       </c>
       <c r="D1112" t="str">
         <v>NO</v>
@@ -15976,7 +15976,7 @@
         <v>6589</v>
       </c>
       <c r="C1113" t="str">
-        <v>2026-07-27 18:27:55</v>
+        <v>2026-07-27 17:47:39</v>
       </c>
       <c r="D1113" t="str">
         <v>NO</v>
@@ -15990,7 +15990,7 @@
         <v>6589</v>
       </c>
       <c r="C1114" t="str">
-        <v>2026-07-27 18:35:55</v>
+        <v>2026-07-27 18:27:55</v>
       </c>
       <c r="D1114" t="str">
         <v>NO</v>
@@ -16004,7 +16004,7 @@
         <v>6589</v>
       </c>
       <c r="C1115" t="str">
-        <v>2026-07-27 18:37:29</v>
+        <v>2026-07-27 18:35:55</v>
       </c>
       <c r="D1115" t="str">
         <v>NO</v>
@@ -16018,10 +16018,10 @@
         <v>6589</v>
       </c>
       <c r="C1116" t="str">
-        <v>2026-07-27 19:10:01</v>
+        <v>2026-07-27 18:37:29</v>
       </c>
       <c r="D1116" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1117">
@@ -16032,7 +16032,7 @@
         <v>6589</v>
       </c>
       <c r="C1117" t="str">
-        <v>2026-07-27 19:35:23</v>
+        <v>2026-07-27 19:10:01</v>
       </c>
       <c r="D1117" t="str">
         <v>SI</v>
@@ -16046,7 +16046,7 @@
         <v>6589</v>
       </c>
       <c r="C1118" t="str">
-        <v>2026-07-27 19:43:39</v>
+        <v>2026-07-27 19:35:23</v>
       </c>
       <c r="D1118" t="str">
         <v>SI</v>
@@ -16060,7 +16060,7 @@
         <v>6589</v>
       </c>
       <c r="C1119" t="str">
-        <v>2026-07-27 20:15:23</v>
+        <v>2026-07-27 19:43:39</v>
       </c>
       <c r="D1119" t="str">
         <v>SI</v>
@@ -16074,10 +16074,10 @@
         <v>6589</v>
       </c>
       <c r="C1120" t="str">
-        <v>2026-07-28 10:24:50</v>
+        <v>2026-07-27 20:15:23</v>
       </c>
       <c r="D1120" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1121">
@@ -16088,7 +16088,7 @@
         <v>6589</v>
       </c>
       <c r="C1121" t="str">
-        <v>2026-07-28 12:38:29</v>
+        <v>2026-07-28 10:24:50</v>
       </c>
       <c r="D1121" t="str">
         <v>NO</v>
@@ -16102,7 +16102,7 @@
         <v>6589</v>
       </c>
       <c r="C1122" t="str">
-        <v>2026-07-28 15:14:33</v>
+        <v>2026-07-28 12:38:29</v>
       </c>
       <c r="D1122" t="str">
         <v>NO</v>
@@ -16116,7 +16116,7 @@
         <v>6589</v>
       </c>
       <c r="C1123" t="str">
-        <v>2026-07-28 15:31:51</v>
+        <v>2026-07-28 15:14:33</v>
       </c>
       <c r="D1123" t="str">
         <v>NO</v>
@@ -16130,7 +16130,7 @@
         <v>6589</v>
       </c>
       <c r="C1124" t="str">
-        <v>2026-07-28 16:19:01</v>
+        <v>2026-07-28 15:31:51</v>
       </c>
       <c r="D1124" t="str">
         <v>NO</v>
@@ -16144,7 +16144,7 @@
         <v>6589</v>
       </c>
       <c r="C1125" t="str">
-        <v>2026-07-28 16:24:11</v>
+        <v>2026-07-28 16:19:01</v>
       </c>
       <c r="D1125" t="str">
         <v>NO</v>
@@ -16158,7 +16158,7 @@
         <v>6589</v>
       </c>
       <c r="C1126" t="str">
-        <v>2026-07-28 17:10:02</v>
+        <v>2026-07-28 16:24:11</v>
       </c>
       <c r="D1126" t="str">
         <v>NO</v>
@@ -16172,7 +16172,7 @@
         <v>6589</v>
       </c>
       <c r="C1127" t="str">
-        <v>2026-07-28 17:20:08</v>
+        <v>2026-07-28 17:10:02</v>
       </c>
       <c r="D1127" t="str">
         <v>NO</v>
@@ -16186,10 +16186,10 @@
         <v>6589</v>
       </c>
       <c r="C1128" t="str">
-        <v>2026-07-28 21:01:06</v>
+        <v>2026-07-28 17:20:08</v>
       </c>
       <c r="D1128" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1129">
@@ -16200,7 +16200,7 @@
         <v>6589</v>
       </c>
       <c r="C1129" t="str">
-        <v>2026-07-28 21:03:51</v>
+        <v>2026-07-28 21:01:06</v>
       </c>
       <c r="D1129" t="str">
         <v>SI</v>
@@ -16214,7 +16214,7 @@
         <v>6589</v>
       </c>
       <c r="C1130" t="str">
-        <v>2026-07-28 22:16:42</v>
+        <v>2026-07-28 21:03:51</v>
       </c>
       <c r="D1130" t="str">
         <v>SI</v>
@@ -16228,7 +16228,7 @@
         <v>6589</v>
       </c>
       <c r="C1131" t="str">
-        <v>2026-07-28 23:30:04</v>
+        <v>2026-07-28 22:16:42</v>
       </c>
       <c r="D1131" t="str">
         <v>SI</v>
@@ -16242,7 +16242,7 @@
         <v>6589</v>
       </c>
       <c r="C1132" t="str">
-        <v>2026-07-29 01:15:41</v>
+        <v>2026-07-28 23:30:04</v>
       </c>
       <c r="D1132" t="str">
         <v>SI</v>
@@ -16256,7 +16256,7 @@
         <v>6589</v>
       </c>
       <c r="C1133" t="str">
-        <v>2026-07-29 01:37:45</v>
+        <v>2026-07-29 01:15:41</v>
       </c>
       <c r="D1133" t="str">
         <v>SI</v>
@@ -16270,7 +16270,7 @@
         <v>6589</v>
       </c>
       <c r="C1134" t="str">
-        <v>2026-07-29 03:38:11</v>
+        <v>2026-07-29 01:37:45</v>
       </c>
       <c r="D1134" t="str">
         <v>SI</v>
@@ -16284,10 +16284,10 @@
         <v>6589</v>
       </c>
       <c r="C1135" t="str">
-        <v>2026-07-29 10:07:11</v>
+        <v>2026-07-29 03:38:11</v>
       </c>
       <c r="D1135" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1136">
@@ -16298,7 +16298,7 @@
         <v>6589</v>
       </c>
       <c r="C1136" t="str">
-        <v>2026-07-29 11:32:51</v>
+        <v>2026-07-29 10:07:11</v>
       </c>
       <c r="D1136" t="str">
         <v>NO</v>
@@ -16312,7 +16312,7 @@
         <v>6589</v>
       </c>
       <c r="C1137" t="str">
-        <v>2026-07-29 12:44:54</v>
+        <v>2026-07-29 11:32:51</v>
       </c>
       <c r="D1137" t="str">
         <v>NO</v>
@@ -16326,7 +16326,7 @@
         <v>6589</v>
       </c>
       <c r="C1138" t="str">
-        <v>2026-07-29 13:09:42</v>
+        <v>2026-07-29 12:44:54</v>
       </c>
       <c r="D1138" t="str">
         <v>NO</v>
@@ -16340,7 +16340,7 @@
         <v>6589</v>
       </c>
       <c r="C1139" t="str">
-        <v>2026-07-29 14:15:25</v>
+        <v>2026-07-29 13:09:42</v>
       </c>
       <c r="D1139" t="str">
         <v>NO</v>
@@ -16354,7 +16354,7 @@
         <v>6589</v>
       </c>
       <c r="C1140" t="str">
-        <v>2026-07-29 14:35:45</v>
+        <v>2026-07-29 14:15:25</v>
       </c>
       <c r="D1140" t="str">
         <v>NO</v>
@@ -16368,7 +16368,7 @@
         <v>6589</v>
       </c>
       <c r="C1141" t="str">
-        <v>2026-07-29 16:44:27</v>
+        <v>2026-07-29 14:35:45</v>
       </c>
       <c r="D1141" t="str">
         <v>NO</v>
@@ -16382,7 +16382,7 @@
         <v>6589</v>
       </c>
       <c r="C1142" t="str">
-        <v>2026-07-29 16:55:10</v>
+        <v>2026-07-29 16:44:27</v>
       </c>
       <c r="D1142" t="str">
         <v>NO</v>
@@ -16396,7 +16396,7 @@
         <v>6589</v>
       </c>
       <c r="C1143" t="str">
-        <v>2026-07-29 18:07:02</v>
+        <v>2026-07-29 16:55:10</v>
       </c>
       <c r="D1143" t="str">
         <v>NO</v>
@@ -16410,10 +16410,10 @@
         <v>6589</v>
       </c>
       <c r="C1144" t="str">
-        <v>2026-07-29 20:51:50</v>
+        <v>2026-07-29 18:07:02</v>
       </c>
       <c r="D1144" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1145">
@@ -16424,7 +16424,7 @@
         <v>6589</v>
       </c>
       <c r="C1145" t="str">
-        <v>2026-07-29 21:01:56</v>
+        <v>2026-07-29 20:51:50</v>
       </c>
       <c r="D1145" t="str">
         <v>SI</v>
@@ -16438,10 +16438,10 @@
         <v>6589</v>
       </c>
       <c r="C1146" t="str">
-        <v>2026-07-30 10:23:07</v>
+        <v>2026-07-29 21:01:56</v>
       </c>
       <c r="D1146" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1147">
@@ -16452,7 +16452,7 @@
         <v>6589</v>
       </c>
       <c r="C1147" t="str">
-        <v>2026-07-30 14:22:07</v>
+        <v>2026-07-30 10:23:07</v>
       </c>
       <c r="D1147" t="str">
         <v>NO</v>
@@ -16466,7 +16466,7 @@
         <v>6589</v>
       </c>
       <c r="C1148" t="str">
-        <v>2026-07-30 17:32:30</v>
+        <v>2026-07-30 14:22:07</v>
       </c>
       <c r="D1148" t="str">
         <v>NO</v>
@@ -16480,7 +16480,7 @@
         <v>6589</v>
       </c>
       <c r="C1149" t="str">
-        <v>2026-07-30 18:21:58</v>
+        <v>2026-07-30 17:32:30</v>
       </c>
       <c r="D1149" t="str">
         <v>NO</v>
@@ -16494,10 +16494,10 @@
         <v>6589</v>
       </c>
       <c r="C1150" t="str">
-        <v>2026-07-30 21:26:02</v>
+        <v>2026-07-30 18:21:58</v>
       </c>
       <c r="D1150" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1151">
@@ -16508,7 +16508,7 @@
         <v>6589</v>
       </c>
       <c r="C1151" t="str">
-        <v>2026-07-30 21:58:44</v>
+        <v>2026-07-30 21:26:02</v>
       </c>
       <c r="D1151" t="str">
         <v>SI</v>
@@ -16522,7 +16522,7 @@
         <v>6589</v>
       </c>
       <c r="C1152" t="str">
-        <v>2026-07-30 22:26:38</v>
+        <v>2026-07-30 21:58:44</v>
       </c>
       <c r="D1152" t="str">
         <v>SI</v>
@@ -16536,10 +16536,10 @@
         <v>6589</v>
       </c>
       <c r="C1153" t="str">
-        <v>2026-07-31 10:40:30</v>
+        <v>2026-07-30 22:26:38</v>
       </c>
       <c r="D1153" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1154">
@@ -16550,7 +16550,7 @@
         <v>6589</v>
       </c>
       <c r="C1154" t="str">
-        <v>2026-07-31 12:53:34</v>
+        <v>2026-07-31 10:40:30</v>
       </c>
       <c r="D1154" t="str">
         <v>NO</v>
@@ -16564,7 +16564,7 @@
         <v>6589</v>
       </c>
       <c r="C1155" t="str">
-        <v>2026-07-31 13:59:08</v>
+        <v>2026-07-31 12:53:34</v>
       </c>
       <c r="D1155" t="str">
         <v>NO</v>
@@ -16578,7 +16578,7 @@
         <v>6589</v>
       </c>
       <c r="C1156" t="str">
-        <v>2026-07-31 14:17:34</v>
+        <v>2026-07-31 13:59:08</v>
       </c>
       <c r="D1156" t="str">
         <v>NO</v>
@@ -16592,7 +16592,7 @@
         <v>6589</v>
       </c>
       <c r="C1157" t="str">
-        <v>2026-07-31 15:58:04</v>
+        <v>2026-07-31 14:17:34</v>
       </c>
       <c r="D1157" t="str">
         <v>NO</v>
@@ -16606,7 +16606,7 @@
         <v>6589</v>
       </c>
       <c r="C1158" t="str">
-        <v>2026-07-31 16:07:34</v>
+        <v>2026-07-31 15:58:04</v>
       </c>
       <c r="D1158" t="str">
         <v>NO</v>
@@ -16620,7 +16620,7 @@
         <v>6589</v>
       </c>
       <c r="C1159" t="str">
-        <v>2026-07-31 16:49:09</v>
+        <v>2026-07-31 16:07:34</v>
       </c>
       <c r="D1159" t="str">
         <v>NO</v>
@@ -16628,13 +16628,13 @@
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B1160">
-        <v>6596</v>
+        <v>6589</v>
       </c>
       <c r="C1160" t="str">
-        <v>2026-07-27 10:15:01</v>
+        <v>2026-07-31 16:49:09</v>
       </c>
       <c r="D1160" t="str">
         <v>NO</v>
@@ -16648,7 +16648,7 @@
         <v>6596</v>
       </c>
       <c r="C1161" t="str">
-        <v>2026-07-27 10:17:45</v>
+        <v>2026-07-27 10:15:01</v>
       </c>
       <c r="D1161" t="str">
         <v>NO</v>
@@ -16662,7 +16662,7 @@
         <v>6596</v>
       </c>
       <c r="C1162" t="str">
-        <v>2026-07-27 10:25:07</v>
+        <v>2026-07-27 10:17:45</v>
       </c>
       <c r="D1162" t="str">
         <v>NO</v>
@@ -16676,7 +16676,7 @@
         <v>6596</v>
       </c>
       <c r="C1163" t="str">
-        <v>2026-07-27 10:40:21</v>
+        <v>2026-07-27 10:25:07</v>
       </c>
       <c r="D1163" t="str">
         <v>NO</v>
@@ -16690,7 +16690,7 @@
         <v>6596</v>
       </c>
       <c r="C1164" t="str">
-        <v>2026-07-27 11:34:31</v>
+        <v>2026-07-27 10:40:21</v>
       </c>
       <c r="D1164" t="str">
         <v>NO</v>
@@ -16704,7 +16704,7 @@
         <v>6596</v>
       </c>
       <c r="C1165" t="str">
-        <v>2026-07-27 12:32:51</v>
+        <v>2026-07-27 11:34:31</v>
       </c>
       <c r="D1165" t="str">
         <v>NO</v>
@@ -16718,10 +16718,10 @@
         <v>6596</v>
       </c>
       <c r="C1166" t="str">
-        <v>2026-07-27 21:23:51</v>
+        <v>2026-07-27 12:32:51</v>
       </c>
       <c r="D1166" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1167">
@@ -16732,7 +16732,7 @@
         <v>6596</v>
       </c>
       <c r="C1167" t="str">
-        <v>2026-07-27 22:45:40</v>
+        <v>2026-07-27 21:23:51</v>
       </c>
       <c r="D1167" t="str">
         <v>SI</v>
@@ -16746,7 +16746,7 @@
         <v>6596</v>
       </c>
       <c r="C1168" t="str">
-        <v>2026-07-27 23:20:32</v>
+        <v>2026-07-27 22:45:40</v>
       </c>
       <c r="D1168" t="str">
         <v>SI</v>
@@ -16760,7 +16760,7 @@
         <v>6596</v>
       </c>
       <c r="C1169" t="str">
-        <v>2026-07-28 00:43:18</v>
+        <v>2026-07-27 23:20:32</v>
       </c>
       <c r="D1169" t="str">
         <v>SI</v>
@@ -16774,7 +16774,7 @@
         <v>6596</v>
       </c>
       <c r="C1170" t="str">
-        <v>2026-07-28 02:10:01</v>
+        <v>2026-07-28 00:43:18</v>
       </c>
       <c r="D1170" t="str">
         <v>SI</v>
@@ -16788,7 +16788,7 @@
         <v>6596</v>
       </c>
       <c r="C1171" t="str">
-        <v>2026-07-28 02:22:31</v>
+        <v>2026-07-28 02:10:01</v>
       </c>
       <c r="D1171" t="str">
         <v>SI</v>
@@ -16802,7 +16802,7 @@
         <v>6596</v>
       </c>
       <c r="C1172" t="str">
-        <v>2026-07-28 04:39:51</v>
+        <v>2026-07-28 02:22:31</v>
       </c>
       <c r="D1172" t="str">
         <v>SI</v>
@@ -16816,10 +16816,10 @@
         <v>6596</v>
       </c>
       <c r="C1173" t="str">
-        <v>2026-07-28 09:35:18</v>
+        <v>2026-07-28 04:39:51</v>
       </c>
       <c r="D1173" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1174">
@@ -16830,7 +16830,7 @@
         <v>6596</v>
       </c>
       <c r="C1174" t="str">
-        <v>2026-07-28 11:14:15</v>
+        <v>2026-07-28 09:35:18</v>
       </c>
       <c r="D1174" t="str">
         <v>NO</v>
@@ -16844,7 +16844,7 @@
         <v>6596</v>
       </c>
       <c r="C1175" t="str">
-        <v>2026-07-28 12:01:33</v>
+        <v>2026-07-28 11:14:15</v>
       </c>
       <c r="D1175" t="str">
         <v>NO</v>
@@ -16858,7 +16858,7 @@
         <v>6596</v>
       </c>
       <c r="C1176" t="str">
-        <v>2026-07-28 12:35:35</v>
+        <v>2026-07-28 12:01:33</v>
       </c>
       <c r="D1176" t="str">
         <v>NO</v>
@@ -16872,7 +16872,7 @@
         <v>6596</v>
       </c>
       <c r="C1177" t="str">
-        <v>2026-07-28 13:19:57</v>
+        <v>2026-07-28 12:35:35</v>
       </c>
       <c r="D1177" t="str">
         <v>NO</v>
@@ -16886,7 +16886,7 @@
         <v>6596</v>
       </c>
       <c r="C1178" t="str">
-        <v>2026-07-28 15:07:11</v>
+        <v>2026-07-28 13:19:57</v>
       </c>
       <c r="D1178" t="str">
         <v>NO</v>
@@ -16900,7 +16900,7 @@
         <v>6596</v>
       </c>
       <c r="C1179" t="str">
-        <v>2026-07-28 15:38:11</v>
+        <v>2026-07-28 15:07:11</v>
       </c>
       <c r="D1179" t="str">
         <v>NO</v>
@@ -16914,7 +16914,7 @@
         <v>6596</v>
       </c>
       <c r="C1180" t="str">
-        <v>2026-07-28 16:32:03</v>
+        <v>2026-07-28 15:38:11</v>
       </c>
       <c r="D1180" t="str">
         <v>NO</v>
@@ -16928,7 +16928,7 @@
         <v>6596</v>
       </c>
       <c r="C1181" t="str">
-        <v>2026-07-28 17:45:05</v>
+        <v>2026-07-28 16:32:03</v>
       </c>
       <c r="D1181" t="str">
         <v>NO</v>
@@ -16942,7 +16942,7 @@
         <v>6596</v>
       </c>
       <c r="C1182" t="str">
-        <v>2026-07-28 18:14:23</v>
+        <v>2026-07-28 17:45:05</v>
       </c>
       <c r="D1182" t="str">
         <v>NO</v>
@@ -16956,10 +16956,10 @@
         <v>6596</v>
       </c>
       <c r="C1183" t="str">
-        <v>2026-07-28 21:56:03</v>
+        <v>2026-07-28 18:14:23</v>
       </c>
       <c r="D1183" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1184">
@@ -16970,7 +16970,7 @@
         <v>6596</v>
       </c>
       <c r="C1184" t="str">
-        <v>2026-07-28 22:53:08</v>
+        <v>2026-07-28 21:56:03</v>
       </c>
       <c r="D1184" t="str">
         <v>SI</v>
@@ -16984,10 +16984,10 @@
         <v>6596</v>
       </c>
       <c r="C1185" t="str">
-        <v>2026-07-29 10:55:50</v>
+        <v>2026-07-28 22:53:08</v>
       </c>
       <c r="D1185" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1186">
@@ -16998,7 +16998,7 @@
         <v>6596</v>
       </c>
       <c r="C1186" t="str">
-        <v>2026-07-29 11:12:06</v>
+        <v>2026-07-29 10:55:50</v>
       </c>
       <c r="D1186" t="str">
         <v>NO</v>
@@ -17012,7 +17012,7 @@
         <v>6596</v>
       </c>
       <c r="C1187" t="str">
-        <v>2026-07-29 11:32:32</v>
+        <v>2026-07-29 11:12:06</v>
       </c>
       <c r="D1187" t="str">
         <v>NO</v>
@@ -17026,7 +17026,7 @@
         <v>6596</v>
       </c>
       <c r="C1188" t="str">
-        <v>2026-07-29 11:54:58</v>
+        <v>2026-07-29 11:32:32</v>
       </c>
       <c r="D1188" t="str">
         <v>NO</v>
@@ -17040,7 +17040,7 @@
         <v>6596</v>
       </c>
       <c r="C1189" t="str">
-        <v>2026-07-29 13:03:05</v>
+        <v>2026-07-29 11:54:58</v>
       </c>
       <c r="D1189" t="str">
         <v>NO</v>
@@ -17054,7 +17054,7 @@
         <v>6596</v>
       </c>
       <c r="C1190" t="str">
-        <v>2026-07-29 14:11:50</v>
+        <v>2026-07-29 13:03:05</v>
       </c>
       <c r="D1190" t="str">
         <v>NO</v>
@@ -17068,7 +17068,7 @@
         <v>6596</v>
       </c>
       <c r="C1191" t="str">
-        <v>2026-07-29 16:01:16</v>
+        <v>2026-07-29 14:11:50</v>
       </c>
       <c r="D1191" t="str">
         <v>NO</v>
@@ -17082,7 +17082,7 @@
         <v>6596</v>
       </c>
       <c r="C1192" t="str">
-        <v>2026-07-29 16:01:59</v>
+        <v>2026-07-29 16:01:16</v>
       </c>
       <c r="D1192" t="str">
         <v>NO</v>
@@ -17096,7 +17096,7 @@
         <v>6596</v>
       </c>
       <c r="C1193" t="str">
-        <v>2026-07-29 16:10:39</v>
+        <v>2026-07-29 16:01:59</v>
       </c>
       <c r="D1193" t="str">
         <v>NO</v>
@@ -17110,10 +17110,10 @@
         <v>6596</v>
       </c>
       <c r="C1194" t="str">
-        <v>2026-07-29 19:51:54</v>
+        <v>2026-07-29 16:10:39</v>
       </c>
       <c r="D1194" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1195">
@@ -17124,7 +17124,7 @@
         <v>6596</v>
       </c>
       <c r="C1195" t="str">
-        <v>2026-07-29 19:58:02</v>
+        <v>2026-07-29 19:51:54</v>
       </c>
       <c r="D1195" t="str">
         <v>SI</v>
@@ -17138,7 +17138,7 @@
         <v>6596</v>
       </c>
       <c r="C1196" t="str">
-        <v>2026-07-29 20:07:37</v>
+        <v>2026-07-29 19:58:02</v>
       </c>
       <c r="D1196" t="str">
         <v>SI</v>
@@ -17152,7 +17152,7 @@
         <v>6596</v>
       </c>
       <c r="C1197" t="str">
-        <v>2026-07-29 22:57:55</v>
+        <v>2026-07-29 20:07:37</v>
       </c>
       <c r="D1197" t="str">
         <v>SI</v>
@@ -17166,7 +17166,7 @@
         <v>6596</v>
       </c>
       <c r="C1198" t="str">
-        <v>2026-07-29 23:24:59</v>
+        <v>2026-07-29 22:57:55</v>
       </c>
       <c r="D1198" t="str">
         <v>SI</v>
@@ -17180,7 +17180,7 @@
         <v>6596</v>
       </c>
       <c r="C1199" t="str">
-        <v>2026-07-30 02:02:26</v>
+        <v>2026-07-29 23:24:59</v>
       </c>
       <c r="D1199" t="str">
         <v>SI</v>
@@ -17194,7 +17194,7 @@
         <v>6596</v>
       </c>
       <c r="C1200" t="str">
-        <v>2026-07-30 02:08:17</v>
+        <v>2026-07-30 02:02:26</v>
       </c>
       <c r="D1200" t="str">
         <v>SI</v>
@@ -17208,7 +17208,7 @@
         <v>6596</v>
       </c>
       <c r="C1201" t="str">
-        <v>2026-07-30 02:40:44</v>
+        <v>2026-07-30 02:08:17</v>
       </c>
       <c r="D1201" t="str">
         <v>SI</v>
@@ -17222,7 +17222,7 @@
         <v>6596</v>
       </c>
       <c r="C1202" t="str">
-        <v>2026-07-30 03:30:44</v>
+        <v>2026-07-30 02:40:44</v>
       </c>
       <c r="D1202" t="str">
         <v>SI</v>
@@ -17236,7 +17236,7 @@
         <v>6596</v>
       </c>
       <c r="C1203" t="str">
-        <v>2026-07-30 04:07:12</v>
+        <v>2026-07-30 03:30:44</v>
       </c>
       <c r="D1203" t="str">
         <v>SI</v>
@@ -17250,7 +17250,7 @@
         <v>6596</v>
       </c>
       <c r="C1204" t="str">
-        <v>2026-07-30 04:18:54</v>
+        <v>2026-07-30 04:07:12</v>
       </c>
       <c r="D1204" t="str">
         <v>SI</v>
@@ -17264,7 +17264,7 @@
         <v>6596</v>
       </c>
       <c r="C1205" t="str">
-        <v>2026-07-30 05:02:04</v>
+        <v>2026-07-30 04:18:54</v>
       </c>
       <c r="D1205" t="str">
         <v>SI</v>
@@ -17278,10 +17278,10 @@
         <v>6596</v>
       </c>
       <c r="C1206" t="str">
-        <v>2026-07-30 09:49:39</v>
+        <v>2026-07-30 05:02:04</v>
       </c>
       <c r="D1206" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1207">
@@ -17292,7 +17292,7 @@
         <v>6596</v>
       </c>
       <c r="C1207" t="str">
-        <v>2026-07-30 10:22:47</v>
+        <v>2026-07-30 09:49:39</v>
       </c>
       <c r="D1207" t="str">
         <v>NO</v>
@@ -17306,7 +17306,7 @@
         <v>6596</v>
       </c>
       <c r="C1208" t="str">
-        <v>2026-07-30 11:54:25</v>
+        <v>2026-07-30 10:22:47</v>
       </c>
       <c r="D1208" t="str">
         <v>NO</v>
@@ -17320,7 +17320,7 @@
         <v>6596</v>
       </c>
       <c r="C1209" t="str">
-        <v>2026-07-30 13:14:55</v>
+        <v>2026-07-30 11:54:25</v>
       </c>
       <c r="D1209" t="str">
         <v>NO</v>
@@ -17334,7 +17334,7 @@
         <v>6596</v>
       </c>
       <c r="C1210" t="str">
-        <v>2026-07-30 14:16:39</v>
+        <v>2026-07-30 13:14:55</v>
       </c>
       <c r="D1210" t="str">
         <v>NO</v>
@@ -17348,7 +17348,7 @@
         <v>6596</v>
       </c>
       <c r="C1211" t="str">
-        <v>2026-07-30 18:00:47</v>
+        <v>2026-07-30 14:16:39</v>
       </c>
       <c r="D1211" t="str">
         <v>NO</v>
@@ -17362,7 +17362,7 @@
         <v>6596</v>
       </c>
       <c r="C1212" t="str">
-        <v>2026-07-30 18:33:03</v>
+        <v>2026-07-30 18:00:47</v>
       </c>
       <c r="D1212" t="str">
         <v>NO</v>
@@ -17376,7 +17376,7 @@
         <v>6596</v>
       </c>
       <c r="C1213" t="str">
-        <v>2026-07-30 18:57:51</v>
+        <v>2026-07-30 18:33:03</v>
       </c>
       <c r="D1213" t="str">
         <v>NO</v>
@@ -17390,10 +17390,10 @@
         <v>6596</v>
       </c>
       <c r="C1214" t="str">
-        <v>2026-07-30 19:14:45</v>
+        <v>2026-07-30 18:57:51</v>
       </c>
       <c r="D1214" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1215">
@@ -17404,7 +17404,7 @@
         <v>6596</v>
       </c>
       <c r="C1215" t="str">
-        <v>2026-07-30 19:26:56</v>
+        <v>2026-07-30 19:14:45</v>
       </c>
       <c r="D1215" t="str">
         <v>SI</v>
@@ -17418,7 +17418,7 @@
         <v>6596</v>
       </c>
       <c r="C1216" t="str">
-        <v>2026-07-30 19:37:21</v>
+        <v>2026-07-30 19:26:56</v>
       </c>
       <c r="D1216" t="str">
         <v>SI</v>
@@ -17432,7 +17432,7 @@
         <v>6596</v>
       </c>
       <c r="C1217" t="str">
-        <v>2026-07-30 19:42:02</v>
+        <v>2026-07-30 19:37:21</v>
       </c>
       <c r="D1217" t="str">
         <v>SI</v>
@@ -17446,7 +17446,7 @@
         <v>6596</v>
       </c>
       <c r="C1218" t="str">
-        <v>2026-07-30 19:51:51</v>
+        <v>2026-07-30 19:42:02</v>
       </c>
       <c r="D1218" t="str">
         <v>SI</v>
@@ -17460,7 +17460,7 @@
         <v>6596</v>
       </c>
       <c r="C1219" t="str">
-        <v>2026-07-31 01:24:05</v>
+        <v>2026-07-30 19:51:51</v>
       </c>
       <c r="D1219" t="str">
         <v>SI</v>
@@ -17474,7 +17474,7 @@
         <v>6596</v>
       </c>
       <c r="C1220" t="str">
-        <v>2026-07-31 04:35:27</v>
+        <v>2026-07-31 01:24:05</v>
       </c>
       <c r="D1220" t="str">
         <v>SI</v>
@@ -17488,7 +17488,7 @@
         <v>6596</v>
       </c>
       <c r="C1221" t="str">
-        <v>2026-07-31 04:57:39</v>
+        <v>2026-07-31 04:35:27</v>
       </c>
       <c r="D1221" t="str">
         <v>SI</v>
@@ -17502,7 +17502,7 @@
         <v>6596</v>
       </c>
       <c r="C1222" t="str">
-        <v>2026-07-31 06:08:25</v>
+        <v>2026-07-31 04:57:39</v>
       </c>
       <c r="D1222" t="str">
         <v>SI</v>
@@ -17516,10 +17516,10 @@
         <v>6596</v>
       </c>
       <c r="C1223" t="str">
-        <v>2026-07-31 07:23:39</v>
+        <v>2026-07-31 06:08:25</v>
       </c>
       <c r="D1223" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1224">
@@ -17530,7 +17530,7 @@
         <v>6596</v>
       </c>
       <c r="C1224" t="str">
-        <v>2026-07-31 09:16:04</v>
+        <v>2026-07-31 07:23:39</v>
       </c>
       <c r="D1224" t="str">
         <v>NO</v>
@@ -17544,7 +17544,7 @@
         <v>6596</v>
       </c>
       <c r="C1225" t="str">
-        <v>2026-07-31 10:04:54</v>
+        <v>2026-07-31 09:16:04</v>
       </c>
       <c r="D1225" t="str">
         <v>NO</v>
@@ -17558,7 +17558,7 @@
         <v>6596</v>
       </c>
       <c r="C1226" t="str">
-        <v>2026-07-31 10:38:12</v>
+        <v>2026-07-31 10:04:54</v>
       </c>
       <c r="D1226" t="str">
         <v>NO</v>
@@ -17572,7 +17572,7 @@
         <v>6596</v>
       </c>
       <c r="C1227" t="str">
-        <v>2026-07-31 10:52:16</v>
+        <v>2026-07-31 10:38:12</v>
       </c>
       <c r="D1227" t="str">
         <v>NO</v>
@@ -17586,7 +17586,7 @@
         <v>6596</v>
       </c>
       <c r="C1228" t="str">
-        <v>2026-07-31 14:02:12</v>
+        <v>2026-07-31 10:52:16</v>
       </c>
       <c r="D1228" t="str">
         <v>NO</v>
@@ -17600,7 +17600,7 @@
         <v>6596</v>
       </c>
       <c r="C1229" t="str">
-        <v>2026-07-31 14:03:14</v>
+        <v>2026-07-31 14:02:12</v>
       </c>
       <c r="D1229" t="str">
         <v>NO</v>
@@ -17614,7 +17614,7 @@
         <v>6596</v>
       </c>
       <c r="C1230" t="str">
-        <v>2026-07-31 15:42:49</v>
+        <v>2026-07-31 14:03:14</v>
       </c>
       <c r="D1230" t="str">
         <v>NO</v>
@@ -17628,7 +17628,7 @@
         <v>6596</v>
       </c>
       <c r="C1231" t="str">
-        <v>2026-07-31 16:13:01</v>
+        <v>2026-07-31 15:42:49</v>
       </c>
       <c r="D1231" t="str">
         <v>NO</v>
@@ -17642,7 +17642,7 @@
         <v>6596</v>
       </c>
       <c r="C1232" t="str">
-        <v>2026-07-31 16:22:43</v>
+        <v>2026-07-31 16:13:01</v>
       </c>
       <c r="D1232" t="str">
         <v>NO</v>
@@ -17656,7 +17656,7 @@
         <v>6596</v>
       </c>
       <c r="C1233" t="str">
-        <v>2026-07-31 16:23:07</v>
+        <v>2026-07-31 16:22:43</v>
       </c>
       <c r="D1233" t="str">
         <v>NO</v>
@@ -17670,7 +17670,7 @@
         <v>6596</v>
       </c>
       <c r="C1234" t="str">
-        <v>2026-07-31 16:31:33</v>
+        <v>2026-07-31 16:23:07</v>
       </c>
       <c r="D1234" t="str">
         <v>NO</v>
@@ -17684,7 +17684,7 @@
         <v>6596</v>
       </c>
       <c r="C1235" t="str">
-        <v>2026-07-31 16:40:41</v>
+        <v>2026-07-31 16:31:33</v>
       </c>
       <c r="D1235" t="str">
         <v>NO</v>
@@ -17698,7 +17698,7 @@
         <v>6596</v>
       </c>
       <c r="C1236" t="str">
-        <v>2026-07-31 16:52:29</v>
+        <v>2026-07-31 16:40:41</v>
       </c>
       <c r="D1236" t="str">
         <v>NO</v>
@@ -17712,7 +17712,7 @@
         <v>6596</v>
       </c>
       <c r="C1237" t="str">
-        <v>2026-07-31 17:05:05</v>
+        <v>2026-07-31 16:52:29</v>
       </c>
       <c r="D1237" t="str">
         <v>NO</v>
@@ -17726,7 +17726,7 @@
         <v>6596</v>
       </c>
       <c r="C1238" t="str">
-        <v>2026-07-31 17:11:09</v>
+        <v>2026-07-31 17:05:05</v>
       </c>
       <c r="D1238" t="str">
         <v>NO</v>
@@ -17740,7 +17740,7 @@
         <v>6596</v>
       </c>
       <c r="C1239" t="str">
-        <v>2026-07-31 17:18:53</v>
+        <v>2026-07-31 17:11:09</v>
       </c>
       <c r="D1239" t="str">
         <v>NO</v>
@@ -17754,10 +17754,10 @@
         <v>6596</v>
       </c>
       <c r="C1240" t="str">
-        <v>2026-08-01 01:10:03</v>
+        <v>2026-07-31 17:18:53</v>
       </c>
       <c r="D1240" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1241">
@@ -17768,7 +17768,7 @@
         <v>6596</v>
       </c>
       <c r="C1241" t="str">
-        <v>2026-08-01 05:21:14</v>
+        <v>2026-08-01 01:10:03</v>
       </c>
       <c r="D1241" t="str">
         <v>SI</v>
@@ -17782,7 +17782,7 @@
         <v>6596</v>
       </c>
       <c r="C1242" t="str">
-        <v>2026-08-01 05:42:13</v>
+        <v>2026-08-01 05:21:14</v>
       </c>
       <c r="D1242" t="str">
         <v>SI</v>
@@ -17796,7 +17796,7 @@
         <v>6596</v>
       </c>
       <c r="C1243" t="str">
-        <v>2026-08-01 05:43:27</v>
+        <v>2026-08-01 05:42:13</v>
       </c>
       <c r="D1243" t="str">
         <v>SI</v>
@@ -17810,7 +17810,7 @@
         <v>6596</v>
       </c>
       <c r="C1244" t="str">
-        <v>2026-08-01 09:35:43</v>
+        <v>2026-08-01 05:43:27</v>
       </c>
       <c r="D1244" t="str">
         <v>SI</v>
@@ -17824,7 +17824,7 @@
         <v>6596</v>
       </c>
       <c r="C1245" t="str">
-        <v>2026-08-01 10:30:25</v>
+        <v>2026-08-01 09:35:43</v>
       </c>
       <c r="D1245" t="str">
         <v>SI</v>
@@ -17838,7 +17838,7 @@
         <v>6596</v>
       </c>
       <c r="C1246" t="str">
-        <v>2026-08-01 10:50:43</v>
+        <v>2026-08-01 10:30:25</v>
       </c>
       <c r="D1246" t="str">
         <v>SI</v>
@@ -17852,7 +17852,7 @@
         <v>6596</v>
       </c>
       <c r="C1247" t="str">
-        <v>2026-08-01 10:53:39</v>
+        <v>2026-08-01 10:50:43</v>
       </c>
       <c r="D1247" t="str">
         <v>SI</v>
@@ -17866,7 +17866,7 @@
         <v>6596</v>
       </c>
       <c r="C1248" t="str">
-        <v>2026-08-01 11:25:33</v>
+        <v>2026-08-01 10:53:39</v>
       </c>
       <c r="D1248" t="str">
         <v>SI</v>
@@ -17880,7 +17880,7 @@
         <v>6596</v>
       </c>
       <c r="C1249" t="str">
-        <v>2026-08-01 11:44:33</v>
+        <v>2026-08-01 11:25:33</v>
       </c>
       <c r="D1249" t="str">
         <v>SI</v>
@@ -17894,7 +17894,7 @@
         <v>6596</v>
       </c>
       <c r="C1250" t="str">
-        <v>2026-08-02 01:50:32</v>
+        <v>2026-08-01 11:44:33</v>
       </c>
       <c r="D1250" t="str">
         <v>SI</v>
@@ -17908,7 +17908,7 @@
         <v>6596</v>
       </c>
       <c r="C1251" t="str">
-        <v>2026-08-02 02:23:01</v>
+        <v>2026-08-02 01:50:32</v>
       </c>
       <c r="D1251" t="str">
         <v>SI</v>
@@ -17922,7 +17922,7 @@
         <v>6596</v>
       </c>
       <c r="C1252" t="str">
-        <v>2026-08-02 04:19:31</v>
+        <v>2026-08-02 02:23:01</v>
       </c>
       <c r="D1252" t="str">
         <v>SI</v>
@@ -17936,7 +17936,7 @@
         <v>6596</v>
       </c>
       <c r="C1253" t="str">
-        <v>2026-08-02 06:15:11</v>
+        <v>2026-08-02 04:19:31</v>
       </c>
       <c r="D1253" t="str">
         <v>SI</v>
@@ -17950,7 +17950,7 @@
         <v>6596</v>
       </c>
       <c r="C1254" t="str">
-        <v>2026-08-02 08:45:45</v>
+        <v>2026-08-02 06:15:11</v>
       </c>
       <c r="D1254" t="str">
         <v>SI</v>
@@ -17964,7 +17964,7 @@
         <v>6596</v>
       </c>
       <c r="C1255" t="str">
-        <v>2026-08-02 09:44:12</v>
+        <v>2026-08-02 08:45:45</v>
       </c>
       <c r="D1255" t="str">
         <v>SI</v>
@@ -17978,7 +17978,7 @@
         <v>6596</v>
       </c>
       <c r="C1256" t="str">
-        <v>2026-08-02 11:34:12</v>
+        <v>2026-08-02 09:44:12</v>
       </c>
       <c r="D1256" t="str">
         <v>SI</v>
@@ -17992,7 +17992,7 @@
         <v>6596</v>
       </c>
       <c r="C1257" t="str">
-        <v>2026-08-03 01:30:01</v>
+        <v>2026-08-02 11:34:12</v>
       </c>
       <c r="D1257" t="str">
         <v>SI</v>
@@ -18000,16 +18000,16 @@
     </row>
     <row r="1258">
       <c r="A1258" t="str">
-        <v>JAC  LYTS-17 G GALEA</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B1258">
-        <v>6614</v>
+        <v>6596</v>
       </c>
       <c r="C1258" t="str">
-        <v>2026-07-30 15:16:30</v>
+        <v>2026-08-03 01:30:01</v>
       </c>
       <c r="D1258" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1259">
@@ -18020,7 +18020,7 @@
         <v>6614</v>
       </c>
       <c r="C1259" t="str">
-        <v>2026-07-30 16:55:36</v>
+        <v>2026-07-30 15:16:30</v>
       </c>
       <c r="D1259" t="str">
         <v>NO</v>
@@ -18034,7 +18034,7 @@
         <v>6614</v>
       </c>
       <c r="C1260" t="str">
-        <v>2026-07-30 17:35:42</v>
+        <v>2026-07-30 16:55:36</v>
       </c>
       <c r="D1260" t="str">
         <v>NO</v>
@@ -18048,7 +18048,7 @@
         <v>6614</v>
       </c>
       <c r="C1261" t="str">
-        <v>2026-07-30 18:39:22</v>
+        <v>2026-07-30 17:35:42</v>
       </c>
       <c r="D1261" t="str">
         <v>NO</v>
@@ -18062,10 +18062,10 @@
         <v>6614</v>
       </c>
       <c r="C1262" t="str">
-        <v>2026-07-30 21:58:25</v>
+        <v>2026-07-30 18:39:22</v>
       </c>
       <c r="D1262" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="1263">
@@ -18076,7 +18076,7 @@
         <v>6614</v>
       </c>
       <c r="C1263" t="str">
-        <v>2026-07-30 22:06:04</v>
+        <v>2026-07-30 21:58:25</v>
       </c>
       <c r="D1263" t="str">
         <v>SI</v>
@@ -18090,7 +18090,7 @@
         <v>6614</v>
       </c>
       <c r="C1264" t="str">
-        <v>2026-07-30 22:06:26</v>
+        <v>2026-07-30 22:06:04</v>
       </c>
       <c r="D1264" t="str">
         <v>SI</v>
@@ -18104,7 +18104,7 @@
         <v>6614</v>
       </c>
       <c r="C1265" t="str">
-        <v>2026-07-30 22:07:44</v>
+        <v>2026-07-30 22:06:26</v>
       </c>
       <c r="D1265" t="str">
         <v>SI</v>
@@ -18118,7 +18118,7 @@
         <v>6614</v>
       </c>
       <c r="C1266" t="str">
-        <v>2026-07-30 22:11:32</v>
+        <v>2026-07-30 22:07:44</v>
       </c>
       <c r="D1266" t="str">
         <v>SI</v>
@@ -18132,7 +18132,7 @@
         <v>6614</v>
       </c>
       <c r="C1267" t="str">
-        <v>2026-07-30 22:12:32</v>
+        <v>2026-07-30 22:11:32</v>
       </c>
       <c r="D1267" t="str">
         <v>SI</v>
@@ -18146,7 +18146,7 @@
         <v>6614</v>
       </c>
       <c r="C1268" t="str">
-        <v>2026-07-30 22:17:24</v>
+        <v>2026-07-30 22:12:32</v>
       </c>
       <c r="D1268" t="str">
         <v>SI</v>
@@ -18160,7 +18160,7 @@
         <v>6614</v>
       </c>
       <c r="C1269" t="str">
-        <v>2026-07-30 22:18:10</v>
+        <v>2026-07-30 22:17:24</v>
       </c>
       <c r="D1269" t="str">
         <v>SI</v>
@@ -18174,7 +18174,7 @@
         <v>6614</v>
       </c>
       <c r="C1270" t="str">
-        <v>2026-07-30 22:42:28</v>
+        <v>2026-07-30 22:18:10</v>
       </c>
       <c r="D1270" t="str">
         <v>SI</v>
@@ -18188,7 +18188,7 @@
         <v>6614</v>
       </c>
       <c r="C1271" t="str">
-        <v>2026-07-31 00:21:24</v>
+        <v>2026-07-30 22:42:28</v>
       </c>
       <c r="D1271" t="str">
         <v>SI</v>
@@ -18202,7 +18202,7 @@
         <v>6614</v>
       </c>
       <c r="C1272" t="str">
-        <v>2026-07-31 00:24:56</v>
+        <v>2026-07-31 00:21:24</v>
       </c>
       <c r="D1272" t="str">
         <v>SI</v>
@@ -18216,7 +18216,7 @@
         <v>6614</v>
       </c>
       <c r="C1273" t="str">
-        <v>2026-07-31 00:34:46</v>
+        <v>2026-07-31 00:24:56</v>
       </c>
       <c r="D1273" t="str">
         <v>SI</v>
@@ -18230,10 +18230,10 @@
         <v>6614</v>
       </c>
       <c r="C1274" t="str">
-        <v>2026-07-31 09:50:34</v>
+        <v>2026-07-31 00:34:46</v>
       </c>
       <c r="D1274" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="1275">
@@ -18244,7 +18244,7 @@
         <v>6614</v>
       </c>
       <c r="C1275" t="str">
-        <v>2026-07-31 10:06:29</v>
+        <v>2026-07-31 09:50:34</v>
       </c>
       <c r="D1275" t="str">
         <v>NO</v>
@@ -18258,7 +18258,7 @@
         <v>6614</v>
       </c>
       <c r="C1276" t="str">
-        <v>2026-07-31 10:11:09</v>
+        <v>2026-07-31 10:06:29</v>
       </c>
       <c r="D1276" t="str">
         <v>NO</v>
@@ -18272,7 +18272,7 @@
         <v>6614</v>
       </c>
       <c r="C1277" t="str">
-        <v>2026-07-31 10:37:41</v>
+        <v>2026-07-31 10:11:09</v>
       </c>
       <c r="D1277" t="str">
         <v>NO</v>
@@ -18286,7 +18286,7 @@
         <v>6614</v>
       </c>
       <c r="C1278" t="str">
-        <v>2026-07-31 13:07:20</v>
+        <v>2026-07-31 10:37:41</v>
       </c>
       <c r="D1278" t="str">
         <v>NO</v>
@@ -18300,7 +18300,7 @@
         <v>6614</v>
       </c>
       <c r="C1279" t="str">
-        <v>2026-07-31 14:12:28</v>
+        <v>2026-07-31 13:07:20</v>
       </c>
       <c r="D1279" t="str">
         <v>NO</v>
@@ -18314,7 +18314,7 @@
         <v>6614</v>
       </c>
       <c r="C1280" t="str">
-        <v>2026-07-31 14:29:50</v>
+        <v>2026-07-31 14:12:28</v>
       </c>
       <c r="D1280" t="str">
         <v>NO</v>
@@ -18328,7 +18328,7 @@
         <v>6614</v>
       </c>
       <c r="C1281" t="str">
-        <v>2026-07-31 14:59:00</v>
+        <v>2026-07-31 14:29:50</v>
       </c>
       <c r="D1281" t="str">
         <v>NO</v>
@@ -18342,7 +18342,7 @@
         <v>6614</v>
       </c>
       <c r="C1282" t="str">
-        <v>2026-07-31 15:52:28</v>
+        <v>2026-07-31 14:59:00</v>
       </c>
       <c r="D1282" t="str">
         <v>NO</v>
@@ -18356,7 +18356,7 @@
         <v>6614</v>
       </c>
       <c r="C1283" t="str">
-        <v>2026-07-31 16:03:49</v>
+        <v>2026-07-31 15:52:28</v>
       </c>
       <c r="D1283" t="str">
         <v>NO</v>
@@ -18370,7 +18370,7 @@
         <v>6614</v>
       </c>
       <c r="C1284" t="str">
-        <v>2026-07-31 16:14:22</v>
+        <v>2026-07-31 16:03:49</v>
       </c>
       <c r="D1284" t="str">
         <v>NO</v>
@@ -18384,7 +18384,7 @@
         <v>6614</v>
       </c>
       <c r="C1285" t="str">
-        <v>2026-07-31 16:48:58</v>
+        <v>2026-07-31 16:14:22</v>
       </c>
       <c r="D1285" t="str">
         <v>NO</v>
@@ -18398,7 +18398,7 @@
         <v>6614</v>
       </c>
       <c r="C1286" t="str">
-        <v>2026-07-31 17:22:14</v>
+        <v>2026-07-31 16:48:58</v>
       </c>
       <c r="D1286" t="str">
         <v>NO</v>
@@ -18412,15 +18412,29 @@
         <v>6614</v>
       </c>
       <c r="C1287" t="str">
+        <v>2026-07-31 17:22:14</v>
+      </c>
+      <c r="D1287" t="str">
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="str">
+        <v>JAC  LYTS-17 G GALEA</v>
+      </c>
+      <c r="B1288">
+        <v>6614</v>
+      </c>
+      <c r="C1288" t="str">
         <v>2026-07-31 18:36:24</v>
       </c>
-      <c r="D1287" t="str">
+      <c r="D1288" t="str">
         <v>NO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1287"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1288"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -18465,10 +18479,10 @@
         <v>6597</v>
       </c>
       <c r="C3">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">

--- a/latest-events.xlsx
+++ b/latest-events.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D138"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,7 +422,7 @@
         <v>6618</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-07-30 16:53:20</v>
+        <v>2026-08-03 09:54:04</v>
       </c>
       <c r="D2" t="str">
         <v>NO</v>
@@ -436,10 +436,10 @@
         <v>6618</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-07-30 16:53:20</v>
+        <v>2026-08-03 21:38:01</v>
       </c>
       <c r="D3" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="4">
@@ -450,21 +450,21 @@
         <v>6618</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-07-30 21:26:39</v>
+        <v>2026-08-04 17:17:29</v>
       </c>
       <c r="D4" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GC MAXUS PCRF-25 TERRENO</v>
+        <v>DONGFENG DF6 SRSR-97</v>
       </c>
       <c r="B5">
-        <v>6617</v>
+        <v>6618</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-07-31 12:39:58</v>
+        <v>2026-08-07 16:39:44</v>
       </c>
       <c r="D5" t="str">
         <v>NO</v>
@@ -472,13 +472,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B6">
-        <v>6616</v>
+        <v>6617</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-07-30 15:06:14</v>
+        <v>2026-08-03 07:42:06</v>
       </c>
       <c r="D6" t="str">
         <v>NO</v>
@@ -486,13 +486,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B7">
-        <v>6616</v>
+        <v>6617</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-07-30 15:06:14</v>
+        <v>2026-08-04 10:24:14</v>
       </c>
       <c r="D7" t="str">
         <v>NO</v>
@@ -500,41 +500,41 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B8">
-        <v>6616</v>
+        <v>6617</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-07-30 20:17:06</v>
+        <v>2026-08-04 16:37:27</v>
       </c>
       <c r="D8" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GC RXDL-59 OPERACIONES</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B9">
-        <v>6581</v>
+        <v>6617</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-07-27 09:07:04</v>
+        <v>2026-08-07 20:05:00</v>
       </c>
       <c r="D9" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GC RXDL-59 OPERACIONES</v>
+        <v>GC MAXUS PKFF-65 G VICENCIO</v>
       </c>
       <c r="B10">
-        <v>6581</v>
+        <v>6616</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-07-30 21:03:38</v>
+        <v>2026-08-04 20:29:03</v>
       </c>
       <c r="D10" t="str">
         <v>SI</v>
@@ -548,7 +548,7 @@
         <v>6608</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-07-30 14:38:45</v>
+        <v>2026-08-03 11:30:01</v>
       </c>
       <c r="D11" t="str">
         <v>NO</v>
@@ -562,10 +562,10 @@
         <v>6608</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-07-30 14:38:45</v>
+        <v>2026-08-03 22:05:36</v>
       </c>
       <c r="D12" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="13">
@@ -576,7 +576,7 @@
         <v>6608</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-07-30 14:47:35</v>
+        <v>2026-08-04 18:08:38</v>
       </c>
       <c r="D13" t="str">
         <v>NO</v>
@@ -590,7 +590,7 @@
         <v>6608</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-07-30 15:47:11</v>
+        <v>2026-08-07 16:24:51</v>
       </c>
       <c r="D14" t="str">
         <v>NO</v>
@@ -598,16 +598,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GC TM5-RXXG-13 D SILVA</v>
+        <v>GC TM5-VKFB-85 M CASTRO</v>
       </c>
       <c r="B15">
-        <v>6608</v>
+        <v>6609</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-07-30 20:43:05</v>
+        <v>2026-08-03 11:20:30</v>
       </c>
       <c r="D15" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="16">
@@ -618,10 +618,10 @@
         <v>6609</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-07-30 14:35:58</v>
+        <v>2026-08-03 21:25:32</v>
       </c>
       <c r="D16" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="17">
@@ -632,10 +632,10 @@
         <v>6609</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-07-30 14:35:58</v>
+        <v>2026-08-03 22:01:58</v>
       </c>
       <c r="D17" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="18">
@@ -646,7 +646,7 @@
         <v>6609</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-07-30 16:36:45</v>
+        <v>2026-08-04 16:37:54</v>
       </c>
       <c r="D18" t="str">
         <v>NO</v>
@@ -660,7 +660,7 @@
         <v>6609</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-07-30 16:36:45</v>
+        <v>2026-08-07 15:22:06</v>
       </c>
       <c r="D19" t="str">
         <v>NO</v>
@@ -668,27 +668,27 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B20">
-        <v>6609</v>
+        <v>6620</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-07-30 20:25:25</v>
+        <v>2026-08-03 12:26:10</v>
       </c>
       <c r="D20" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B21">
-        <v>6609</v>
+        <v>6620</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-07-30 21:03:47</v>
+        <v>2026-08-03 22:01:18</v>
       </c>
       <c r="D21" t="str">
         <v>SI</v>
@@ -702,7 +702,7 @@
         <v>6620</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-07-30 18:24:36</v>
+        <v>2026-08-04 14:40:43</v>
       </c>
       <c r="D22" t="str">
         <v>NO</v>
@@ -716,7 +716,7 @@
         <v>6620</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-07-30 18:24:36</v>
+        <v>2026-08-07 16:29:03</v>
       </c>
       <c r="D23" t="str">
         <v>NO</v>
@@ -724,16 +724,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GC TM5-VRVJ-20 L SALINAS</v>
+        <v>GC TSVS-89 M AEDO</v>
       </c>
       <c r="B24">
-        <v>6620</v>
+        <v>6610</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-07-30 21:05:12</v>
+        <v>2026-08-03 09:43:08</v>
       </c>
       <c r="D24" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="25">
@@ -744,7 +744,7 @@
         <v>6610</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-07-30 20:14:12</v>
+        <v>2026-08-04 00:01:46</v>
       </c>
       <c r="D25" t="str">
         <v>SI</v>
@@ -758,21 +758,21 @@
         <v>6610</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-07-30 21:08:04</v>
+        <v>2026-08-04 16:31:07</v>
       </c>
       <c r="D26" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GLP ALJIBE SJHW-20</v>
+        <v>GC TSVS-89 M AEDO</v>
       </c>
       <c r="B27">
-        <v>6583</v>
+        <v>6610</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-07-30 16:41:21</v>
+        <v>2026-08-07 17:30:59</v>
       </c>
       <c r="D27" t="str">
         <v>NO</v>
@@ -786,7 +786,7 @@
         <v>6583</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-07-30 16:41:21</v>
+        <v>2026-08-03 12:12:32</v>
       </c>
       <c r="D28" t="str">
         <v>NO</v>
@@ -800,7 +800,7 @@
         <v>6583</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-07-30 20:17:06</v>
+        <v>2026-08-03 21:31:40</v>
       </c>
       <c r="D29" t="str">
         <v>SI</v>
@@ -814,10 +814,10 @@
         <v>6583</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-07-30 20:30:55</v>
+        <v>2026-08-04 11:36:09</v>
       </c>
       <c r="D30" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="31">
@@ -828,24 +828,24 @@
         <v>6583</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-07-30 20:44:02</v>
+        <v>2026-08-04 15:43:39</v>
       </c>
       <c r="D31" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GLP DF6 RXDL-61 OPERACIONES</v>
+        <v>GLP ALJIBE SJHW-20</v>
       </c>
       <c r="B32">
-        <v>6600</v>
+        <v>6583</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-07-30 19:14:36</v>
+        <v>2026-08-07 17:56:28</v>
       </c>
       <c r="D32" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="33">
@@ -856,10 +856,10 @@
         <v>6600</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-07-30 19:14:36</v>
+        <v>2026-08-03 14:30:29</v>
       </c>
       <c r="D33" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="34">
@@ -870,7 +870,7 @@
         <v>6600</v>
       </c>
       <c r="C34" t="str">
-        <v>2026-07-31 14:36:05</v>
+        <v>2026-08-04 15:30:08</v>
       </c>
       <c r="D34" t="str">
         <v>NO</v>
@@ -878,13 +878,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
+        <v>GLP DF6 RXDL-61 OPERACIONES</v>
       </c>
       <c r="B35">
-        <v>6593</v>
+        <v>6600</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-07-30 17:02:34</v>
+        <v>2026-08-07 18:18:28</v>
       </c>
       <c r="D35" t="str">
         <v>NO</v>
@@ -898,7 +898,7 @@
         <v>6593</v>
       </c>
       <c r="C36" t="str">
-        <v>2026-07-30 17:02:34</v>
+        <v>2026-08-03 12:22:44</v>
       </c>
       <c r="D36" t="str">
         <v>NO</v>
@@ -912,7 +912,7 @@
         <v>6593</v>
       </c>
       <c r="C37" t="str">
-        <v>2026-07-30 21:32:39</v>
+        <v>2026-08-03 22:25:40</v>
       </c>
       <c r="D37" t="str">
         <v>SI</v>
@@ -920,13 +920,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B38">
-        <v>6597</v>
+        <v>6593</v>
       </c>
       <c r="C38" t="str">
-        <v>2026-07-30 14:46:39</v>
+        <v>2026-08-04 15:36:41</v>
       </c>
       <c r="D38" t="str">
         <v>NO</v>
@@ -934,13 +934,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B39">
-        <v>6597</v>
+        <v>6593</v>
       </c>
       <c r="C39" t="str">
-        <v>2026-07-30 14:46:39</v>
+        <v>2026-08-07 15:59:52</v>
       </c>
       <c r="D39" t="str">
         <v>NO</v>
@@ -954,7 +954,7 @@
         <v>6597</v>
       </c>
       <c r="C40" t="str">
-        <v>2026-07-30 20:17:44</v>
+        <v>2026-08-03 04:19:39</v>
       </c>
       <c r="D40" t="str">
         <v>SI</v>
@@ -968,7 +968,7 @@
         <v>6597</v>
       </c>
       <c r="C41" t="str">
-        <v>2026-07-30 21:29:13</v>
+        <v>2026-08-03 23:22:08</v>
       </c>
       <c r="D41" t="str">
         <v>SI</v>
@@ -976,27 +976,27 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B42">
-        <v>6598</v>
+        <v>6597</v>
       </c>
       <c r="C42" t="str">
-        <v>2026-07-30 22:46:18</v>
+        <v>2026-08-04 15:18:53</v>
       </c>
       <c r="D42" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B43">
-        <v>6586</v>
+        <v>6597</v>
       </c>
       <c r="C43" t="str">
-        <v>2026-07-27 12:10:20</v>
+        <v>2026-08-07 17:58:03</v>
       </c>
       <c r="D43" t="str">
         <v>NO</v>
@@ -1004,13 +1004,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B44">
-        <v>6586</v>
+        <v>6598</v>
       </c>
       <c r="C44" t="str">
-        <v>2026-07-30 14:33:26</v>
+        <v>2026-08-03 11:39:20</v>
       </c>
       <c r="D44" t="str">
         <v>NO</v>
@@ -1018,27 +1018,27 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B45">
-        <v>6586</v>
+        <v>6598</v>
       </c>
       <c r="C45" t="str">
-        <v>2026-07-30 14:33:26</v>
+        <v>2026-08-03 21:36:03</v>
       </c>
       <c r="D45" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B46">
-        <v>6586</v>
+        <v>6598</v>
       </c>
       <c r="C46" t="str">
-        <v>2026-07-30 16:23:24</v>
+        <v>2026-08-04 11:32:35</v>
       </c>
       <c r="D46" t="str">
         <v>NO</v>
@@ -1046,30 +1046,30 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B47">
-        <v>6586</v>
+        <v>6598</v>
       </c>
       <c r="C47" t="str">
-        <v>2026-07-30 16:23:24</v>
+        <v>2026-08-04 20:58:14</v>
       </c>
       <c r="D47" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B48">
-        <v>6586</v>
+        <v>6598</v>
       </c>
       <c r="C48" t="str">
-        <v>2026-07-30 20:06:50</v>
+        <v>2026-08-07 17:53:01</v>
       </c>
       <c r="D48" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="49">
@@ -1080,10 +1080,10 @@
         <v>6586</v>
       </c>
       <c r="C49" t="str">
-        <v>2026-07-30 20:31:32</v>
+        <v>2026-08-03 12:02:56</v>
       </c>
       <c r="D49" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="50">
@@ -1094,21 +1094,21 @@
         <v>6586</v>
       </c>
       <c r="C50" t="str">
-        <v>2026-07-30 20:40:54</v>
+        <v>2026-08-04 12:02:40</v>
       </c>
       <c r="D50" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B51">
-        <v>6604</v>
+        <v>6586</v>
       </c>
       <c r="C51" t="str">
-        <v>2026-07-27 14:15:16</v>
+        <v>2026-08-04 15:30:32</v>
       </c>
       <c r="D51" t="str">
         <v>NO</v>
@@ -1116,13 +1116,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B52">
-        <v>6604</v>
+        <v>6586</v>
       </c>
       <c r="C52" t="str">
-        <v>2026-07-30 14:30:59</v>
+        <v>2026-08-07 15:37:09</v>
       </c>
       <c r="D52" t="str">
         <v>NO</v>
@@ -1136,7 +1136,7 @@
         <v>6604</v>
       </c>
       <c r="C53" t="str">
-        <v>2026-07-30 14:30:59</v>
+        <v>2026-08-03 12:56:45</v>
       </c>
       <c r="D53" t="str">
         <v>NO</v>
@@ -1150,10 +1150,10 @@
         <v>6604</v>
       </c>
       <c r="C54" t="str">
-        <v>2026-07-30 18:22:45</v>
+        <v>2026-08-03 21:37:44</v>
       </c>
       <c r="D54" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="55">
@@ -1164,7 +1164,7 @@
         <v>6604</v>
       </c>
       <c r="C55" t="str">
-        <v>2026-07-30 18:22:45</v>
+        <v>2026-08-04 18:12:37</v>
       </c>
       <c r="D55" t="str">
         <v>NO</v>
@@ -1172,16 +1172,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B56">
-        <v>6601</v>
+        <v>6604</v>
       </c>
       <c r="C56" t="str">
-        <v>2026-07-30 16:03:58</v>
+        <v>2026-08-07 20:17:02</v>
       </c>
       <c r="D56" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="57">
@@ -1192,7 +1192,7 @@
         <v>6601</v>
       </c>
       <c r="C57" t="str">
-        <v>2026-07-30 16:03:58</v>
+        <v>2026-08-03 13:00:25</v>
       </c>
       <c r="D57" t="str">
         <v>NO</v>
@@ -1206,7 +1206,7 @@
         <v>6601</v>
       </c>
       <c r="C58" t="str">
-        <v>2026-07-30 20:05:46</v>
+        <v>2026-08-03 21:43:44</v>
       </c>
       <c r="D58" t="str">
         <v>SI</v>
@@ -1220,7 +1220,7 @@
         <v>6601</v>
       </c>
       <c r="C59" t="str">
-        <v>2026-07-31 13:32:02</v>
+        <v>2026-08-04 18:10:16</v>
       </c>
       <c r="D59" t="str">
         <v>NO</v>
@@ -1228,16 +1228,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B60">
-        <v>6606</v>
+        <v>6601</v>
       </c>
       <c r="C60" t="str">
-        <v>2026-07-30 15:13:24</v>
+        <v>2026-08-07 20:10:35</v>
       </c>
       <c r="D60" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="61">
@@ -1248,10 +1248,10 @@
         <v>6606</v>
       </c>
       <c r="C61" t="str">
-        <v>2026-07-30 15:13:24</v>
+        <v>2026-08-03 04:11:21</v>
       </c>
       <c r="D61" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="62">
@@ -1262,10 +1262,10 @@
         <v>6606</v>
       </c>
       <c r="C62" t="str">
-        <v>2026-07-30 15:46:42</v>
+        <v>2026-08-03 21:31:58</v>
       </c>
       <c r="D62" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="63">
@@ -1276,7 +1276,7 @@
         <v>6606</v>
       </c>
       <c r="C63" t="str">
-        <v>2026-07-30 20:07:37</v>
+        <v>2026-08-03 22:04:14</v>
       </c>
       <c r="D63" t="str">
         <v>SI</v>
@@ -1290,24 +1290,24 @@
         <v>6606</v>
       </c>
       <c r="C64" t="str">
-        <v>2026-07-30 20:41:04</v>
+        <v>2026-08-04 15:59:57</v>
       </c>
       <c r="D64" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B65">
-        <v>6580</v>
+        <v>6606</v>
       </c>
       <c r="C65" t="str">
-        <v>2026-07-30 15:06:09</v>
+        <v>2026-08-07 20:30:53</v>
       </c>
       <c r="D65" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="66">
@@ -1318,7 +1318,7 @@
         <v>6580</v>
       </c>
       <c r="C66" t="str">
-        <v>2026-07-30 15:06:09</v>
+        <v>2026-08-03 13:11:36</v>
       </c>
       <c r="D66" t="str">
         <v>NO</v>
@@ -1332,7 +1332,7 @@
         <v>6580</v>
       </c>
       <c r="C67" t="str">
-        <v>2026-07-30 15:49:59</v>
+        <v>2026-08-04 12:11:08</v>
       </c>
       <c r="D67" t="str">
         <v>NO</v>
@@ -1346,10 +1346,10 @@
         <v>6580</v>
       </c>
       <c r="C68" t="str">
-        <v>2026-07-30 20:02:33</v>
+        <v>2026-08-04 15:49:21</v>
       </c>
       <c r="D68" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="69">
@@ -1360,7 +1360,7 @@
         <v>6580</v>
       </c>
       <c r="C69" t="str">
-        <v>2026-07-31 12:16:04</v>
+        <v>2026-08-07 15:38:15</v>
       </c>
       <c r="D69" t="str">
         <v>NO</v>
@@ -1374,7 +1374,7 @@
         <v>6594</v>
       </c>
       <c r="C70" t="str">
-        <v>2026-07-30 14:53:24</v>
+        <v>2026-08-03 12:19:44</v>
       </c>
       <c r="D70" t="str">
         <v>NO</v>
@@ -1388,7 +1388,7 @@
         <v>6594</v>
       </c>
       <c r="C71" t="str">
-        <v>2026-07-30 14:53:24</v>
+        <v>2026-08-04 12:35:47</v>
       </c>
       <c r="D71" t="str">
         <v>NO</v>
@@ -1402,7 +1402,7 @@
         <v>6594</v>
       </c>
       <c r="C72" t="str">
-        <v>2026-07-30 15:57:45</v>
+        <v>2026-08-04 15:18:55</v>
       </c>
       <c r="D72" t="str">
         <v>NO</v>
@@ -1416,7 +1416,7 @@
         <v>6594</v>
       </c>
       <c r="C73" t="str">
-        <v>2026-07-30 22:46:03</v>
+        <v>2026-08-07 19:45:54</v>
       </c>
       <c r="D73" t="str">
         <v>SI</v>
@@ -1430,7 +1430,7 @@
         <v>6605</v>
       </c>
       <c r="C74" t="str">
-        <v>2026-07-27 12:23:18</v>
+        <v>2026-08-03 12:11:14</v>
       </c>
       <c r="D74" t="str">
         <v>NO</v>
@@ -1444,10 +1444,10 @@
         <v>6605</v>
       </c>
       <c r="C75" t="str">
-        <v>2026-07-30 16:58:42</v>
+        <v>2026-08-03 21:44:27</v>
       </c>
       <c r="D75" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="76">
@@ -1458,24 +1458,24 @@
         <v>6605</v>
       </c>
       <c r="C76" t="str">
-        <v>2026-07-31 12:33:45</v>
+        <v>2026-08-04 21:41:25</v>
       </c>
       <c r="D76" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B77">
-        <v>6603</v>
+        <v>6605</v>
       </c>
       <c r="C77" t="str">
-        <v>2026-07-27 13:26:44</v>
+        <v>2026-08-07 21:57:15</v>
       </c>
       <c r="D77" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="78">
@@ -1486,7 +1486,7 @@
         <v>6603</v>
       </c>
       <c r="C78" t="str">
-        <v>2026-07-30 15:14:08</v>
+        <v>2026-08-03 15:41:55</v>
       </c>
       <c r="D78" t="str">
         <v>NO</v>
@@ -1500,7 +1500,7 @@
         <v>6603</v>
       </c>
       <c r="C79" t="str">
-        <v>2026-07-30 15:14:08</v>
+        <v>2026-08-04 13:14:32</v>
       </c>
       <c r="D79" t="str">
         <v>NO</v>
@@ -1514,7 +1514,7 @@
         <v>6603</v>
       </c>
       <c r="C80" t="str">
-        <v>2026-07-30 17:11:48</v>
+        <v>2026-08-04 15:53:51</v>
       </c>
       <c r="D80" t="str">
         <v>NO</v>
@@ -1528,10 +1528,10 @@
         <v>6603</v>
       </c>
       <c r="C81" t="str">
-        <v>2026-07-30 20:46:24</v>
+        <v>2026-08-07 15:22:53</v>
       </c>
       <c r="D81" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="82">
@@ -1542,7 +1542,7 @@
         <v>6607</v>
       </c>
       <c r="C82" t="str">
-        <v>2026-07-27 10:15:18</v>
+        <v>2026-08-03 10:22:12</v>
       </c>
       <c r="D82" t="str">
         <v>NO</v>
@@ -1556,10 +1556,10 @@
         <v>6607</v>
       </c>
       <c r="C83" t="str">
-        <v>2026-07-30 14:23:32</v>
+        <v>2026-08-03 22:05:15</v>
       </c>
       <c r="D83" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="84">
@@ -1570,7 +1570,7 @@
         <v>6607</v>
       </c>
       <c r="C84" t="str">
-        <v>2026-07-30 14:23:32</v>
+        <v>2026-08-04 17:05:27</v>
       </c>
       <c r="D84" t="str">
         <v>NO</v>
@@ -1584,10 +1584,10 @@
         <v>6607</v>
       </c>
       <c r="C85" t="str">
-        <v>2026-07-30 21:02:29</v>
+        <v>2026-08-07 16:25:27</v>
       </c>
       <c r="D85" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="86">
@@ -1598,7 +1598,7 @@
         <v>6602</v>
       </c>
       <c r="C86" t="str">
-        <v>2026-07-27 10:53:20</v>
+        <v>2026-08-03 10:59:15</v>
       </c>
       <c r="D86" t="str">
         <v>NO</v>
@@ -1612,10 +1612,10 @@
         <v>6602</v>
       </c>
       <c r="C87" t="str">
-        <v>2026-07-30 15:16:13</v>
+        <v>2026-08-03 22:21:40</v>
       </c>
       <c r="D87" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="88">
@@ -1626,7 +1626,7 @@
         <v>6602</v>
       </c>
       <c r="C88" t="str">
-        <v>2026-07-30 15:16:13</v>
+        <v>2026-08-04 17:14:50</v>
       </c>
       <c r="D88" t="str">
         <v>NO</v>
@@ -1640,7 +1640,7 @@
         <v>6602</v>
       </c>
       <c r="C89" t="str">
-        <v>2026-07-30 18:48:57</v>
+        <v>2026-08-07 16:27:55</v>
       </c>
       <c r="D89" t="str">
         <v>NO</v>
@@ -1648,16 +1648,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B90">
-        <v>6602</v>
+        <v>6612</v>
       </c>
       <c r="C90" t="str">
-        <v>2026-07-30 20:39:13</v>
+        <v>2026-08-03 11:54:46</v>
       </c>
       <c r="D90" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="91">
@@ -1668,10 +1668,10 @@
         <v>6612</v>
       </c>
       <c r="C91" t="str">
-        <v>2026-07-27 12:14:30</v>
+        <v>2026-08-03 22:23:08</v>
       </c>
       <c r="D91" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="92">
@@ -1682,7 +1682,7 @@
         <v>6612</v>
       </c>
       <c r="C92" t="str">
-        <v>2026-07-30 18:01:14</v>
+        <v>2026-08-04 15:20:25</v>
       </c>
       <c r="D92" t="str">
         <v>NO</v>
@@ -1696,7 +1696,7 @@
         <v>6612</v>
       </c>
       <c r="C93" t="str">
-        <v>2026-07-30 18:01:14</v>
+        <v>2026-08-07 15:39:42</v>
       </c>
       <c r="D93" t="str">
         <v>NO</v>
@@ -1704,13 +1704,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B94">
-        <v>6612</v>
+        <v>6599</v>
       </c>
       <c r="C94" t="str">
-        <v>2026-07-31 12:03:35</v>
+        <v>2026-08-03 11:56:13</v>
       </c>
       <c r="D94" t="str">
         <v>NO</v>
@@ -1724,10 +1724,10 @@
         <v>6599</v>
       </c>
       <c r="C95" t="str">
-        <v>2026-07-27 11:58:07</v>
+        <v>2026-08-03 21:57:20</v>
       </c>
       <c r="D95" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="96">
@@ -1738,7 +1738,7 @@
         <v>6599</v>
       </c>
       <c r="C96" t="str">
-        <v>2026-07-30 13:44:54</v>
+        <v>2026-08-04 15:59:30</v>
       </c>
       <c r="D96" t="str">
         <v>NO</v>
@@ -1752,7 +1752,7 @@
         <v>6599</v>
       </c>
       <c r="C97" t="str">
-        <v>2026-07-31 12:03:01</v>
+        <v>2026-08-07 16:16:03</v>
       </c>
       <c r="D97" t="str">
         <v>NO</v>
@@ -1760,16 +1760,16 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>GV FOSERO SJHW-18 V OLIVARES</v>
+        <v>GV FORD BU-9781 V OLIVARES</v>
       </c>
       <c r="B98">
-        <v>6592</v>
+        <v>6621</v>
       </c>
       <c r="C98" t="str">
-        <v>2026-07-27 08:27:58</v>
+        <v>2026-08-05 20:54:37</v>
       </c>
       <c r="D98" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="99">
@@ -1780,38 +1780,38 @@
         <v>6592</v>
       </c>
       <c r="C99" t="str">
-        <v>2026-07-31 21:25:46</v>
+        <v>2026-08-03 08:17:28</v>
       </c>
       <c r="D99" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B100">
-        <v>6595</v>
+        <v>6592</v>
       </c>
       <c r="C100" t="str">
-        <v>2026-07-27 10:52:15</v>
+        <v>2026-08-05 21:17:52</v>
       </c>
       <c r="D100" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B101">
-        <v>6595</v>
+        <v>6592</v>
       </c>
       <c r="C101" t="str">
-        <v>2026-07-30 14:27:54</v>
+        <v>2026-08-07 21:43:53</v>
       </c>
       <c r="D101" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="102">
@@ -1822,7 +1822,7 @@
         <v>6595</v>
       </c>
       <c r="C102" t="str">
-        <v>2026-07-30 14:27:54</v>
+        <v>2026-08-03 10:36:54</v>
       </c>
       <c r="D102" t="str">
         <v>NO</v>
@@ -1836,10 +1836,10 @@
         <v>6595</v>
       </c>
       <c r="C103" t="str">
-        <v>2026-07-30 15:44:25</v>
+        <v>2026-08-03 22:58:27</v>
       </c>
       <c r="D103" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="104">
@@ -1850,7 +1850,7 @@
         <v>6595</v>
       </c>
       <c r="C104" t="str">
-        <v>2026-07-30 16:40:21</v>
+        <v>2026-08-04 15:28:23</v>
       </c>
       <c r="D104" t="str">
         <v>NO</v>
@@ -1864,7 +1864,7 @@
         <v>6595</v>
       </c>
       <c r="C105" t="str">
-        <v>2026-07-30 22:51:55</v>
+        <v>2026-08-07 19:49:21</v>
       </c>
       <c r="D105" t="str">
         <v>SI</v>
@@ -1878,7 +1878,7 @@
         <v>6585</v>
       </c>
       <c r="C106" t="str">
-        <v>2026-07-27 11:10:46</v>
+        <v>2026-08-03 11:08:27</v>
       </c>
       <c r="D106" t="str">
         <v>NO</v>
@@ -1892,10 +1892,10 @@
         <v>6585</v>
       </c>
       <c r="C107" t="str">
-        <v>2026-07-30 14:52:40</v>
+        <v>2026-08-03 23:10:16</v>
       </c>
       <c r="D107" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="108">
@@ -1906,7 +1906,7 @@
         <v>6585</v>
       </c>
       <c r="C108" t="str">
-        <v>2026-07-30 14:52:40</v>
+        <v>2026-08-04 16:01:44</v>
       </c>
       <c r="D108" t="str">
         <v>NO</v>
@@ -1920,7 +1920,7 @@
         <v>6585</v>
       </c>
       <c r="C109" t="str">
-        <v>2026-07-30 17:32:22</v>
+        <v>2026-08-07 15:44:31</v>
       </c>
       <c r="D109" t="str">
         <v>NO</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>GV SHDV-50 C CARDENAS</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B110">
-        <v>6585</v>
+        <v>6588</v>
       </c>
       <c r="C110" t="str">
-        <v>2026-07-30 21:08:18</v>
+        <v>2026-08-03 04:02:26</v>
       </c>
       <c r="D110" t="str">
         <v>SI</v>
@@ -1948,7 +1948,7 @@
         <v>6588</v>
       </c>
       <c r="C111" t="str">
-        <v>2026-07-27 04:03:27</v>
+        <v>2026-08-03 21:59:47</v>
       </c>
       <c r="D111" t="str">
         <v>SI</v>
@@ -1962,10 +1962,10 @@
         <v>6588</v>
       </c>
       <c r="C112" t="str">
-        <v>2026-07-30 15:34:31</v>
+        <v>2026-08-05 02:04:31</v>
       </c>
       <c r="D112" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="113">
@@ -1976,21 +1976,21 @@
         <v>6588</v>
       </c>
       <c r="C113" t="str">
-        <v>2026-07-30 15:34:31</v>
+        <v>2026-08-08 02:13:27</v>
       </c>
       <c r="D113" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B114">
-        <v>6588</v>
+        <v>6587</v>
       </c>
       <c r="C114" t="str">
-        <v>2026-07-30 18:10:13</v>
+        <v>2026-08-03 10:10:28</v>
       </c>
       <c r="D114" t="str">
         <v>NO</v>
@@ -1998,16 +1998,16 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B115">
-        <v>6588</v>
+        <v>6587</v>
       </c>
       <c r="C115" t="str">
-        <v>2026-07-30 20:38:08</v>
+        <v>2026-08-04 10:07:31</v>
       </c>
       <c r="D115" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="116">
@@ -2018,7 +2018,7 @@
         <v>6587</v>
       </c>
       <c r="C116" t="str">
-        <v>2026-07-27 11:02:26</v>
+        <v>2026-08-04 15:20:33</v>
       </c>
       <c r="D116" t="str">
         <v>NO</v>
@@ -2032,7 +2032,7 @@
         <v>6587</v>
       </c>
       <c r="C117" t="str">
-        <v>2026-07-30 14:25:06</v>
+        <v>2026-08-07 16:12:21</v>
       </c>
       <c r="D117" t="str">
         <v>NO</v>
@@ -2040,13 +2040,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B118">
-        <v>6587</v>
+        <v>6582</v>
       </c>
       <c r="C118" t="str">
-        <v>2026-07-30 14:25:06</v>
+        <v>2026-08-03 17:54:39</v>
       </c>
       <c r="D118" t="str">
         <v>NO</v>
@@ -2054,27 +2054,27 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B119">
-        <v>6587</v>
+        <v>6582</v>
       </c>
       <c r="C119" t="str">
-        <v>2026-07-30 16:40:20</v>
+        <v>2026-08-03 22:04:17</v>
       </c>
       <c r="D119" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B120">
-        <v>6587</v>
+        <v>6582</v>
       </c>
       <c r="C120" t="str">
-        <v>2026-07-30 16:40:20</v>
+        <v>2026-08-04 17:59:02</v>
       </c>
       <c r="D120" t="str">
         <v>NO</v>
@@ -2082,27 +2082,27 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B121">
-        <v>6587</v>
+        <v>6582</v>
       </c>
       <c r="C121" t="str">
-        <v>2026-07-31 01:53:32</v>
+        <v>2026-08-07 18:02:52</v>
       </c>
       <c r="D121" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B122">
-        <v>6582</v>
+        <v>6589</v>
       </c>
       <c r="C122" t="str">
-        <v>2026-07-30 15:14:24</v>
+        <v>2026-08-03 10:28:49</v>
       </c>
       <c r="D122" t="str">
         <v>NO</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B123">
-        <v>6582</v>
+        <v>6589</v>
       </c>
       <c r="C123" t="str">
-        <v>2026-07-30 15:14:24</v>
+        <v>2026-08-04 10:24:25</v>
       </c>
       <c r="D123" t="str">
         <v>NO</v>
@@ -2124,13 +2124,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B124">
-        <v>6582</v>
+        <v>6589</v>
       </c>
       <c r="C124" t="str">
-        <v>2026-07-30 16:24:49</v>
+        <v>2026-08-04 17:21:02</v>
       </c>
       <c r="D124" t="str">
         <v>NO</v>
@@ -2138,27 +2138,27 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B125">
-        <v>6582</v>
+        <v>6589</v>
       </c>
       <c r="C125" t="str">
-        <v>2026-07-30 20:17:33</v>
+        <v>2026-08-07 16:56:12</v>
       </c>
       <c r="D125" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B126">
-        <v>6582</v>
+        <v>6596</v>
       </c>
       <c r="C126" t="str">
-        <v>2026-07-30 21:09:05</v>
+        <v>2026-08-03 04:04:12</v>
       </c>
       <c r="D126" t="str">
         <v>SI</v>
@@ -2166,27 +2166,27 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B127">
-        <v>6589</v>
+        <v>6596</v>
       </c>
       <c r="C127" t="str">
-        <v>2026-07-27 10:26:43</v>
+        <v>2026-08-04 01:33:39</v>
       </c>
       <c r="D127" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B128">
-        <v>6589</v>
+        <v>6596</v>
       </c>
       <c r="C128" t="str">
-        <v>2026-07-30 14:22:07</v>
+        <v>2026-08-04 16:02:33</v>
       </c>
       <c r="D128" t="str">
         <v>NO</v>
@@ -2194,69 +2194,69 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B129">
-        <v>6589</v>
+        <v>6596</v>
       </c>
       <c r="C129" t="str">
-        <v>2026-07-30 14:22:07</v>
+        <v>2026-08-08 01:43:20</v>
       </c>
       <c r="D129" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B130">
-        <v>6589</v>
+        <v>6619</v>
       </c>
       <c r="C130" t="str">
-        <v>2026-07-30 17:32:30</v>
+        <v>2026-08-03 21:08:45</v>
       </c>
       <c r="D130" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B131">
-        <v>6589</v>
+        <v>6619</v>
       </c>
       <c r="C131" t="str">
-        <v>2026-07-30 17:32:30</v>
+        <v>2026-08-03 21:25:10</v>
       </c>
       <c r="D131" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B132">
-        <v>6589</v>
+        <v>6619</v>
       </c>
       <c r="C132" t="str">
-        <v>2026-07-30 21:26:02</v>
+        <v>2026-08-04 10:28:45</v>
       </c>
       <c r="D132" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B133">
-        <v>6596</v>
+        <v>6619</v>
       </c>
       <c r="C133" t="str">
-        <v>2026-07-27 10:15:01</v>
+        <v>2026-08-04 16:53:22</v>
       </c>
       <c r="D133" t="str">
         <v>NO</v>
@@ -2264,13 +2264,13 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B134">
-        <v>6596</v>
+        <v>6619</v>
       </c>
       <c r="C134" t="str">
-        <v>2026-07-30 18:00:47</v>
+        <v>2026-08-07 15:22:48</v>
       </c>
       <c r="D134" t="str">
         <v>NO</v>
@@ -2278,13 +2278,13 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>JAC  LYTS-17 G GALEA</v>
       </c>
       <c r="B135">
-        <v>6596</v>
+        <v>6614</v>
       </c>
       <c r="C135" t="str">
-        <v>2026-07-30 18:00:47</v>
+        <v>2026-08-03 09:55:55</v>
       </c>
       <c r="D135" t="str">
         <v>NO</v>
@@ -2292,13 +2292,13 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>JAC  LYTS-17 G GALEA</v>
       </c>
       <c r="B136">
-        <v>6596</v>
+        <v>6614</v>
       </c>
       <c r="C136" t="str">
-        <v>2026-07-31 01:24:05</v>
+        <v>2026-08-03 21:39:01</v>
       </c>
       <c r="D136" t="str">
         <v>SI</v>
@@ -2312,7 +2312,7 @@
         <v>6614</v>
       </c>
       <c r="C137" t="str">
-        <v>2026-07-30 15:16:30</v>
+        <v>2026-08-04 17:19:13</v>
       </c>
       <c r="D137" t="str">
         <v>NO</v>
@@ -2326,50 +2326,22 @@
         <v>6614</v>
       </c>
       <c r="C138" t="str">
-        <v>2026-07-30 15:16:30</v>
+        <v>2026-08-07 16:48:51</v>
       </c>
       <c r="D138" t="str">
         <v>NO</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>JAC  LYTS-17 G GALEA</v>
-      </c>
-      <c r="B139">
-        <v>6614</v>
-      </c>
-      <c r="C139" t="str">
-        <v>2026-07-30 16:55:36</v>
-      </c>
-      <c r="D139" t="str">
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>JAC  LYTS-17 G GALEA</v>
-      </c>
-      <c r="B140">
-        <v>6614</v>
-      </c>
-      <c r="C140" t="str">
-        <v>2026-07-30 21:58:25</v>
-      </c>
-      <c r="D140" t="str">
-        <v>SI</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D140"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D138"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2387,69 +2359,69 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>GLP ALJIBE SJHW-20</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B2">
-        <v>6583</v>
+        <v>6606</v>
       </c>
       <c r="C2">
         <v>5</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B3">
-        <v>6586</v>
+        <v>6588</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B4">
-        <v>6609</v>
+        <v>6605</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GC TSVS-89 M AEDO</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B5">
-        <v>6610</v>
+        <v>6596</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GLP DF6 RXDL-61 OPERACIONES</v>
+        <v>GC TM5-VKFB-85 M CASTRO</v>
       </c>
       <c r="B6">
-        <v>6600</v>
+        <v>6609</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -2471,10 +2443,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B8">
-        <v>6606</v>
+        <v>6598</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -2485,13 +2457,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B9">
-        <v>6588</v>
+        <v>6604</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -2499,13 +2471,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B10">
-        <v>6582</v>
+        <v>6601</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -2513,55 +2485,55 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>DONGFENG DF6 SRSR-97</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B11">
-        <v>6618</v>
+        <v>6592</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GV PEUGEOT THJY-73 J PONCE</v>
       </c>
       <c r="B12">
-        <v>6616</v>
+        <v>6595</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>GC RXDL-59 OPERACIONES</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B13">
-        <v>6581</v>
+        <v>6619</v>
       </c>
       <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
         <v>2</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GC TM5-RXXG-13 D SILVA</v>
+        <v>DONGFENG DF6 SRSR-97</v>
       </c>
       <c r="B14">
-        <v>6608</v>
+        <v>6618</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2569,13 +2541,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GC TM5-VRVJ-20 L SALINAS</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B15">
-        <v>6620</v>
+        <v>6617</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2583,13 +2555,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
+        <v>GC MAXUS PKFF-65 G VICENCIO</v>
       </c>
       <c r="B16">
-        <v>6593</v>
+        <v>6616</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2597,13 +2569,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GC TM5-RXXG-13 D SILVA</v>
       </c>
       <c r="B17">
-        <v>6598</v>
+        <v>6608</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2611,10 +2583,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B18">
-        <v>6601</v>
+        <v>6620</v>
       </c>
       <c r="C18">
         <v>4</v>
@@ -2625,13 +2597,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GC TSVS-89 M AEDO</v>
       </c>
       <c r="B19">
-        <v>6580</v>
+        <v>6610</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -2639,13 +2611,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GLP ALJIBE SJHW-20</v>
       </c>
       <c r="B20">
-        <v>6594</v>
+        <v>6583</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -2653,13 +2625,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B21">
-        <v>6603</v>
+        <v>6593</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -2667,10 +2639,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B22">
-        <v>6607</v>
+        <v>6594</v>
       </c>
       <c r="C22">
         <v>4</v>
@@ -2681,13 +2653,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B23">
-        <v>6602</v>
+        <v>6607</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2695,13 +2667,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GV FOSERO SJHW-18 V OLIVARES</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B24">
-        <v>6592</v>
+        <v>6602</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2709,13 +2681,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B25">
-        <v>6595</v>
+        <v>6612</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2723,13 +2695,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GV SHDV-50 C CARDENAS</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B26">
-        <v>6585</v>
+        <v>6599</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2737,13 +2709,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV FORD BU-9781 V OLIVARES</v>
       </c>
       <c r="B27">
-        <v>6587</v>
+        <v>6621</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2751,13 +2723,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV SHDV-50 C CARDENAS</v>
       </c>
       <c r="B28">
-        <v>6589</v>
+        <v>6585</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2765,10 +2737,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B29">
-        <v>6596</v>
+        <v>6582</v>
       </c>
       <c r="C29">
         <v>4</v>
@@ -2793,13 +2765,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>GC MAXUS PCRF-25 TERRENO</v>
+        <v>GLP DF6 RXDL-61 OPERACIONES</v>
       </c>
       <c r="B31">
-        <v>6617</v>
+        <v>6600</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2807,13 +2779,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B32">
-        <v>6604</v>
+        <v>6586</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2821,13 +2793,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B33">
-        <v>6605</v>
+        <v>6580</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2835,10 +2807,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B34">
-        <v>6612</v>
+        <v>6603</v>
       </c>
       <c r="C34">
         <v>4</v>
@@ -2849,21 +2821,35 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B35">
-        <v>6599</v>
+        <v>6587</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
+      </c>
+      <c r="B36">
+        <v>6589</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/latest-events.xlsx
+++ b/latest-events.xlsx
@@ -422,7 +422,7 @@
         <v>6618</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-08-10 09:52:36</v>
+        <v>2026-08-17 09:11:08</v>
       </c>
       <c r="D2" t="str">
         <v>NO</v>
@@ -436,10 +436,10 @@
         <v>6617</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-08-10 05:20:18</v>
+        <v>2026-08-18 12:12:46</v>
       </c>
       <c r="D3" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="4">
@@ -450,35 +450,35 @@
         <v>6616</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-08-10 22:30:15</v>
+        <v>2026-08-17 14:13:16</v>
       </c>
       <c r="D4" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GC TM5-RXXG-13 D SILVA</v>
+        <v>GC RXDL-59 OPERACIONES</v>
       </c>
       <c r="B5">
-        <v>6608</v>
+        <v>6581</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-08-10 11:21:35</v>
+        <v>2026-08-19 19:04:39</v>
       </c>
       <c r="D5" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GC TM5-RXXG-13 D SILVA</v>
       </c>
       <c r="B6">
-        <v>6609</v>
+        <v>6608</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-08-10 11:17:09</v>
+        <v>2026-08-17 10:35:53</v>
       </c>
       <c r="D6" t="str">
         <v>NO</v>
@@ -486,13 +486,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>GC TM5-VRVJ-20 L SALINAS</v>
+        <v>GC TM5-VKFB-85 M CASTRO</v>
       </c>
       <c r="B7">
-        <v>6620</v>
+        <v>6609</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-08-10 12:22:31</v>
+        <v>2026-08-17 11:18:30</v>
       </c>
       <c r="D7" t="str">
         <v>NO</v>
@@ -500,13 +500,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GC TSVS-89 M AEDO</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B8">
-        <v>6610</v>
+        <v>6620</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-08-10 09:46:18</v>
+        <v>2026-08-17 11:22:23</v>
       </c>
       <c r="D8" t="str">
         <v>NO</v>
@@ -514,13 +514,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GLP ALJIBE SJHW-20</v>
+        <v>GC TSVS-89 M AEDO</v>
       </c>
       <c r="B9">
-        <v>6583</v>
+        <v>6610</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-08-10 12:16:12</v>
+        <v>2026-08-17 09:48:32</v>
       </c>
       <c r="D9" t="str">
         <v>NO</v>
@@ -528,13 +528,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
+        <v>GLP ALJIBE SJHW-20</v>
       </c>
       <c r="B10">
-        <v>6593</v>
+        <v>6583</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-08-10 12:33:50</v>
+        <v>2026-08-17 13:48:17</v>
       </c>
       <c r="D10" t="str">
         <v>NO</v>
@@ -542,41 +542,41 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B11">
-        <v>6597</v>
+        <v>6593</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-08-10 04:29:24</v>
+        <v>2026-08-17 12:31:16</v>
       </c>
       <c r="D11" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B12">
-        <v>6598</v>
+        <v>6597</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-08-10 11:41:26</v>
+        <v>2026-08-17 04:29:03</v>
       </c>
       <c r="D12" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B13">
-        <v>6586</v>
+        <v>6598</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-08-10 11:56:55</v>
+        <v>2026-08-17 11:36:50</v>
       </c>
       <c r="D13" t="str">
         <v>NO</v>
@@ -584,27 +584,27 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B14">
-        <v>6604</v>
+        <v>6586</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-08-10 20:05:38</v>
+        <v>2026-08-17 12:06:31</v>
       </c>
       <c r="D14" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B15">
-        <v>6601</v>
+        <v>6604</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-08-10 12:35:44</v>
+        <v>2026-08-17 13:49:40</v>
       </c>
       <c r="D15" t="str">
         <v>NO</v>
@@ -612,41 +612,41 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B16">
-        <v>6606</v>
+        <v>6601</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-08-10 05:38:25</v>
+        <v>2026-08-17 13:45:10</v>
       </c>
       <c r="D16" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B17">
-        <v>6580</v>
+        <v>6606</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-08-10 12:17:45</v>
+        <v>2026-08-17 04:50:09</v>
       </c>
       <c r="D17" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B18">
-        <v>6594</v>
+        <v>6580</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-08-10 10:45:06</v>
+        <v>2026-08-17 12:07:12</v>
       </c>
       <c r="D18" t="str">
         <v>NO</v>
@@ -654,13 +654,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B19">
-        <v>6605</v>
+        <v>6594</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-08-10 12:10:17</v>
+        <v>2026-08-17 17:45:26</v>
       </c>
       <c r="D19" t="str">
         <v>NO</v>
@@ -668,13 +668,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B20">
-        <v>6603</v>
+        <v>6605</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-08-10 12:53:09</v>
+        <v>2026-08-17 14:13:45</v>
       </c>
       <c r="D20" t="str">
         <v>NO</v>
@@ -682,13 +682,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B21">
-        <v>6607</v>
+        <v>6603</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-08-10 09:23:43</v>
+        <v>2026-08-17 12:48:30</v>
       </c>
       <c r="D21" t="str">
         <v>NO</v>
@@ -696,13 +696,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B22">
-        <v>6602</v>
+        <v>6607</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-08-10 10:34:41</v>
+        <v>2026-08-17 10:14:58</v>
       </c>
       <c r="D22" t="str">
         <v>NO</v>
@@ -710,13 +710,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B23">
-        <v>6612</v>
+        <v>6602</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-08-10 12:08:15</v>
+        <v>2026-08-17 11:46:09</v>
       </c>
       <c r="D23" t="str">
         <v>NO</v>
@@ -724,13 +724,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B24">
-        <v>6599</v>
+        <v>6612</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-08-10 12:34:36</v>
+        <v>2026-08-17 12:25:12</v>
       </c>
       <c r="D24" t="str">
         <v>NO</v>
@@ -738,27 +738,27 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>GV FORD BU-9781 V OLIVARES</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B25">
-        <v>6621</v>
+        <v>6599</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-08-10 21:37:05</v>
+        <v>2026-08-17 10:25:18</v>
       </c>
       <c r="D25" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GV FOSERO SJHW-18 V OLIVARES</v>
+        <v>GV FORD BU-9781 V OLIVARES</v>
       </c>
       <c r="B26">
-        <v>6592</v>
+        <v>6621</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-08-10 08:23:42</v>
+        <v>2026-08-18 12:11:13</v>
       </c>
       <c r="D26" t="str">
         <v>NO</v>
@@ -766,13 +766,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B27">
-        <v>6595</v>
+        <v>6592</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-08-10 12:53:39</v>
+        <v>2026-08-17 08:19:27</v>
       </c>
       <c r="D27" t="str">
         <v>NO</v>
@@ -780,13 +780,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>GV SHDV-50 C CARDENAS</v>
+        <v>GV PEUGEOT THJY-73 J PONCE</v>
       </c>
       <c r="B28">
-        <v>6585</v>
+        <v>6595</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-08-10 10:41:22</v>
+        <v>2026-08-17 10:56:09</v>
       </c>
       <c r="D28" t="str">
         <v>NO</v>
@@ -794,13 +794,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV SHDV-50 C CARDENAS</v>
       </c>
       <c r="B29">
-        <v>6588</v>
+        <v>6585</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-08-10 10:00:42</v>
+        <v>2026-08-17 11:21:52</v>
       </c>
       <c r="D29" t="str">
         <v>NO</v>
@@ -808,41 +808,41 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B30">
-        <v>6587</v>
+        <v>6588</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-08-10 10:10:06</v>
+        <v>2026-08-17 19:22:51</v>
       </c>
       <c r="D30" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B31">
-        <v>6582</v>
+        <v>6587</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-08-10 05:19:51</v>
+        <v>2026-08-17 11:31:01</v>
       </c>
       <c r="D31" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B32">
-        <v>6589</v>
+        <v>6582</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-08-10 11:59:01</v>
+        <v>2026-08-17 11:53:13</v>
       </c>
       <c r="D32" t="str">
         <v>NO</v>
@@ -850,44 +850,44 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B33">
-        <v>6596</v>
+        <v>6589</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-08-10 05:13:10</v>
+        <v>2026-08-17 11:53:44</v>
       </c>
       <c r="D33" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B34">
-        <v>6619</v>
+        <v>6596</v>
       </c>
       <c r="C34" t="str">
-        <v>2026-08-10 21:58:09</v>
+        <v>2026-08-17 18:06:27</v>
       </c>
       <c r="D34" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>JAC  LYTS-17 G GALEA</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B35">
-        <v>6614</v>
+        <v>6619</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-08-10 09:53:58</v>
+        <v>2026-08-17 19:35:34</v>
       </c>
       <c r="D35" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
   </sheetData>
@@ -917,10 +917,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>GC MAXUS PCRF-25 TERRENO</v>
+        <v>GC RXDL-59 OPERACIONES</v>
       </c>
       <c r="B2">
-        <v>6617</v>
+        <v>6581</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B3">
-        <v>6616</v>
+        <v>6597</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B4">
-        <v>6597</v>
+        <v>6606</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -959,10 +959,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B5">
-        <v>6604</v>
+        <v>6588</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B6">
-        <v>6606</v>
+        <v>6619</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -987,66 +987,66 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>GV FORD BU-9781 V OLIVARES</v>
+        <v>DONGFENG DF6 SRSR-97</v>
       </c>
       <c r="B7">
-        <v>6621</v>
+        <v>6618</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B8">
-        <v>6582</v>
+        <v>6617</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>GC MAXUS PKFF-65 G VICENCIO</v>
       </c>
       <c r="B9">
-        <v>6596</v>
+        <v>6616</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+        <v>GC TM5-RXXG-13 D SILVA</v>
       </c>
       <c r="B10">
-        <v>6619</v>
+        <v>6608</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>DONGFENG DF6 SRSR-97</v>
+        <v>GC TM5-VKFB-85 M CASTRO</v>
       </c>
       <c r="B11">
-        <v>6618</v>
+        <v>6609</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1057,10 +1057,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>GC TM5-RXXG-13 D SILVA</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B12">
-        <v>6608</v>
+        <v>6620</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GC TSVS-89 M AEDO</v>
       </c>
       <c r="B13">
-        <v>6609</v>
+        <v>6610</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GC TM5-VRVJ-20 L SALINAS</v>
+        <v>GLP ALJIBE SJHW-20</v>
       </c>
       <c r="B14">
-        <v>6620</v>
+        <v>6583</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GC TSVS-89 M AEDO</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B15">
-        <v>6610</v>
+        <v>6593</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>GLP ALJIBE SJHW-20</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B16">
-        <v>6583</v>
+        <v>6598</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B17">
-        <v>6593</v>
+        <v>6586</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B18">
-        <v>6598</v>
+        <v>6604</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B19">
-        <v>6586</v>
+        <v>6601</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B20">
-        <v>6601</v>
+        <v>6580</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B21">
-        <v>6580</v>
+        <v>6594</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B22">
-        <v>6594</v>
+        <v>6605</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B23">
-        <v>6605</v>
+        <v>6603</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B24">
-        <v>6603</v>
+        <v>6607</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B25">
-        <v>6607</v>
+        <v>6602</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B26">
-        <v>6602</v>
+        <v>6612</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B27">
-        <v>6612</v>
+        <v>6599</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GV FORD BU-9781 V OLIVARES</v>
       </c>
       <c r="B28">
-        <v>6599</v>
+        <v>6621</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B32">
-        <v>6588</v>
+        <v>6587</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B33">
-        <v>6587</v>
+        <v>6582</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>JAC  LYTS-17 G GALEA</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B35">
-        <v>6614</v>
+        <v>6596</v>
       </c>
       <c r="C35">
         <v>1</v>

--- a/latest-events.xlsx
+++ b/latest-events.xlsx
@@ -422,7 +422,7 @@
         <v>6618</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-08-17 09:11:08</v>
+        <v>2026-08-24 09:52:37</v>
       </c>
       <c r="D2" t="str">
         <v>NO</v>
@@ -436,7 +436,7 @@
         <v>6617</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-08-18 12:12:46</v>
+        <v>2026-08-24 12:18:21</v>
       </c>
       <c r="D3" t="str">
         <v>NO</v>
@@ -450,7 +450,7 @@
         <v>6616</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-08-17 14:13:16</v>
+        <v>2026-08-24 09:46:56</v>
       </c>
       <c r="D4" t="str">
         <v>NO</v>
@@ -458,27 +458,27 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GC RXDL-59 OPERACIONES</v>
+        <v>GC TM5-RXXG-13 D SILVA</v>
       </c>
       <c r="B5">
-        <v>6581</v>
+        <v>6608</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-08-19 19:04:39</v>
+        <v>2026-08-24 10:22:58</v>
       </c>
       <c r="D5" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GC TM5-RXXG-13 D SILVA</v>
+        <v>GC TM5-VKFB-85 M CASTRO</v>
       </c>
       <c r="B6">
-        <v>6608</v>
+        <v>6609</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-08-17 10:35:53</v>
+        <v>2026-08-24 11:18:17</v>
       </c>
       <c r="D6" t="str">
         <v>NO</v>
@@ -486,13 +486,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B7">
-        <v>6609</v>
+        <v>6620</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-08-17 11:18:30</v>
+        <v>2026-08-24 11:23:41</v>
       </c>
       <c r="D7" t="str">
         <v>NO</v>
@@ -500,13 +500,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GC TM5-VRVJ-20 L SALINAS</v>
+        <v>GC TSVS-89 M AEDO</v>
       </c>
       <c r="B8">
-        <v>6620</v>
+        <v>6610</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-08-17 11:22:23</v>
+        <v>2026-08-24 18:02:29</v>
       </c>
       <c r="D8" t="str">
         <v>NO</v>
@@ -514,13 +514,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GC TSVS-89 M AEDO</v>
+        <v>GLP ALJIBE SJHW-20</v>
       </c>
       <c r="B9">
-        <v>6610</v>
+        <v>6583</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-08-17 09:48:32</v>
+        <v>2026-08-24 15:49:00</v>
       </c>
       <c r="D9" t="str">
         <v>NO</v>
@@ -528,13 +528,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GLP ALJIBE SJHW-20</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B10">
-        <v>6583</v>
+        <v>6593</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-08-17 13:48:17</v>
+        <v>2026-08-24 12:38:38</v>
       </c>
       <c r="D10" t="str">
         <v>NO</v>
@@ -542,41 +542,41 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B11">
-        <v>6593</v>
+        <v>6597</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-08-17 12:31:16</v>
+        <v>2026-08-24 06:52:18</v>
       </c>
       <c r="D11" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B12">
-        <v>6597</v>
+        <v>6598</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-08-17 04:29:03</v>
+        <v>2026-08-24 11:49:46</v>
       </c>
       <c r="D12" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B13">
-        <v>6598</v>
+        <v>6586</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-08-17 11:36:50</v>
+        <v>2026-08-24 12:02:22</v>
       </c>
       <c r="D13" t="str">
         <v>NO</v>
@@ -584,13 +584,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B14">
-        <v>6586</v>
+        <v>6604</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-08-17 12:06:31</v>
+        <v>2026-08-24 12:53:48</v>
       </c>
       <c r="D14" t="str">
         <v>NO</v>
@@ -598,13 +598,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B15">
-        <v>6604</v>
+        <v>6601</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-08-17 13:49:40</v>
+        <v>2026-08-24 13:31:21</v>
       </c>
       <c r="D15" t="str">
         <v>NO</v>
@@ -612,13 +612,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B16">
-        <v>6601</v>
+        <v>6606</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-08-17 13:45:10</v>
+        <v>2026-08-24 10:17:07</v>
       </c>
       <c r="D16" t="str">
         <v>NO</v>
@@ -626,27 +626,27 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B17">
-        <v>6606</v>
+        <v>6580</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-08-17 04:50:09</v>
+        <v>2026-08-24 12:00:50</v>
       </c>
       <c r="D17" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B18">
-        <v>6580</v>
+        <v>6594</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-08-17 12:07:12</v>
+        <v>2026-08-24 11:58:25</v>
       </c>
       <c r="D18" t="str">
         <v>NO</v>
@@ -654,13 +654,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B19">
-        <v>6594</v>
+        <v>6605</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-08-17 17:45:26</v>
+        <v>2026-08-24 12:37:53</v>
       </c>
       <c r="D19" t="str">
         <v>NO</v>
@@ -668,27 +668,27 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B20">
-        <v>6605</v>
+        <v>6603</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-08-17 14:13:45</v>
+        <v>2026-08-24 06:02:10</v>
       </c>
       <c r="D20" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B21">
-        <v>6603</v>
+        <v>6607</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-08-17 12:48:30</v>
+        <v>2026-08-24 10:14:42</v>
       </c>
       <c r="D21" t="str">
         <v>NO</v>
@@ -696,13 +696,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B22">
-        <v>6607</v>
+        <v>6602</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-08-17 10:14:58</v>
+        <v>2026-08-24 10:52:38</v>
       </c>
       <c r="D22" t="str">
         <v>NO</v>
@@ -710,13 +710,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B23">
-        <v>6602</v>
+        <v>6612</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-08-17 11:46:09</v>
+        <v>2026-08-24 10:48:32</v>
       </c>
       <c r="D23" t="str">
         <v>NO</v>
@@ -724,13 +724,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B24">
-        <v>6612</v>
+        <v>6599</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-08-17 12:25:12</v>
+        <v>2026-08-24 11:52:41</v>
       </c>
       <c r="D24" t="str">
         <v>NO</v>
@@ -738,13 +738,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GV FORD BU-9781 V OLIVARES</v>
       </c>
       <c r="B25">
-        <v>6599</v>
+        <v>6621</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-08-17 10:25:18</v>
+        <v>2026-08-25 12:12:37</v>
       </c>
       <c r="D25" t="str">
         <v>NO</v>
@@ -752,13 +752,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GV FORD BU-9781 V OLIVARES</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B26">
-        <v>6621</v>
+        <v>6592</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-08-18 12:11:13</v>
+        <v>2026-08-24 08:16:27</v>
       </c>
       <c r="D26" t="str">
         <v>NO</v>
@@ -766,13 +766,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GV FOSERO SJHW-18 V OLIVARES</v>
+        <v>GV PEUGEOT THJY-73 J PONCE</v>
       </c>
       <c r="B27">
-        <v>6592</v>
+        <v>6595</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-08-17 08:19:27</v>
+        <v>2026-08-24 11:13:59</v>
       </c>
       <c r="D27" t="str">
         <v>NO</v>
@@ -780,13 +780,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GV SHDV-50 C CARDENAS</v>
       </c>
       <c r="B28">
-        <v>6595</v>
+        <v>6585</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-08-17 10:56:09</v>
+        <v>2026-08-24 11:16:07</v>
       </c>
       <c r="D28" t="str">
         <v>NO</v>
@@ -794,13 +794,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>GV SHDV-50 C CARDENAS</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B29">
-        <v>6585</v>
+        <v>6588</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-08-17 11:21:52</v>
+        <v>2026-08-24 12:12:41</v>
       </c>
       <c r="D29" t="str">
         <v>NO</v>
@@ -808,27 +808,27 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B30">
-        <v>6588</v>
+        <v>6587</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-08-17 19:22:51</v>
+        <v>2026-08-24 11:24:36</v>
       </c>
       <c r="D30" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B31">
-        <v>6587</v>
+        <v>6582</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-08-17 11:31:01</v>
+        <v>2026-08-24 11:54:32</v>
       </c>
       <c r="D31" t="str">
         <v>NO</v>
@@ -836,13 +836,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B32">
-        <v>6582</v>
+        <v>6589</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-08-17 11:53:13</v>
+        <v>2026-08-24 12:01:27</v>
       </c>
       <c r="D32" t="str">
         <v>NO</v>
@@ -850,13 +850,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B33">
-        <v>6589</v>
+        <v>6596</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-08-17 11:53:44</v>
+        <v>2026-08-24 12:08:13</v>
       </c>
       <c r="D33" t="str">
         <v>NO</v>
@@ -864,13 +864,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B34">
-        <v>6596</v>
+        <v>6619</v>
       </c>
       <c r="C34" t="str">
-        <v>2026-08-17 18:06:27</v>
+        <v>2026-08-24 11:30:02</v>
       </c>
       <c r="D34" t="str">
         <v>NO</v>
@@ -878,13 +878,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+        <v>JAC  LYTS-17 G GALEA</v>
       </c>
       <c r="B35">
-        <v>6619</v>
+        <v>6614</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-08-17 19:35:34</v>
+        <v>2026-08-26 19:53:11</v>
       </c>
       <c r="D35" t="str">
         <v>SI</v>
@@ -917,10 +917,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>GC RXDL-59 OPERACIONES</v>
+        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
       </c>
       <c r="B2">
-        <v>6581</v>
+        <v>6597</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GLP DF6 SRSL-99 EMERGENCIA</v>
+        <v>GP CHANGAN RRDF-75 L LOBOS</v>
       </c>
       <c r="B3">
-        <v>6597</v>
+        <v>6603</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GLP SKDX-44 V VIAL</v>
+        <v>JAC  LYTS-17 G GALEA</v>
       </c>
       <c r="B4">
-        <v>6606</v>
+        <v>6614</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -959,38 +959,38 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GV SHLC-74 B MIRANDA</v>
+        <v>DONGFENG DF6 SRSR-97</v>
       </c>
       <c r="B5">
-        <v>6588</v>
+        <v>6618</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GV TOLVA SPGW-29 V OLIVARES</v>
+        <v>GC MAXUS PCRF-25 TERRENO</v>
       </c>
       <c r="B6">
-        <v>6619</v>
+        <v>6617</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>DONGFENG DF6 SRSR-97</v>
+        <v>GC MAXUS PKFF-65 G VICENCIO</v>
       </c>
       <c r="B7">
-        <v>6618</v>
+        <v>6616</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GC MAXUS PCRF-25 TERRENO</v>
+        <v>GC TM5-RXXG-13 D SILVA</v>
       </c>
       <c r="B8">
-        <v>6617</v>
+        <v>6608</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GC MAXUS PKFF-65 G VICENCIO</v>
+        <v>GC TM5-VKFB-85 M CASTRO</v>
       </c>
       <c r="B9">
-        <v>6616</v>
+        <v>6609</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GC TM5-RXXG-13 D SILVA</v>
+        <v>GC TM5-VRVJ-20 L SALINAS</v>
       </c>
       <c r="B10">
-        <v>6608</v>
+        <v>6620</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1043,10 +1043,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>GC TM5-VKFB-85 M CASTRO</v>
+        <v>GC TSVS-89 M AEDO</v>
       </c>
       <c r="B11">
-        <v>6609</v>
+        <v>6610</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1057,10 +1057,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>GC TM5-VRVJ-20 L SALINAS</v>
+        <v>GLP ALJIBE SJHW-20</v>
       </c>
       <c r="B12">
-        <v>6620</v>
+        <v>6583</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>GC TSVS-89 M AEDO</v>
+        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
       </c>
       <c r="B13">
-        <v>6610</v>
+        <v>6593</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GLP ALJIBE SJHW-20</v>
+        <v>GLP SHDV-51 J REBOLLEDO</v>
       </c>
       <c r="B14">
-        <v>6583</v>
+        <v>6598</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GLP DF6 SRSK-54 TOPOGRAFIA</v>
+        <v>GLP SHLC-75 L FONSECA</v>
       </c>
       <c r="B15">
-        <v>6593</v>
+        <v>6586</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>GLP SHDV-51 J REBOLLEDO</v>
+        <v>GLP SHXP-98 CAMION PLUMA</v>
       </c>
       <c r="B16">
-        <v>6598</v>
+        <v>6604</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GLP SHLC-75 L FONSECA</v>
+        <v>GLP SHXP-99 ALZA HOMBRE</v>
       </c>
       <c r="B17">
-        <v>6586</v>
+        <v>6601</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GLP SHXP-98 CAMION PLUMA</v>
+        <v>GLP SKDX-44 V VIAL</v>
       </c>
       <c r="B18">
-        <v>6604</v>
+        <v>6606</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>GLP SHXP-99 ALZA HOMBRE</v>
+        <v>GLP SSZD-71  J VALLEJOS</v>
       </c>
       <c r="B19">
-        <v>6601</v>
+        <v>6580</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>GLP SSZD-71  J VALLEJOS</v>
+        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
       </c>
       <c r="B20">
-        <v>6580</v>
+        <v>6594</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>GLP TM5 TDKV-89 PAISAJISMO</v>
+        <v>GP -SHLC-76 F SEPULVEDA</v>
       </c>
       <c r="B21">
-        <v>6594</v>
+        <v>6605</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>GP -SHLC-76 F SEPULVEDA</v>
+        <v>GP DONGFENG DF6-RXDL-60</v>
       </c>
       <c r="B22">
-        <v>6605</v>
+        <v>6607</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GP CHANGAN RRDF-75 L LOBOS</v>
+        <v>GP FOTON G7 TSVS-96</v>
       </c>
       <c r="B23">
-        <v>6603</v>
+        <v>6602</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>GP DONGFENG DF6-RXDL-60</v>
+        <v>GP TM5 TRRD-32 V PIZARRO</v>
       </c>
       <c r="B24">
-        <v>6607</v>
+        <v>6612</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>GP FOTON G7 TSVS-96</v>
+        <v>GP TM5 TSDK-95 L MUNOZ</v>
       </c>
       <c r="B25">
-        <v>6602</v>
+        <v>6599</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>GP TM5 TRRD-32 V PIZARRO</v>
+        <v>GV FORD BU-9781 V OLIVARES</v>
       </c>
       <c r="B26">
-        <v>6612</v>
+        <v>6621</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>GP TM5 TSDK-95 L MUNOZ</v>
+        <v>GV FOSERO SJHW-18 V OLIVARES</v>
       </c>
       <c r="B27">
-        <v>6599</v>
+        <v>6592</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>GV FORD BU-9781 V OLIVARES</v>
+        <v>GV PEUGEOT THJY-73 J PONCE</v>
       </c>
       <c r="B28">
-        <v>6621</v>
+        <v>6595</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>GV FOSERO SJHW-18 V OLIVARES</v>
+        <v>GV SHDV-50 C CARDENAS</v>
       </c>
       <c r="B29">
-        <v>6592</v>
+        <v>6585</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1309,10 +1309,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>GV PEUGEOT THJY-73 J PONCE</v>
+        <v>GV SHLC-74 B MIRANDA</v>
       </c>
       <c r="B30">
-        <v>6595</v>
+        <v>6588</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1323,10 +1323,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>GV SHDV-50 C CARDENAS</v>
+        <v>GV TDKV-88 L CORDERO</v>
       </c>
       <c r="B31">
-        <v>6585</v>
+        <v>6587</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>GV TDKV-88 L CORDERO</v>
+        <v>GV TDLD-98 J PACHECHO</v>
       </c>
       <c r="B32">
-        <v>6587</v>
+        <v>6582</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GV TDLD-98 J PACHECHO</v>
+        <v>GV TM5 RXXG-15 E CABANILLA</v>
       </c>
       <c r="B33">
-        <v>6582</v>
+        <v>6589</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>GV TM5 RXXG-15 E CABANILLA</v>
+        <v>GV TM5 TDLD-46 M MARTINEZ</v>
       </c>
       <c r="B34">
-        <v>6589</v>
+        <v>6596</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>GV TM5 TDLD-46 M MARTINEZ</v>
+        <v>GV TOLVA SPGW-29 V OLIVARES</v>
       </c>
       <c r="B35">
-        <v>6596</v>
+        <v>6619</v>
       </c>
       <c r="C35">
         <v>1</v>
